--- a/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
+++ b/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\South Korea\eps-southkorea\InputData\trans\AVL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flust\Desktop\trans\AVL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96FCACA-7CE5-468B-A3F1-2FD77B0C96ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{873790B0-173F-4B5F-B2EB-2E7598FFA7FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -20,23 +20,11 @@
     <sheet name="AVL" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
   <si>
     <t>Car Avg Lifetime, years (Page 22, Table 7)</t>
   </si>
@@ -400,55 +388,89 @@
     <t>SYVBT-frgt</t>
   </si>
   <si>
+    <t>LDV passenger - gasoline</t>
+  </si>
+  <si>
+    <t>LDV passenger - diesel</t>
+  </si>
+  <si>
+    <t>LDV passenger - electricity</t>
+  </si>
+  <si>
+    <t>LDV passenger - hydrogen</t>
+  </si>
+  <si>
+    <t>HDV freight - gasoline</t>
+  </si>
+  <si>
+    <t>HDV freight - diesel</t>
+  </si>
+  <si>
+    <t>HDV freight - electricity</t>
+  </si>
+  <si>
+    <t>HDV freight - hydrogen</t>
+  </si>
+  <si>
+    <t>calculated share of vehicles replaced this year</t>
+  </si>
+  <si>
     <t>Source: New vehicle registration statistics (http://stat.molit.go.kr/portal/cate/statFileView.do?hRsId=58&amp;hFormId=5)</t>
-  </si>
-  <si>
-    <t>LDV passenger - gasoline</t>
-  </si>
-  <si>
-    <t>LDV passenger - diesel</t>
-  </si>
-  <si>
-    <t>LDV passenger - electricity</t>
-  </si>
-  <si>
-    <t>LDV passenger - hydrogen</t>
-  </si>
-  <si>
-    <t>HDV freight - gasoline</t>
-  </si>
-  <si>
-    <t>HDV freight - diesel</t>
-  </si>
-  <si>
-    <t>HDV freight - electricity</t>
-  </si>
-  <si>
-    <t>HDV freight - hydrogen</t>
-  </si>
-  <si>
-    <t>calculated share of vehicles replaced this year</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>승용</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>승합</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>화물</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDV</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDV</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>Source: Decommissioning cycles by year (https://v.daum.net/v/E5WSO03fTV)</t>
+    <phoneticPr fontId="38" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="8">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="###0.00_)"/>
-    <numFmt numFmtId="165" formatCode="\(\R\)General"/>
-    <numFmt numFmtId="166" formatCode="\(\R\)\ ###0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="\(\R\)0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0_)"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="9">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="###0.00_)"/>
+    <numFmt numFmtId="178" formatCode="\(\R\)General"/>
+    <numFmt numFmtId="179" formatCode="\(\R\)\ ###0"/>
+    <numFmt numFmtId="180" formatCode="0.0"/>
+    <numFmt numFmtId="181" formatCode="\(\R\)0.0"/>
+    <numFmt numFmtId="182" formatCode="#,##0_)"/>
+    <numFmt numFmtId="183" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="184" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -456,7 +478,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -464,7 +486,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -472,14 +494,14 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -487,7 +509,7 @@
       <u/>
       <sz val="10"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -502,7 +524,7 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -519,14 +541,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -534,7 +556,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Cambria"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -542,7 +564,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -550,7 +572,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -558,35 +580,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -594,7 +616,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -602,14 +624,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -617,14 +639,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -632,21 +654,21 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -703,8 +725,23 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1280,7 +1317,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10">
@@ -1337,12 +1374,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="10">
+    <xf numFmtId="182" fontId="33" fillId="0" borderId="10">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1465,10 +1502,10 @@
     <xf numFmtId="1" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1480,7 +1517,7 @@
     <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1505,23 +1542,23 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1555,8 +1592,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1581,72 +1619,75 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="24" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="184" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="63">
-    <cellStyle name="20% - Accent1" xfId="35" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="39" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="43" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="47" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="51" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="55" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="36" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="40" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="44" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="48" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="52" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="56" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="37" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="41" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="45" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="49" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="53" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="57" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="34" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="38" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="42" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="46" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="50" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="54" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색1" xfId="35" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="39" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="43" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="47" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="51" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="55" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="36" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="40" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="44" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="48" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="52" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="56" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="37" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="41" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="45" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="49" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="53" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="57" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Body: normal cell" xfId="3" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Calculation" xfId="27" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="29" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="62" builtinId="3"/>
     <cellStyle name="Data" xfId="14" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
     <cellStyle name="Data no deci" xfId="61" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="Explanatory Text" xfId="32" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="11" builtinId="9" customBuiltin="1"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="9" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="Footnotes: all except top row" xfId="12" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
     <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="Good" xfId="22" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Header: bottom row" xfId="2" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="Header: top rows" xfId="4" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="19" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="20" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="21" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Hed Side" xfId="15" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
     <cellStyle name="Hed Side Regular" xfId="60" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="Hed Top" xfId="59" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="Input" xfId="25" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="28" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="31" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="26" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Percent" xfId="16" builtinId="5"/>
     <cellStyle name="Section Break" xfId="8" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="Section Break: parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="Table title" xfId="13" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="Title" xfId="17" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Title-2" xfId="58" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="Total" xfId="33" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="30" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="34" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="38" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="42" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="46" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="50" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="54" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="30" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="27" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="23" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="31" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="백분율" xfId="16" builtinId="5"/>
+    <cellStyle name="보통" xfId="24" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="32" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="29" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="쉼표" xfId="62" builtinId="3"/>
+    <cellStyle name="연결된 셀" xfId="28" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="열어 본 하이퍼링크" xfId="11" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="33" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="25" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="17" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="18" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="19" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="20" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="21" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="22" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="26" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1692,7 +1733,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2013,17 +2054,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="132.26953125" customWidth="1"/>
+    <col min="2" max="2" width="132.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
@@ -2031,238 +2072,239 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
         <v>2006</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
         <v>2016</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="10">
         <v>2015</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="10">
         <v>2019</v>
       </c>
     </row>
-    <row r="27" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="10">
         <v>2013</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" s="20">
         <v>2009</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="25" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B49" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>99</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="38" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -2277,74 +2319,74 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC61"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" style="13" customWidth="1"/>
-    <col min="2" max="27" width="7.7265625" style="13" customWidth="1"/>
-    <col min="28" max="28" width="7.08984375" style="77" customWidth="1"/>
-    <col min="29" max="55" width="9.08984375" style="77"/>
-    <col min="56" max="16384" width="9.08984375" style="13"/>
+    <col min="1" max="1" width="19.375" style="13" customWidth="1"/>
+    <col min="2" max="27" width="7.75" style="13" customWidth="1"/>
+    <col min="28" max="28" width="7.125" style="77" customWidth="1"/>
+    <col min="29" max="55" width="9.125" style="77"/>
+    <col min="56" max="16384" width="9.125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
-      <c r="W1" s="94"/>
-      <c r="X1" s="94"/>
-      <c r="Y1" s="94"/>
-      <c r="Z1" s="94"/>
-      <c r="AA1" s="94"/>
-      <c r="AB1" s="94"/>
-      <c r="AC1" s="95"/>
-      <c r="AD1" s="95"/>
-      <c r="AE1" s="95"/>
-      <c r="AF1" s="95"/>
-      <c r="AG1" s="95"/>
-      <c r="AH1" s="95"/>
-      <c r="AI1" s="95"/>
-      <c r="AJ1" s="95"/>
-      <c r="AK1" s="95"/>
-      <c r="AL1" s="95"/>
-      <c r="AM1" s="95"/>
-      <c r="AN1" s="95"/>
-      <c r="AO1" s="95"/>
-      <c r="AP1" s="95"/>
-      <c r="AQ1" s="95"/>
-      <c r="AR1" s="95"/>
-      <c r="AS1" s="95"/>
-      <c r="AT1" s="95"/>
-      <c r="AU1" s="95"/>
-      <c r="AV1" s="95"/>
-      <c r="AW1" s="95"/>
-      <c r="AX1" s="95"/>
-      <c r="AY1" s="95"/>
-      <c r="AZ1" s="95"/>
-      <c r="BA1" s="95"/>
-      <c r="BB1" s="95"/>
-    </row>
-    <row r="2" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="95"/>
+      <c r="Y1" s="95"/>
+      <c r="Z1" s="95"/>
+      <c r="AA1" s="95"/>
+      <c r="AB1" s="95"/>
+      <c r="AC1" s="96"/>
+      <c r="AD1" s="96"/>
+      <c r="AE1" s="96"/>
+      <c r="AF1" s="96"/>
+      <c r="AG1" s="96"/>
+      <c r="AH1" s="96"/>
+      <c r="AI1" s="96"/>
+      <c r="AJ1" s="96"/>
+      <c r="AK1" s="96"/>
+      <c r="AL1" s="96"/>
+      <c r="AM1" s="96"/>
+      <c r="AN1" s="96"/>
+      <c r="AO1" s="96"/>
+      <c r="AP1" s="96"/>
+      <c r="AQ1" s="96"/>
+      <c r="AR1" s="96"/>
+      <c r="AS1" s="96"/>
+      <c r="AT1" s="96"/>
+      <c r="AU1" s="96"/>
+      <c r="AV1" s="96"/>
+      <c r="AW1" s="96"/>
+      <c r="AX1" s="96"/>
+      <c r="AY1" s="96"/>
+      <c r="AZ1" s="96"/>
+      <c r="BA1" s="96"/>
+      <c r="BB1" s="96"/>
+    </row>
+    <row r="2" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46"/>
       <c r="B2" s="47">
         <v>1980</v>
@@ -2454,7 +2496,7 @@
       <c r="BA2" s="53"/>
       <c r="BB2" s="54"/>
     </row>
-    <row r="3" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
         <v>65</v>
       </c>
@@ -2566,7 +2608,7 @@
       <c r="BA3" s="58"/>
       <c r="BB3" s="58"/>
     </row>
-    <row r="4" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="59" t="s">
         <v>67</v>
       </c>
@@ -2678,7 +2720,7 @@
       <c r="BA4" s="63"/>
       <c r="BB4" s="63"/>
     </row>
-    <row r="5" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="59" t="s">
         <v>68</v>
       </c>
@@ -2790,7 +2832,7 @@
       <c r="BA5" s="63"/>
       <c r="BB5" s="63"/>
     </row>
-    <row r="6" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="59" t="s">
         <v>69</v>
       </c>
@@ -2902,7 +2944,7 @@
       <c r="BA6" s="63"/>
       <c r="BB6" s="63"/>
     </row>
-    <row r="7" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="59" t="s">
         <v>70</v>
       </c>
@@ -3014,7 +3056,7 @@
       <c r="BA7" s="63"/>
       <c r="BB7" s="63"/>
     </row>
-    <row r="8" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="59" t="s">
         <v>71</v>
       </c>
@@ -3126,7 +3168,7 @@
       <c r="BA8" s="63"/>
       <c r="BB8" s="63"/>
     </row>
-    <row r="9" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
         <v>72</v>
       </c>
@@ -3184,7 +3226,7 @@
       <c r="BA9" s="66"/>
       <c r="BB9" s="66"/>
     </row>
-    <row r="10" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59" t="s">
         <v>67</v>
       </c>
@@ -3298,7 +3340,7 @@
       <c r="BA10" s="68"/>
       <c r="BB10" s="68"/>
     </row>
-    <row r="11" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="59" t="s">
         <v>68</v>
       </c>
@@ -3410,7 +3452,7 @@
       <c r="BA11" s="68"/>
       <c r="BB11" s="68"/>
     </row>
-    <row r="12" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="59" t="s">
         <v>69</v>
       </c>
@@ -3522,7 +3564,7 @@
       <c r="BA12" s="68"/>
       <c r="BB12" s="68"/>
     </row>
-    <row r="13" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="59" t="s">
         <v>70</v>
       </c>
@@ -3634,7 +3676,7 @@
       <c r="BA13" s="68"/>
       <c r="BB13" s="68"/>
     </row>
-    <row r="14" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="59" t="s">
         <v>71</v>
       </c>
@@ -3746,7 +3788,7 @@
       <c r="BA14" s="68"/>
       <c r="BB14" s="68"/>
     </row>
-    <row r="15" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="55" t="s">
         <v>73</v>
       </c>
@@ -3804,7 +3846,7 @@
       <c r="BA15" s="70"/>
       <c r="BB15" s="70"/>
     </row>
-    <row r="16" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="59" t="s">
         <v>67</v>
       </c>
@@ -3916,7 +3958,7 @@
       <c r="BA16" s="72"/>
       <c r="BB16" s="72"/>
     </row>
-    <row r="17" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="59" t="s">
         <v>68</v>
       </c>
@@ -4028,7 +4070,7 @@
       <c r="BA17" s="72"/>
       <c r="BB17" s="72"/>
     </row>
-    <row r="18" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="59" t="s">
         <v>69</v>
       </c>
@@ -4140,7 +4182,7 @@
       <c r="BA18" s="72"/>
       <c r="BB18" s="72"/>
     </row>
-    <row r="19" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="59" t="s">
         <v>70</v>
       </c>
@@ -4252,7 +4294,7 @@
       <c r="BA19" s="72"/>
       <c r="BB19" s="72"/>
     </row>
-    <row r="20" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="73" t="s">
         <v>71</v>
       </c>
@@ -4364,223 +4406,223 @@
       <c r="BA20" s="72"/>
       <c r="BB20" s="72"/>
     </row>
-    <row r="21" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="96" t="s">
+    <row r="21" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="96"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96"/>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96"/>
-      <c r="Q21" s="96"/>
-    </row>
-    <row r="22" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
-      <c r="B22" s="97"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="97"/>
-      <c r="F22" s="97"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="97"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="97"/>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="97"/>
-      <c r="Q22" s="97"/>
-    </row>
-    <row r="23" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97" t="s">
+      <c r="B21" s="97"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="97"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="97"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="97"/>
+      <c r="Q21" s="97"/>
+    </row>
+    <row r="22" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="98"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="98"/>
+      <c r="K22" s="98"/>
+      <c r="L22" s="98"/>
+      <c r="M22" s="98"/>
+      <c r="N22" s="98"/>
+      <c r="O22" s="98"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="98"/>
+    </row>
+    <row r="23" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="97"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="97"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="97"/>
-    </row>
-    <row r="24" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="90" t="s">
+      <c r="B23" s="98"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="98"/>
+      <c r="J23" s="98"/>
+      <c r="K23" s="98"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="98"/>
+      <c r="N23" s="98"/>
+      <c r="O23" s="98"/>
+      <c r="P23" s="98"/>
+      <c r="Q23" s="98"/>
+    </row>
+    <row r="24" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="90"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="90"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="90"/>
-    </row>
-    <row r="25" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="90" t="s">
+      <c r="B24" s="91"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="91"/>
+      <c r="Q24" s="91"/>
+    </row>
+    <row r="25" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="90"/>
-      <c r="K25" s="90"/>
-      <c r="L25" s="90"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="O25" s="90"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="90"/>
-    </row>
-    <row r="26" spans="1:54" s="76" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="91" t="s">
+      <c r="B25" s="91"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="91"/>
+    </row>
+    <row r="26" spans="1:54" s="76" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="91"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="91"/>
-      <c r="M26" s="91"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="91"/>
-      <c r="Q26" s="91"/>
-    </row>
-    <row r="27" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="91"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="91"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="91"/>
-      <c r="Q27" s="91"/>
-    </row>
-    <row r="28" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="92" t="s">
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="92"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="92"/>
+    </row>
+    <row r="27" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="92"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="92"/>
+      <c r="O27" s="92"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="92"/>
+    </row>
+    <row r="28" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="92"/>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="92"/>
-      <c r="L28" s="92"/>
-      <c r="M28" s="92"/>
-      <c r="N28" s="92"/>
-      <c r="O28" s="92"/>
-      <c r="P28" s="92"/>
-      <c r="Q28" s="92"/>
-    </row>
-    <row r="29" spans="1:54" s="76" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="93" t="s">
+      <c r="B28" s="93"/>
+      <c r="C28" s="93"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="93"/>
+      <c r="N28" s="93"/>
+      <c r="O28" s="93"/>
+      <c r="P28" s="93"/>
+      <c r="Q28" s="93"/>
+    </row>
+    <row r="29" spans="1:54" s="76" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="93"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="93"/>
-      <c r="O29" s="93"/>
-      <c r="P29" s="93"/>
-      <c r="Q29" s="93"/>
-    </row>
-    <row r="30" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="33" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="34" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="39" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="40" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="42" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="43" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="44" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="46" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="47" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="48" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="49" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="50" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="51" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="53" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="54" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="55" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="56" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="57" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="59" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="60" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" s="77" customFormat="1" x14ac:dyDescent="0.35"/>
+      <c r="B29" s="94"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="94"/>
+      <c r="L29" s="94"/>
+      <c r="M29" s="94"/>
+      <c r="N29" s="94"/>
+      <c r="O29" s="94"/>
+      <c r="P29" s="94"/>
+      <c r="Q29" s="94"/>
+    </row>
+    <row r="30" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="35" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="36" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="40" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="41" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="42" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="43" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="44" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="45" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="46" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="48" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="49" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="50" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="51" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="53" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="56" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="57" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="58" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="59" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="60" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A24:Q24"/>
@@ -4595,6 +4637,7 @@
     <mergeCell ref="A28:Q28"/>
     <mergeCell ref="A29:Q29"/>
   </mergeCells>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4602,17 +4645,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.08984375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.81640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.26953125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.7265625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.08984375" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9.08984375" style="3"/>
+    <col min="1" max="1" width="30.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.125" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -4621,7 +4664,7 @@
       <c r="D1" s="40"/>
       <c r="E1" s="40"/>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4638,7 +4681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>13</v>
       </c>
@@ -4658,12 +4701,12 @@
         <v>13.378781688359696</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>59</v>
       </c>
@@ -4678,7 +4721,7 @@
       </c>
       <c r="E6" s="84"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="86">
         <v>28</v>
       </c>
@@ -4693,13 +4736,13 @@
       </c>
       <c r="E7" s="85"/>
     </row>
-    <row r="8" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="81"/>
       <c r="B8" s="81"/>
       <c r="C8" s="82"/>
       <c r="D8" s="82"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>56</v>
       </c>
@@ -4708,14 +4751,14 @@
       <c r="D10" s="42"/>
       <c r="E10" s="42"/>
     </row>
-    <row r="11" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="18"/>
     </row>
-    <row r="12" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>34</v>
       </c>
@@ -4723,7 +4766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>36</v>
       </c>
@@ -4731,7 +4774,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" s="10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>38</v>
       </c>
@@ -4739,19 +4782,19 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="22"/>
     </row>
-    <row r="16" spans="1:5" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" s="10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="24">
         <v>24</v>
       </c>
       <c r="C16" s="21"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>21</v>
       </c>
@@ -4760,7 +4803,7 @@
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="41" t="s">
         <v>10</v>
       </c>
@@ -4771,7 +4814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>22</v>
       </c>
@@ -4782,7 +4825,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>24</v>
       </c>
@@ -4793,7 +4836,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="14" t="s">
         <v>26</v>
@@ -4802,17 +4845,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>13</v>
       </c>
@@ -4821,7 +4864,7 @@
       <c r="D26" s="42"/>
       <c r="E26" s="42"/>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="41" t="s">
         <v>10</v>
       </c>
@@ -4832,7 +4875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>14</v>
       </c>
@@ -4843,7 +4886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
         <v>58</v>
       </c>
@@ -4852,7 +4895,7 @@
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
     </row>
-    <row r="31" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
         <v>43</v>
       </c>
@@ -4869,7 +4912,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="26">
         <v>1997</v>
       </c>
@@ -4882,7 +4925,7 @@
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="26">
         <v>1998</v>
       </c>
@@ -4901,7 +4944,7 @@
         <v>6.6484424338501588E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="26">
         <v>1999</v>
       </c>
@@ -4920,7 +4963,7 @@
         <v>2.9143636995467476E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="26">
         <v>2000</v>
       </c>
@@ -4939,7 +4982,7 @@
         <v>6.8191523924614153E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="26">
         <v>2001</v>
       </c>
@@ -4958,7 +5001,7 @@
         <v>4.0815360868813244E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
         <v>2002</v>
       </c>
@@ -4977,7 +5020,7 @@
         <v>0.10769048766665149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="26">
         <v>2003</v>
       </c>
@@ -4996,7 +5039,7 @@
         <v>5.9053805049687755E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="26">
         <v>2004</v>
       </c>
@@ -5015,7 +5058,7 @@
         <v>5.8670234757052138E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="26">
         <v>2005</v>
       </c>
@@ -5034,7 +5077,7 @@
         <v>6.1781753631599455E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="26">
         <v>2006</v>
       </c>
@@ -5053,7 +5096,7 @@
         <v>6.5906687839630079E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="31">
         <v>2007</v>
       </c>
@@ -5072,14 +5115,14 @@
         <v>5.9604038733197397E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -5087,7 +5130,7 @@
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="34">
         <f>AVERAGE(E33:E42)</f>
         <v>5.8060812902328285E-2</v>
@@ -5096,13 +5139,13 @@
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
     </row>
-    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
     </row>
-    <row r="47" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" s="44" t="s">
         <v>48</v>
       </c>
@@ -5110,7 +5153,7 @@
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
     </row>
-    <row r="48" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="43">
         <f>1/A45</f>
         <v>17.22332068760786</v>
@@ -5120,6 +5163,7 @@
       <c r="D48" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="C3:D3" formulaRange="1"/>
@@ -5129,25 +5173,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD149825-14BA-415D-91AD-354F00EEF420}">
-  <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" style="88" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" style="88" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.08984375" style="88" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.54296875" style="88" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="88" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" style="88" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.08984375" style="88" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="88"/>
+    <col min="1" max="1" width="19.125" style="88" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="88" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="88" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" style="88" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="88" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="88" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" style="88" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.75" style="88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="88" t="s">
         <v>101</v>
       </c>
@@ -5173,59 +5217,59 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="88" t="s">
         <v>52</v>
       </c>
       <c r="C3" s="88">
-        <v>63750.17917891738</v>
+        <v>84650.742266925648</v>
       </c>
       <c r="D3" s="88">
-        <v>26529.653513907131</v>
+        <v>25214.586997392125</v>
       </c>
       <c r="E3" s="88">
-        <v>7863874.8584673926</v>
+        <v>8072982.1194173032</v>
       </c>
       <c r="F3" s="88">
-        <v>4673131.4869109076</v>
+        <v>4633956.5131107848</v>
       </c>
       <c r="G3" s="88">
-        <v>363483.18862196186</v>
+        <v>477958.89831224794</v>
       </c>
       <c r="H3" s="88">
-        <v>1352441.2970028589</v>
+        <v>1315953.270937951</v>
       </c>
       <c r="I3" s="88">
-        <v>3651.0147234652754</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+        <v>7728.5710293009906</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="88" t="s">
         <v>55</v>
       </c>
       <c r="C4" s="88">
-        <v>25003.820821082623</v>
+        <v>34802.257733074344</v>
       </c>
       <c r="D4" s="88">
-        <v>10353.088786529765</v>
+        <v>10314.28274882044</v>
       </c>
       <c r="E4" s="88">
-        <v>3068845.0029395702</v>
+        <v>3302335.2797511155</v>
       </c>
       <c r="F4" s="88">
-        <v>1823670.4512463559</v>
+        <v>1895566.9480886636</v>
       </c>
       <c r="G4" s="88">
-        <v>141847.82783693049</v>
+        <v>195513.93881712668</v>
       </c>
       <c r="H4" s="88">
-        <v>527784.68512979639</v>
+        <v>538304.04289758822</v>
       </c>
       <c r="I4" s="88">
-        <v>1424.7935644221143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>3161.4504274369956</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="88" t="s">
         <v>56</v>
       </c>
@@ -5251,7 +5295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="88" t="s">
         <v>21</v>
       </c>
@@ -5277,7 +5321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="88" t="s">
         <v>13</v>
       </c>
@@ -5303,7 +5347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="88" t="s">
         <v>58</v>
       </c>
@@ -5314,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="88">
-        <v>256111</v>
+        <v>272564</v>
       </c>
       <c r="F8" s="88">
         <v>0</v>
@@ -5329,12 +5373,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="88" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="88" t="s">
         <v>101</v>
       </c>
@@ -5360,59 +5404,59 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="88" t="s">
         <v>52</v>
       </c>
       <c r="C12" s="88">
-        <v>907.7514621547972</v>
+        <v>11965.956562995307</v>
       </c>
       <c r="D12" s="88">
-        <v>1217</v>
+        <v>1366</v>
       </c>
       <c r="E12" s="88">
-        <v>9802.0001098141292</v>
+        <v>14255.143043258835</v>
       </c>
       <c r="F12" s="88">
-        <v>2691698.325326392</v>
+        <v>2664174.8230804084</v>
       </c>
       <c r="G12" s="88">
         <v>0</v>
       </c>
       <c r="H12" s="88">
-        <v>95017.558547199747</v>
+        <v>94459.997166222995</v>
       </c>
       <c r="I12" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="88" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="88">
-        <v>256.24853784520275</v>
+        <v>3543.0434370046937</v>
       </c>
       <c r="D13" s="88">
         <v>0</v>
       </c>
       <c r="E13" s="88">
-        <v>2766.9998901858708</v>
+        <v>4220.8569567411641</v>
       </c>
       <c r="F13" s="88">
-        <v>759837.67467360804</v>
+        <v>788845.17691959161</v>
       </c>
       <c r="G13" s="88">
         <v>0</v>
       </c>
       <c r="H13" s="88">
-        <v>26822.441452800264</v>
+        <v>27969.002833777009</v>
       </c>
       <c r="I13" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="88" t="s">
         <v>56</v>
       </c>
@@ -5438,7 +5482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="88" t="s">
         <v>21</v>
       </c>
@@ -5464,7 +5508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="88" t="s">
         <v>13</v>
       </c>
@@ -5475,22 +5519,22 @@
         <v>0</v>
       </c>
       <c r="E16" s="88">
-        <v>2.0689959414152108</v>
+        <v>2.1101699900005881</v>
       </c>
       <c r="F16" s="88">
-        <v>1404.1034056820188</v>
+        <v>630.10013528615957</v>
       </c>
       <c r="G16" s="88">
         <v>0</v>
       </c>
       <c r="H16" s="88">
-        <v>0.82759837656608437</v>
+        <v>0.8440679960002353</v>
       </c>
       <c r="I16" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" s="88" t="s">
         <v>58</v>
       </c>
@@ -5501,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="88">
-        <v>1980784</v>
+        <v>2016445</v>
       </c>
       <c r="F17" s="88">
         <v>0</v>
@@ -5516,138 +5560,300 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="88" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" s="88">
         <v>2019</v>
       </c>
       <c r="C22" s="89" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="88" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B23" s="88">
         <v>688548.12375329144</v>
       </c>
-      <c r="C23" s="98">
+      <c r="C23" s="90">
         <f>B23/E3</f>
-        <v>8.7558377535967555E-2</v>
+        <v>8.5290430917365878E-2</v>
       </c>
       <c r="D23" s="88">
         <f>1/C23</f>
-        <v>11.42095169122128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+        <v>11.724644713881862</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="88" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B24" s="88">
         <v>409171.81100616272</v>
       </c>
-      <c r="C24" s="98">
+      <c r="C24" s="90">
         <f>B24/F3</f>
-        <v>8.7558377535967569E-2</v>
+        <v>8.8298586714937649E-2</v>
       </c>
       <c r="D24" s="88">
         <f t="shared" ref="D24:D30" si="0">1/C24</f>
-        <v>11.420951691221278</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+        <v>11.325209578137313</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B25" s="88">
         <v>23570.553989311142</v>
       </c>
-      <c r="C25" s="98">
+      <c r="C25" s="90">
         <f>B25/C3</f>
-        <v>0.36973314103415234</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0.27844474080318277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="88" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B26" s="88">
         <v>3006.7960130674305</v>
       </c>
-      <c r="C26" s="98">
+      <c r="C26" s="90">
         <f>B26/I3</f>
-        <v>0.82355077719697611</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C27" s="98"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C28" s="98"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0.38904941180819808</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="90"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="90"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="88" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="88">
         <v>206.54622970105956</v>
       </c>
-      <c r="C29" s="98">
+      <c r="C29" s="90">
         <f>B29/E13</f>
-        <v>7.4646273183330336E-2</v>
+        <v>4.8934667016180905E-2</v>
       </c>
       <c r="D29" s="88">
         <f t="shared" si="0"/>
-        <v>13.396516093228287</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+        <v>20.43541033331925</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="88">
         <v>56719.050638672627</v>
       </c>
-      <c r="C30" s="98">
+      <c r="C30" s="90">
         <f>B30/F13</f>
-        <v>7.4646273183330336E-2</v>
+        <v>7.190137215538063E-2</v>
       </c>
       <c r="D30" s="88">
         <f t="shared" si="0"/>
-        <v>13.396516093228287</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+        <v>13.907940419258974</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="88" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B31" s="88">
         <v>243.47183425946551</v>
       </c>
-      <c r="C31" s="98">
+      <c r="C31" s="90">
         <f>B31/C13</f>
-        <v>0.95013940882091774</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+        <v>6.8718275287445466E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="88" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B32" s="88">
         <v>0</v>
       </c>
-      <c r="C32" s="98" t="e">
+      <c r="C32" s="90" t="e">
         <f>B32/I13</f>
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="100" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="100"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="100"/>
+      <c r="B35" s="100">
+        <v>2000</v>
+      </c>
+      <c r="C35" s="100">
+        <v>2005</v>
+      </c>
+      <c r="D35" s="100">
+        <v>2010</v>
+      </c>
+      <c r="E35" s="100">
+        <v>2015</v>
+      </c>
+      <c r="F35" s="100">
+        <v>2020</v>
+      </c>
+      <c r="G35" s="100">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="102">
+        <v>8.4</v>
+      </c>
+      <c r="C36" s="102">
+        <v>11.2</v>
+      </c>
+      <c r="D36" s="102">
+        <v>13.4</v>
+      </c>
+      <c r="E36" s="102">
+        <v>14.8</v>
+      </c>
+      <c r="F36" s="102">
+        <v>15.3</v>
+      </c>
+      <c r="G36" s="102">
+        <v>15.6</v>
+      </c>
+      <c r="I36" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="J36" s="101">
+        <f>AVERAGE(F36:F37)</f>
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="102">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C37" s="102">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D37" s="102">
+        <v>12</v>
+      </c>
+      <c r="E37" s="102">
+        <v>14.9</v>
+      </c>
+      <c r="F37" s="102">
+        <v>15.5</v>
+      </c>
+      <c r="G37" s="102">
+        <v>15.5</v>
+      </c>
+      <c r="I37" s="101" t="s">
+        <v>127</v>
+      </c>
+      <c r="J37" s="101">
+        <f>AVERAGE(F38:F39)</f>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="102">
+        <v>8</v>
+      </c>
+      <c r="C38" s="102">
+        <v>10.9</v>
+      </c>
+      <c r="D38" s="102">
+        <v>8</v>
+      </c>
+      <c r="E38" s="102">
+        <v>15.1</v>
+      </c>
+      <c r="F38" s="102">
+        <v>16.8</v>
+      </c>
+      <c r="G38" s="102">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="102">
+        <v>9.9</v>
+      </c>
+      <c r="C39" s="102">
+        <v>11.9</v>
+      </c>
+      <c r="D39" s="102">
+        <v>15.6</v>
+      </c>
+      <c r="E39" s="102">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="F39" s="102">
+        <v>16.8</v>
+      </c>
+      <c r="G39" s="102">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="100" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="102">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C40" s="102">
+        <v>11.05</v>
+      </c>
+      <c r="D40" s="102">
+        <v>13.25</v>
+      </c>
+      <c r="E40" s="102">
+        <v>14.87</v>
+      </c>
+      <c r="F40" s="102">
+        <v>15.59</v>
+      </c>
+      <c r="G40" s="102">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5659,14 +5865,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A1" s="87" t="s">
         <v>100</v>
       </c>
@@ -5677,33 +5883,33 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="45">
-        <f>'SK calcs'!D23</f>
-        <v>11.42095169122128</v>
-      </c>
-      <c r="C2" s="45">
-        <f>B2</f>
-        <v>11.42095169122128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B2" s="99">
+        <f>'SK calcs'!J36</f>
+        <v>15.4</v>
+      </c>
+      <c r="C2" s="99">
+        <f t="shared" ref="C2:C7" si="0">B2</f>
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="45">
-        <f>'SK calcs'!D29</f>
-        <v>13.396516093228287</v>
-      </c>
-      <c r="C3" s="45">
-        <f>B3</f>
-        <v>13.396516093228287</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="99">
+        <f>'SK calcs'!J37</f>
+        <v>16.8</v>
+      </c>
+      <c r="C3" s="99">
+        <f t="shared" si="0"/>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -5712,11 +5918,11 @@
         <v>24</v>
       </c>
       <c r="C4" s="45">
-        <f>B4</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -5725,11 +5931,11 @@
         <v>34</v>
       </c>
       <c r="C5">
-        <f>B5</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -5738,11 +5944,11 @@
         <v>33</v>
       </c>
       <c r="C6">
-        <f>B6</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -5751,16 +5957,23 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <f>B7</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -5904,7 +6117,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5913,20 +6126,44 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A9F799-6530-441C-9A49-116D487C0166}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B68363-87CD-464E-8916-DF6FCE3B5AB7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A9F799-6530-441C-9A49-116D487C0166}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B68363-87CD-464E-8916-DF6FCE3B5AB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
+++ b/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flust\Desktop\trans\AVL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\AVL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{873790B0-173F-4B5F-B2EB-2E7598FFA7FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF34157-7591-4A0D-850C-5B993E103A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="24120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32595" yWindow="3795" windowWidth="20145" windowHeight="11235" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="SK calcs" sheetId="12" r:id="rId4"/>
     <sheet name="AVL" sheetId="10" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -456,21 +469,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="9">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="###0.00_)"/>
-    <numFmt numFmtId="178" formatCode="\(\R\)General"/>
-    <numFmt numFmtId="179" formatCode="\(\R\)\ ###0"/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="181" formatCode="\(\R\)0.0"/>
-    <numFmt numFmtId="182" formatCode="#,##0_)"/>
-    <numFmt numFmtId="183" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="184" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="###0.00_)"/>
+    <numFmt numFmtId="165" formatCode="\(\R\)General"/>
+    <numFmt numFmtId="166" formatCode="\(\R\)\ ###0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="\(\R\)0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0_)"/>
+    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -478,7 +491,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -486,7 +499,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -494,14 +507,14 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -509,7 +522,7 @@
       <u/>
       <sz val="10"/>
       <color theme="4"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -524,7 +537,7 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -541,14 +554,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -556,7 +569,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Cambria"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -564,7 +577,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -572,7 +585,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -580,35 +593,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -616,7 +629,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -624,14 +637,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -639,14 +652,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -654,21 +667,21 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -725,13 +738,13 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -739,7 +752,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1317,7 +1330,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10">
@@ -1374,12 +1387,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="33" fillId="0" borderId="10">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="10">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1399,17 +1412,12 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1426,15 +1434,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1454,7 +1453,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1469,9 +1468,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1483,9 +1479,6 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1502,88 +1495,70 @@
     <xf numFmtId="1" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="59" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1592,102 +1567,102 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="183" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="183" fontId="24" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="183" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="63">
-    <cellStyle name="20% - 강조색1" xfId="35" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="39" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="43" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="47" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="51" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="55" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="36" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="40" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="44" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="48" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="52" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="56" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="37" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="41" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="45" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="49" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="53" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="57" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="35" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="39" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="43" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="47" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="51" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="55" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="36" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="40" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="44" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="48" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="52" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="56" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="37" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="41" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="45" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="49" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="53" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="57" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="34" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="38" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="42" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="46" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="50" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="54" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Body: normal cell" xfId="3" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Calculation" xfId="27" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="29" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="62" builtinId="3"/>
     <cellStyle name="Data" xfId="14" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
     <cellStyle name="Data no deci" xfId="61" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Explanatory Text" xfId="32" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="11" builtinId="9" customBuiltin="1"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="9" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="Footnotes: all except top row" xfId="12" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
     <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Good" xfId="22" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Header: bottom row" xfId="2" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="Header: top rows" xfId="4" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Heading 1" xfId="18" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="19" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="20" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="21" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Hed Side" xfId="15" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
     <cellStyle name="Hed Side Regular" xfId="60" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="Hed Top" xfId="59" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Input" xfId="25" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="28" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="31" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="26" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Percent" xfId="16" builtinId="5"/>
     <cellStyle name="Section Break" xfId="8" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="Section Break: parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="Table title" xfId="13" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Title" xfId="17" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Title-2" xfId="58" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="강조색1" xfId="34" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="38" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="42" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="46" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="50" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="54" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="30" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="27" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="23" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="31" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="백분율" xfId="16" builtinId="5"/>
-    <cellStyle name="보통" xfId="24" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="32" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="29" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="62" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="28" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="열어 본 하이퍼링크" xfId="11" builtinId="9" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="33" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="25" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="17" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="18" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="19" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="20" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="21" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="22" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="26" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Total" xfId="33" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="30" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1733,9 +1708,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1773,9 +1748,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1808,26 +1783,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1860,26 +1818,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2054,251 +1995,251 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="132.25" customWidth="1"/>
+    <col min="2" max="2" width="132.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="10">
+    <row r="5" spans="1:2">
+      <c r="B5" s="9">
         <v>2006</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="B10" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B12" s="10">
+    <row r="12" spans="1:2">
+      <c r="B12" s="9">
         <v>2016</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B15" s="9" t="s">
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2">
       <c r="B17" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="10">
+    <row r="19" spans="2:2">
+      <c r="B19" s="9">
         <v>2015</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2">
       <c r="B21" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2"/>
+    <row r="24" spans="2:2">
       <c r="B24" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="9" t="s">
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="10">
+    <row r="26" spans="2:2">
+      <c r="B26" s="9">
         <v>2019</v>
       </c>
     </row>
-    <row r="27" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="9" t="s">
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="2:2" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2">
       <c r="B28" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2">
       <c r="B30" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" s="9" t="s">
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" s="10">
+    <row r="32" spans="2:2">
+      <c r="B32" s="9">
         <v>2013</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" s="9" t="s">
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2">
       <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B35" s="9" t="s">
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2">
       <c r="B37" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B38" s="13" t="s">
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B39" s="13" t="s">
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" s="13" t="s">
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B41" s="25" t="s">
+    <row r="41" spans="2:2">
+      <c r="B41" s="19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B42" s="13" t="s">
+    <row r="42" spans="2:2">
+      <c r="B42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2">
       <c r="B44" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B45" s="13" t="s">
+    <row r="45" spans="2:2">
+      <c r="B45" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B46" s="20">
+    <row r="46" spans="2:2">
+      <c r="B46" s="9">
         <v>2009</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B47" s="13" t="s">
+    <row r="47" spans="2:2">
+      <c r="B47" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B48" s="25" t="s">
+    <row r="48" spans="2:2">
+      <c r="B48" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B49" s="13" t="s">
+    <row r="49" spans="1:2">
+      <c r="B49" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>99</v>
       </c>
@@ -2318,2324 +2259,2319 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BC61"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BB61"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="13" customWidth="1"/>
-    <col min="2" max="27" width="7.75" style="13" customWidth="1"/>
-    <col min="28" max="28" width="7.125" style="77" customWidth="1"/>
-    <col min="29" max="55" width="9.125" style="77"/>
-    <col min="56" max="16384" width="9.125" style="13"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="27" width="7.77734375" customWidth="1"/>
+    <col min="28" max="28" width="7.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A1" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="95"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
-      <c r="Z1" s="95"/>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="95"/>
-      <c r="AC1" s="96"/>
-      <c r="AD1" s="96"/>
-      <c r="AE1" s="96"/>
-      <c r="AF1" s="96"/>
-      <c r="AG1" s="96"/>
-      <c r="AH1" s="96"/>
-      <c r="AI1" s="96"/>
-      <c r="AJ1" s="96"/>
-      <c r="AK1" s="96"/>
-      <c r="AL1" s="96"/>
-      <c r="AM1" s="96"/>
-      <c r="AN1" s="96"/>
-      <c r="AO1" s="96"/>
-      <c r="AP1" s="96"/>
-      <c r="AQ1" s="96"/>
-      <c r="AR1" s="96"/>
-      <c r="AS1" s="96"/>
-      <c r="AT1" s="96"/>
-      <c r="AU1" s="96"/>
-      <c r="AV1" s="96"/>
-      <c r="AW1" s="96"/>
-      <c r="AX1" s="96"/>
-      <c r="AY1" s="96"/>
-      <c r="AZ1" s="96"/>
-      <c r="BA1" s="96"/>
-      <c r="BB1" s="96"/>
-    </row>
-    <row r="2" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="79"/>
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
+      <c r="BA1" s="79"/>
+      <c r="BB1" s="79"/>
+    </row>
+    <row r="2" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A2" s="38"/>
+      <c r="B2" s="39">
         <v>1980</v>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="40">
         <v>1985</v>
       </c>
-      <c r="D2" s="48">
+      <c r="D2" s="40">
         <v>1990</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="40">
         <v>1991</v>
       </c>
-      <c r="F2" s="48">
+      <c r="F2" s="40">
         <v>1992</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="40">
         <v>1993</v>
       </c>
-      <c r="H2" s="48">
+      <c r="H2" s="40">
         <v>1994</v>
       </c>
-      <c r="I2" s="48">
+      <c r="I2" s="40">
         <v>1995</v>
       </c>
-      <c r="J2" s="48">
+      <c r="J2" s="40">
         <v>1996</v>
       </c>
-      <c r="K2" s="48">
+      <c r="K2" s="40">
         <v>1997</v>
       </c>
-      <c r="L2" s="48">
+      <c r="L2" s="40">
         <v>1998</v>
       </c>
-      <c r="M2" s="48">
+      <c r="M2" s="40">
         <v>1999</v>
       </c>
-      <c r="N2" s="48">
+      <c r="N2" s="40">
         <v>2000</v>
       </c>
-      <c r="O2" s="48">
+      <c r="O2" s="40">
         <v>2001</v>
       </c>
-      <c r="P2" s="48">
+      <c r="P2" s="40">
         <v>2002</v>
       </c>
-      <c r="Q2" s="48">
+      <c r="Q2" s="40">
         <v>2003</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="40">
         <v>2004</v>
       </c>
-      <c r="S2" s="48">
+      <c r="S2" s="40">
         <v>2005</v>
       </c>
-      <c r="T2" s="48">
+      <c r="T2" s="40">
         <v>2006</v>
       </c>
-      <c r="U2" s="48">
+      <c r="U2" s="40">
         <v>2007</v>
       </c>
-      <c r="V2" s="48">
+      <c r="V2" s="40">
         <v>2008</v>
       </c>
-      <c r="W2" s="48">
+      <c r="W2" s="40">
         <v>2009</v>
       </c>
-      <c r="X2" s="48">
+      <c r="X2" s="40">
         <v>2010</v>
       </c>
-      <c r="Y2" s="48">
+      <c r="Y2" s="40">
         <v>2011</v>
       </c>
-      <c r="Z2" s="49">
+      <c r="Z2" s="41">
         <v>2012</v>
       </c>
-      <c r="AA2" s="48">
+      <c r="AA2" s="40">
         <v>2013</v>
       </c>
-      <c r="AB2" s="50">
+      <c r="AB2" s="42">
         <v>2014</v>
       </c>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="52"/>
-      <c r="AM2" s="52"/>
-      <c r="AN2" s="52"/>
-      <c r="AO2" s="52"/>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="52"/>
-      <c r="AU2" s="53"/>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="53"/>
-      <c r="AY2" s="53"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="54"/>
-    </row>
-    <row r="3" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="55" t="s">
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="44"/>
+      <c r="AS2" s="44"/>
+      <c r="AT2" s="44"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="45"/>
+      <c r="AX2" s="45"/>
+      <c r="AY2" s="45"/>
+      <c r="AZ2" s="45"/>
+      <c r="BA2" s="45"/>
+      <c r="BB2" s="46"/>
+    </row>
+    <row r="3" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="56">
+      <c r="B3" s="48">
         <v>11306</v>
       </c>
-      <c r="C3" s="56">
+      <c r="C3" s="48">
         <v>14460</v>
       </c>
-      <c r="D3" s="56">
+      <c r="D3" s="48">
         <v>12615</v>
       </c>
-      <c r="E3" s="56">
+      <c r="E3" s="48">
         <v>12573</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="48">
         <v>12172</v>
       </c>
-      <c r="G3" s="56">
+      <c r="G3" s="48">
         <v>13211</v>
       </c>
-      <c r="H3" s="56">
+      <c r="H3" s="48">
         <v>14125</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="48">
         <v>15145</v>
       </c>
-      <c r="J3" s="56">
+      <c r="J3" s="48">
         <v>13144</v>
       </c>
-      <c r="K3" s="56">
+      <c r="K3" s="48">
         <v>14458</v>
       </c>
-      <c r="L3" s="56">
+      <c r="L3" s="48">
         <v>14456</v>
       </c>
-      <c r="M3" s="56">
+      <c r="M3" s="48">
         <v>15215</v>
       </c>
-      <c r="N3" s="56">
+      <c r="N3" s="48">
         <v>16571</v>
       </c>
-      <c r="O3" s="56">
+      <c r="O3" s="48">
         <v>15605</v>
       </c>
-      <c r="P3" s="56">
+      <c r="P3" s="48">
         <v>16115</v>
       </c>
-      <c r="Q3" s="56">
+      <c r="Q3" s="48">
         <v>15773</v>
       </c>
-      <c r="R3" s="56">
+      <c r="R3" s="48">
         <v>15709</v>
       </c>
-      <c r="S3" s="56">
+      <c r="S3" s="48">
         <v>15892</v>
       </c>
-      <c r="T3" s="56">
+      <c r="T3" s="48">
         <v>15104</v>
       </c>
-      <c r="U3" s="56">
+      <c r="U3" s="48">
         <v>15276</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="48">
         <v>13898</v>
       </c>
-      <c r="W3" s="56">
+      <c r="W3" s="48">
         <v>9316</v>
       </c>
-      <c r="X3" s="56">
+      <c r="X3" s="48">
         <v>11110</v>
       </c>
-      <c r="Y3" s="56">
+      <c r="Y3" s="48">
         <v>12003</v>
       </c>
-      <c r="Z3" s="56">
+      <c r="Z3" s="48">
         <v>13438</v>
       </c>
-      <c r="AA3" s="56">
+      <c r="AA3" s="48">
         <v>14846</v>
       </c>
-      <c r="AB3" s="57" t="s">
+      <c r="AB3" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="58"/>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="58"/>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="58"/>
-      <c r="AJ3" s="58"/>
-      <c r="AK3" s="58"/>
-      <c r="AL3" s="58"/>
-      <c r="AM3" s="58"/>
-      <c r="AN3" s="58"/>
-      <c r="AO3" s="58"/>
-      <c r="AP3" s="58"/>
-      <c r="AQ3" s="58"/>
-      <c r="AR3" s="58"/>
-      <c r="AS3" s="58"/>
-      <c r="AT3" s="58"/>
-      <c r="AU3" s="58"/>
-      <c r="AV3" s="58"/>
-      <c r="AW3" s="58"/>
-      <c r="AX3" s="58"/>
-      <c r="AY3" s="58"/>
-      <c r="AZ3" s="58"/>
-      <c r="BA3" s="58"/>
-      <c r="BB3" s="58"/>
-    </row>
-    <row r="4" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="48"/>
+      <c r="AL3" s="48"/>
+      <c r="AM3" s="48"/>
+      <c r="AN3" s="48"/>
+      <c r="AO3" s="48"/>
+      <c r="AP3" s="48"/>
+      <c r="AQ3" s="48"/>
+      <c r="AR3" s="48"/>
+      <c r="AS3" s="48"/>
+      <c r="AT3" s="48"/>
+      <c r="AU3" s="48"/>
+      <c r="AV3" s="48"/>
+      <c r="AW3" s="48"/>
+      <c r="AX3" s="48"/>
+      <c r="AY3" s="48"/>
+      <c r="AZ3" s="48"/>
+      <c r="BA3" s="48"/>
+      <c r="BB3" s="48"/>
+    </row>
+    <row r="4" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A4" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="51">
         <v>9443</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="51">
         <v>10791</v>
       </c>
-      <c r="D4" s="60">
+      <c r="D4" s="51">
         <v>8810</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="51">
         <v>8524</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="51">
         <v>8108</v>
       </c>
-      <c r="G4" s="60">
+      <c r="G4" s="51">
         <v>8456</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="51">
         <v>8415</v>
       </c>
-      <c r="I4" s="60">
+      <c r="I4" s="51">
         <v>9396</v>
       </c>
-      <c r="J4" s="60">
+      <c r="J4" s="51">
         <v>7890</v>
       </c>
-      <c r="K4" s="60">
+      <c r="K4" s="51">
         <v>8334</v>
       </c>
-      <c r="L4" s="60">
+      <c r="L4" s="51">
         <v>7971</v>
       </c>
-      <c r="M4" s="60">
+      <c r="M4" s="51">
         <v>8376</v>
       </c>
-      <c r="N4" s="60">
+      <c r="N4" s="51">
         <v>9125</v>
       </c>
-      <c r="O4" s="60">
+      <c r="O4" s="51">
         <v>8405</v>
       </c>
-      <c r="P4" s="60">
+      <c r="P4" s="51">
         <v>8301</v>
       </c>
-      <c r="Q4" s="60">
+      <c r="Q4" s="51">
         <v>7921</v>
       </c>
-      <c r="R4" s="60">
+      <c r="R4" s="51">
         <v>7537</v>
       </c>
-      <c r="S4" s="60">
+      <c r="S4" s="51">
         <v>8027</v>
       </c>
-      <c r="T4" s="60">
+      <c r="T4" s="51">
         <v>7993</v>
       </c>
-      <c r="U4" s="60">
+      <c r="U4" s="51">
         <v>8082</v>
       </c>
-      <c r="V4" s="60">
+      <c r="V4" s="51">
         <v>7319</v>
       </c>
-      <c r="W4" s="60">
+      <c r="W4" s="51">
         <v>5636</v>
       </c>
-      <c r="X4" s="60">
+      <c r="X4" s="51">
         <v>6055</v>
       </c>
-      <c r="Y4" s="61">
+      <c r="Y4" s="52">
         <v>5728</v>
       </c>
-      <c r="Z4" s="61">
+      <c r="Z4" s="52">
         <v>7379</v>
       </c>
-      <c r="AA4" s="61">
+      <c r="AA4" s="52">
         <v>7907</v>
       </c>
-      <c r="AB4" s="60" t="s">
+      <c r="AB4" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="AC4" s="59"/>
-      <c r="AD4" s="62"/>
-      <c r="AE4" s="62"/>
-      <c r="AF4" s="62"/>
-      <c r="AG4" s="62"/>
-      <c r="AH4" s="62"/>
-      <c r="AI4" s="62"/>
-      <c r="AJ4" s="62"/>
-      <c r="AK4" s="62"/>
-      <c r="AL4" s="62"/>
-      <c r="AM4" s="62"/>
-      <c r="AN4" s="62"/>
-      <c r="AO4" s="62"/>
-      <c r="AP4" s="62"/>
-      <c r="AQ4" s="62"/>
-      <c r="AR4" s="62"/>
-      <c r="AS4" s="62"/>
-      <c r="AT4" s="62"/>
-      <c r="AU4" s="62"/>
-      <c r="AV4" s="62"/>
-      <c r="AW4" s="62"/>
-      <c r="AX4" s="62"/>
-      <c r="AY4" s="62"/>
-      <c r="AZ4" s="62"/>
-      <c r="BA4" s="63"/>
-      <c r="BB4" s="63"/>
-    </row>
-    <row r="5" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="51"/>
+      <c r="AE4" s="51"/>
+      <c r="AF4" s="51"/>
+      <c r="AG4" s="51"/>
+      <c r="AH4" s="51"/>
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="51"/>
+      <c r="AK4" s="51"/>
+      <c r="AL4" s="51"/>
+      <c r="AM4" s="51"/>
+      <c r="AN4" s="51"/>
+      <c r="AO4" s="51"/>
+      <c r="AP4" s="51"/>
+      <c r="AQ4" s="51"/>
+      <c r="AR4" s="51"/>
+      <c r="AS4" s="51"/>
+      <c r="AT4" s="51"/>
+      <c r="AU4" s="51"/>
+      <c r="AV4" s="51"/>
+      <c r="AW4" s="51"/>
+      <c r="AX4" s="51"/>
+      <c r="AY4" s="51"/>
+      <c r="AZ4" s="51"/>
+      <c r="BA4" s="52"/>
+      <c r="BB4" s="52"/>
+    </row>
+    <row r="5" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A5" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="51">
         <v>0</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="51">
         <v>88</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="51">
         <v>65</v>
       </c>
-      <c r="E5" s="60">
+      <c r="E5" s="51">
         <v>224</v>
       </c>
-      <c r="F5" s="60">
+      <c r="F5" s="51">
         <v>243</v>
       </c>
-      <c r="G5" s="60">
+      <c r="G5" s="51">
         <v>473</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="51">
         <v>332</v>
       </c>
-      <c r="I5" s="60">
+      <c r="I5" s="51">
         <v>220</v>
       </c>
-      <c r="J5" s="60">
+      <c r="J5" s="51">
         <v>287</v>
       </c>
-      <c r="K5" s="60">
+      <c r="K5" s="51">
         <v>361</v>
       </c>
-      <c r="L5" s="60">
+      <c r="L5" s="51">
         <v>454</v>
       </c>
-      <c r="M5" s="60">
+      <c r="M5" s="51">
         <v>488</v>
       </c>
-      <c r="N5" s="60">
+      <c r="N5" s="51">
         <v>617</v>
       </c>
-      <c r="O5" s="60">
+      <c r="O5" s="51">
         <v>743</v>
       </c>
-      <c r="P5" s="60">
+      <c r="P5" s="51">
         <v>603</v>
       </c>
-      <c r="Q5" s="60">
+      <c r="Q5" s="51">
         <v>575</v>
       </c>
-      <c r="R5" s="60">
+      <c r="R5" s="51">
         <v>639</v>
       </c>
-      <c r="S5" s="60">
+      <c r="S5" s="51">
         <v>813</v>
       </c>
-      <c r="T5" s="60">
+      <c r="T5" s="51">
         <v>751</v>
       </c>
-      <c r="U5" s="60">
+      <c r="U5" s="51">
         <v>919</v>
       </c>
-      <c r="V5" s="60">
+      <c r="V5" s="51">
         <v>924</v>
       </c>
-      <c r="W5" s="60">
+      <c r="W5" s="51">
         <v>608</v>
       </c>
-      <c r="X5" s="60">
+      <c r="X5" s="51">
         <v>915</v>
       </c>
-      <c r="Y5" s="61">
+      <c r="Y5" s="52">
         <v>1207</v>
       </c>
-      <c r="Z5" s="61">
+      <c r="Z5" s="52">
         <v>1269</v>
       </c>
-      <c r="AA5" s="61">
+      <c r="AA5" s="52">
         <v>1470</v>
       </c>
-      <c r="AB5" s="60" t="s">
+      <c r="AB5" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="AC5" s="59"/>
-      <c r="AD5" s="62"/>
-      <c r="AE5" s="62"/>
-      <c r="AF5" s="62"/>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="62"/>
-      <c r="AI5" s="62"/>
-      <c r="AJ5" s="62"/>
-      <c r="AK5" s="62"/>
-      <c r="AL5" s="62"/>
-      <c r="AM5" s="62"/>
-      <c r="AN5" s="62"/>
-      <c r="AO5" s="62"/>
-      <c r="AP5" s="62"/>
-      <c r="AQ5" s="62"/>
-      <c r="AR5" s="62"/>
-      <c r="AS5" s="62"/>
-      <c r="AT5" s="62"/>
-      <c r="AU5" s="62"/>
-      <c r="AV5" s="62"/>
-      <c r="AW5" s="62"/>
-      <c r="AX5" s="62"/>
-      <c r="AY5" s="62"/>
-      <c r="AZ5" s="62"/>
-      <c r="BA5" s="63"/>
-      <c r="BB5" s="63"/>
-    </row>
-    <row r="6" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="59" t="s">
+      <c r="AC5" s="50"/>
+      <c r="AD5" s="51"/>
+      <c r="AE5" s="51"/>
+      <c r="AF5" s="51"/>
+      <c r="AG5" s="51"/>
+      <c r="AH5" s="51"/>
+      <c r="AI5" s="51"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="51"/>
+      <c r="AL5" s="51"/>
+      <c r="AM5" s="51"/>
+      <c r="AN5" s="51"/>
+      <c r="AO5" s="51"/>
+      <c r="AP5" s="51"/>
+      <c r="AQ5" s="51"/>
+      <c r="AR5" s="51"/>
+      <c r="AS5" s="51"/>
+      <c r="AT5" s="51"/>
+      <c r="AU5" s="51"/>
+      <c r="AV5" s="51"/>
+      <c r="AW5" s="51"/>
+      <c r="AX5" s="51"/>
+      <c r="AY5" s="51"/>
+      <c r="AZ5" s="51"/>
+      <c r="BA5" s="52"/>
+      <c r="BB5" s="52"/>
+    </row>
+    <row r="6" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A6" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="51">
         <v>1437</v>
       </c>
-      <c r="C6" s="60">
+      <c r="C6" s="51">
         <v>2078</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="51">
         <v>1835</v>
       </c>
-      <c r="E6" s="60">
+      <c r="E6" s="51">
         <v>1920</v>
       </c>
-      <c r="F6" s="60">
+      <c r="F6" s="51">
         <v>1840</v>
       </c>
-      <c r="G6" s="60">
+      <c r="G6" s="51">
         <v>2002</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="51">
         <v>2669</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="51">
         <v>2271</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="51">
         <v>1955</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="51">
         <v>2408</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="51">
         <v>2415</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="51">
         <v>2544</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="51">
         <v>2612</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="51">
         <v>2519</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="51">
         <v>2380</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="51">
         <v>2474</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="51">
         <v>2505</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="51">
         <v>2300</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="51">
         <v>2188</v>
       </c>
-      <c r="U6" s="60">
+      <c r="U6" s="51">
         <v>2113</v>
       </c>
-      <c r="V6" s="60">
+      <c r="V6" s="51">
         <v>1794</v>
       </c>
-      <c r="W6" s="60">
+      <c r="W6" s="51">
         <v>989</v>
       </c>
-      <c r="X6" s="60">
+      <c r="X6" s="51">
         <v>1276</v>
       </c>
-      <c r="Y6" s="61">
+      <c r="Y6" s="52">
         <v>1479</v>
       </c>
-      <c r="Z6" s="61">
+      <c r="Z6" s="52">
         <v>1357</v>
       </c>
-      <c r="AA6" s="61">
+      <c r="AA6" s="52">
         <v>1577</v>
       </c>
-      <c r="AB6" s="60" t="s">
+      <c r="AB6" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="62"/>
-      <c r="AE6" s="62"/>
-      <c r="AF6" s="62"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
-      <c r="AL6" s="62"/>
-      <c r="AM6" s="62"/>
-      <c r="AN6" s="62"/>
-      <c r="AO6" s="62"/>
-      <c r="AP6" s="62"/>
-      <c r="AQ6" s="62"/>
-      <c r="AR6" s="62"/>
-      <c r="AS6" s="62"/>
-      <c r="AT6" s="62"/>
-      <c r="AU6" s="62"/>
-      <c r="AV6" s="62"/>
-      <c r="AW6" s="62"/>
-      <c r="AX6" s="62"/>
-      <c r="AY6" s="62"/>
-      <c r="AZ6" s="62"/>
-      <c r="BA6" s="63"/>
-      <c r="BB6" s="63"/>
-    </row>
-    <row r="7" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="59" t="s">
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="51"/>
+      <c r="AE6" s="51"/>
+      <c r="AF6" s="51"/>
+      <c r="AG6" s="51"/>
+      <c r="AH6" s="51"/>
+      <c r="AI6" s="51"/>
+      <c r="AJ6" s="51"/>
+      <c r="AK6" s="51"/>
+      <c r="AL6" s="51"/>
+      <c r="AM6" s="51"/>
+      <c r="AN6" s="51"/>
+      <c r="AO6" s="51"/>
+      <c r="AP6" s="51"/>
+      <c r="AQ6" s="51"/>
+      <c r="AR6" s="51"/>
+      <c r="AS6" s="51"/>
+      <c r="AT6" s="51"/>
+      <c r="AU6" s="51"/>
+      <c r="AV6" s="51"/>
+      <c r="AW6" s="51"/>
+      <c r="AX6" s="51"/>
+      <c r="AY6" s="51"/>
+      <c r="AZ6" s="51"/>
+      <c r="BA6" s="52"/>
+      <c r="BB6" s="52"/>
+    </row>
+    <row r="7" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A7" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="51">
         <v>242</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="51">
         <v>855</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="51">
         <v>1262</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="51">
         <v>1034</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="51">
         <v>1221</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="51">
         <v>1441</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="51">
         <v>1418</v>
       </c>
-      <c r="I7" s="60">
+      <c r="I7" s="51">
         <v>1662</v>
       </c>
-      <c r="J7" s="60">
+      <c r="J7" s="51">
         <v>1409</v>
       </c>
-      <c r="K7" s="60">
+      <c r="K7" s="51">
         <v>1265</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="51">
         <v>1489</v>
       </c>
-      <c r="M7" s="60">
+      <c r="M7" s="51">
         <v>1463</v>
       </c>
-      <c r="N7" s="60">
+      <c r="N7" s="51">
         <v>1691</v>
       </c>
-      <c r="O7" s="60">
+      <c r="O7" s="51">
         <v>1232</v>
       </c>
-      <c r="P7" s="60">
+      <c r="P7" s="51">
         <v>1243</v>
       </c>
-      <c r="Q7" s="60">
+      <c r="Q7" s="51">
         <v>1232</v>
       </c>
-      <c r="R7" s="60">
+      <c r="R7" s="51">
         <v>953</v>
       </c>
-      <c r="S7" s="60">
+      <c r="S7" s="51">
         <v>1481</v>
       </c>
-      <c r="T7" s="60">
+      <c r="T7" s="51">
         <v>1166</v>
       </c>
-      <c r="U7" s="60">
+      <c r="U7" s="51">
         <v>847</v>
       </c>
-      <c r="V7" s="60">
+      <c r="V7" s="51">
         <v>790</v>
       </c>
-      <c r="W7" s="60">
+      <c r="W7" s="51">
         <v>368</v>
       </c>
-      <c r="X7" s="60">
+      <c r="X7" s="51">
         <v>559</v>
       </c>
-      <c r="Y7" s="61">
+      <c r="Y7" s="52">
         <v>521</v>
       </c>
-      <c r="Z7" s="61">
+      <c r="Z7" s="52">
         <v>661</v>
       </c>
-      <c r="AA7" s="61">
+      <c r="AA7" s="52">
         <v>571</v>
       </c>
-      <c r="AB7" s="60" t="s">
+      <c r="AB7" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="AC7" s="59"/>
-      <c r="AD7" s="62"/>
-      <c r="AE7" s="62"/>
-      <c r="AF7" s="62"/>
-      <c r="AG7" s="62"/>
-      <c r="AH7" s="62"/>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="62"/>
-      <c r="AL7" s="62"/>
-      <c r="AM7" s="62"/>
-      <c r="AN7" s="62"/>
-      <c r="AO7" s="62"/>
-      <c r="AP7" s="62"/>
-      <c r="AQ7" s="62"/>
-      <c r="AR7" s="62"/>
-      <c r="AS7" s="62"/>
-      <c r="AT7" s="62"/>
-      <c r="AU7" s="62"/>
-      <c r="AV7" s="62"/>
-      <c r="AW7" s="62"/>
-      <c r="AX7" s="62"/>
-      <c r="AY7" s="62"/>
-      <c r="AZ7" s="62"/>
-      <c r="BA7" s="63"/>
-      <c r="BB7" s="63"/>
-    </row>
-    <row r="8" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="59" t="s">
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="51"/>
+      <c r="AE7" s="51"/>
+      <c r="AF7" s="51"/>
+      <c r="AG7" s="51"/>
+      <c r="AH7" s="51"/>
+      <c r="AI7" s="51"/>
+      <c r="AJ7" s="51"/>
+      <c r="AK7" s="51"/>
+      <c r="AL7" s="51"/>
+      <c r="AM7" s="51"/>
+      <c r="AN7" s="51"/>
+      <c r="AO7" s="51"/>
+      <c r="AP7" s="51"/>
+      <c r="AQ7" s="51"/>
+      <c r="AR7" s="51"/>
+      <c r="AS7" s="51"/>
+      <c r="AT7" s="51"/>
+      <c r="AU7" s="51"/>
+      <c r="AV7" s="51"/>
+      <c r="AW7" s="51"/>
+      <c r="AX7" s="51"/>
+      <c r="AY7" s="51"/>
+      <c r="AZ7" s="51"/>
+      <c r="BA7" s="52"/>
+      <c r="BB7" s="52"/>
+    </row>
+    <row r="8" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A8" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="51">
         <v>184</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="51">
         <v>648</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="51">
         <v>643</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="51">
         <v>871</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="51">
         <v>761</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="51">
         <v>838</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="51">
         <v>1291</v>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="51">
         <v>1596</v>
       </c>
-      <c r="J8" s="60">
+      <c r="J8" s="51">
         <v>1603</v>
       </c>
-      <c r="K8" s="60">
+      <c r="K8" s="51">
         <v>2089</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="51">
         <v>2127</v>
       </c>
-      <c r="M8" s="60">
+      <c r="M8" s="51">
         <v>2342</v>
       </c>
-      <c r="N8" s="60">
+      <c r="N8" s="51">
         <v>2526</v>
       </c>
-      <c r="O8" s="60">
+      <c r="O8" s="51">
         <v>2707</v>
       </c>
-      <c r="P8" s="60">
+      <c r="P8" s="51">
         <v>3588</v>
       </c>
-      <c r="Q8" s="60">
+      <c r="Q8" s="51">
         <v>3571</v>
       </c>
-      <c r="R8" s="60">
+      <c r="R8" s="51">
         <v>4075</v>
       </c>
-      <c r="S8" s="60">
+      <c r="S8" s="51">
         <v>3272</v>
       </c>
-      <c r="T8" s="60">
+      <c r="T8" s="51">
         <v>3006</v>
       </c>
-      <c r="U8" s="60">
+      <c r="U8" s="51">
         <v>3314</v>
       </c>
-      <c r="V8" s="60">
+      <c r="V8" s="51">
         <v>3072</v>
       </c>
-      <c r="W8" s="60">
+      <c r="W8" s="51">
         <v>1713</v>
       </c>
-      <c r="X8" s="60">
+      <c r="X8" s="51">
         <v>2305</v>
       </c>
-      <c r="Y8" s="61">
+      <c r="Y8" s="52">
         <v>3069</v>
       </c>
-      <c r="Z8" s="61">
+      <c r="Z8" s="52">
         <v>2773</v>
       </c>
-      <c r="AA8" s="61">
+      <c r="AA8" s="52">
         <v>3321</v>
       </c>
-      <c r="AB8" s="60" t="s">
+      <c r="AB8" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="AC8" s="59"/>
-      <c r="AD8" s="62"/>
-      <c r="AE8" s="62"/>
-      <c r="AF8" s="62"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="62"/>
-      <c r="AL8" s="62"/>
-      <c r="AM8" s="62"/>
-      <c r="AN8" s="62"/>
-      <c r="AO8" s="62"/>
-      <c r="AP8" s="62"/>
-      <c r="AQ8" s="62"/>
-      <c r="AR8" s="62"/>
-      <c r="AS8" s="62"/>
-      <c r="AT8" s="62"/>
-      <c r="AU8" s="62"/>
-      <c r="AV8" s="62"/>
-      <c r="AW8" s="62"/>
-      <c r="AX8" s="62"/>
-      <c r="AY8" s="62"/>
-      <c r="AZ8" s="62"/>
-      <c r="BA8" s="63"/>
-      <c r="BB8" s="63"/>
-    </row>
-    <row r="9" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="s">
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="51"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="51"/>
+      <c r="AG8" s="51"/>
+      <c r="AH8" s="51"/>
+      <c r="AI8" s="51"/>
+      <c r="AJ8" s="51"/>
+      <c r="AK8" s="51"/>
+      <c r="AL8" s="51"/>
+      <c r="AM8" s="51"/>
+      <c r="AN8" s="51"/>
+      <c r="AO8" s="51"/>
+      <c r="AP8" s="51"/>
+      <c r="AQ8" s="51"/>
+      <c r="AR8" s="51"/>
+      <c r="AS8" s="51"/>
+      <c r="AT8" s="51"/>
+      <c r="AU8" s="51"/>
+      <c r="AV8" s="51"/>
+      <c r="AW8" s="51"/>
+      <c r="AX8" s="51"/>
+      <c r="AY8" s="51"/>
+      <c r="AZ8" s="51"/>
+      <c r="BA8" s="52"/>
+      <c r="BB8" s="52"/>
+    </row>
+    <row r="9" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A9" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="65"/>
-      <c r="P9" s="65"/>
-      <c r="Q9" s="65"/>
-      <c r="R9" s="65"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="65"/>
-      <c r="U9" s="65"/>
-      <c r="V9" s="65"/>
-      <c r="W9" s="65"/>
-      <c r="X9" s="65"/>
-      <c r="Y9" s="65"/>
-      <c r="Z9" s="65"/>
-      <c r="AA9" s="65"/>
-      <c r="AB9" s="65"/>
-      <c r="AC9" s="64"/>
-      <c r="AD9" s="66"/>
-      <c r="AE9" s="66"/>
-      <c r="AF9" s="66"/>
-      <c r="AG9" s="66"/>
-      <c r="AH9" s="66"/>
-      <c r="AI9" s="66"/>
-      <c r="AJ9" s="66"/>
-      <c r="AK9" s="66"/>
-      <c r="AL9" s="66"/>
-      <c r="AM9" s="66"/>
-      <c r="AN9" s="66"/>
-      <c r="AO9" s="66"/>
-      <c r="AP9" s="66"/>
-      <c r="AQ9" s="66"/>
-      <c r="AR9" s="66"/>
-      <c r="AS9" s="66"/>
-      <c r="AT9" s="66"/>
-      <c r="AU9" s="66"/>
-      <c r="AV9" s="66"/>
-      <c r="AW9" s="66"/>
-      <c r="AX9" s="66"/>
-      <c r="AY9" s="66"/>
-      <c r="AZ9" s="66"/>
-      <c r="BA9" s="66"/>
-      <c r="BB9" s="66"/>
-    </row>
-    <row r="10" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="59" t="s">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="53"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="54"/>
+      <c r="AH9" s="54"/>
+      <c r="AI9" s="54"/>
+      <c r="AJ9" s="54"/>
+      <c r="AK9" s="54"/>
+      <c r="AL9" s="54"/>
+      <c r="AM9" s="54"/>
+      <c r="AN9" s="54"/>
+      <c r="AO9" s="54"/>
+      <c r="AP9" s="54"/>
+      <c r="AQ9" s="54"/>
+      <c r="AR9" s="54"/>
+      <c r="AS9" s="54"/>
+      <c r="AT9" s="54"/>
+      <c r="AU9" s="54"/>
+      <c r="AV9" s="54"/>
+      <c r="AW9" s="54"/>
+      <c r="AX9" s="54"/>
+      <c r="AY9" s="54"/>
+      <c r="AZ9" s="54"/>
+      <c r="BA9" s="54"/>
+      <c r="BB9" s="54"/>
+    </row>
+    <row r="10" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A10" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="67">
+      <c r="B10" s="55">
         <f>B4/B$3*100</f>
         <v>83.522023704227848</v>
       </c>
-      <c r="C10" s="67">
+      <c r="C10" s="55">
         <f>C4/C$3*100</f>
         <v>74.626556016597505</v>
       </c>
-      <c r="D10" s="67">
+      <c r="D10" s="55">
         <v>69.8</v>
       </c>
-      <c r="E10" s="67">
+      <c r="E10" s="55">
         <v>67.800000000000011</v>
       </c>
-      <c r="F10" s="67">
+      <c r="F10" s="55">
         <v>66.600000000000009</v>
       </c>
-      <c r="G10" s="67">
+      <c r="G10" s="55">
         <v>64</v>
       </c>
-      <c r="H10" s="67">
+      <c r="H10" s="55">
         <v>59.599999999999994</v>
       </c>
-      <c r="I10" s="67">
+      <c r="I10" s="55">
         <v>62</v>
       </c>
-      <c r="J10" s="67">
+      <c r="J10" s="55">
         <v>60</v>
       </c>
-      <c r="K10" s="67">
+      <c r="K10" s="55">
         <v>57.599999999999994</v>
       </c>
-      <c r="L10" s="67">
+      <c r="L10" s="55">
         <v>55.1</v>
       </c>
-      <c r="M10" s="67">
+      <c r="M10" s="55">
         <v>55.1</v>
       </c>
-      <c r="N10" s="67">
+      <c r="N10" s="55">
         <v>55.1</v>
       </c>
-      <c r="O10" s="67">
+      <c r="O10" s="55">
         <v>53.900000000000006</v>
       </c>
-      <c r="P10" s="67">
+      <c r="P10" s="55">
         <v>51.5</v>
       </c>
-      <c r="Q10" s="67">
+      <c r="Q10" s="55">
         <v>50.2</v>
       </c>
-      <c r="R10" s="67">
+      <c r="R10" s="55">
         <v>48</v>
       </c>
-      <c r="S10" s="67">
+      <c r="S10" s="55">
         <v>50.5</v>
       </c>
-      <c r="T10" s="67">
+      <c r="T10" s="55">
         <v>52.900000000000006</v>
       </c>
-      <c r="U10" s="67">
+      <c r="U10" s="55">
         <v>52.900000000000006</v>
       </c>
-      <c r="V10" s="67">
+      <c r="V10" s="55">
         <v>52.7</v>
       </c>
-      <c r="W10" s="67">
+      <c r="W10" s="55">
         <v>60.5</v>
       </c>
-      <c r="X10" s="67">
+      <c r="X10" s="55">
         <v>54.500000000000007</v>
       </c>
-      <c r="Y10" s="67">
+      <c r="Y10" s="55">
         <v>47.699999999999996</v>
       </c>
-      <c r="Z10" s="67">
+      <c r="Z10" s="55">
         <v>54.900000000000006</v>
       </c>
-      <c r="AA10" s="67">
+      <c r="AA10" s="55">
         <v>53.300000000000004</v>
       </c>
-      <c r="AB10" s="67">
+      <c r="AB10" s="55">
         <v>51.300000000000004</v>
       </c>
-      <c r="AC10" s="59"/>
-      <c r="AD10" s="68"/>
-      <c r="AE10" s="68"/>
-      <c r="AF10" s="68"/>
-      <c r="AG10" s="68"/>
-      <c r="AH10" s="68"/>
-      <c r="AI10" s="68"/>
-      <c r="AJ10" s="68"/>
-      <c r="AK10" s="68"/>
-      <c r="AL10" s="68"/>
-      <c r="AM10" s="68"/>
-      <c r="AN10" s="68"/>
-      <c r="AO10" s="68"/>
-      <c r="AP10" s="68"/>
-      <c r="AQ10" s="68"/>
-      <c r="AR10" s="68"/>
-      <c r="AS10" s="68"/>
-      <c r="AT10" s="68"/>
-      <c r="AU10" s="68"/>
-      <c r="AV10" s="68"/>
-      <c r="AW10" s="68"/>
-      <c r="AX10" s="68"/>
-      <c r="AY10" s="68"/>
-      <c r="AZ10" s="68"/>
-      <c r="BA10" s="68"/>
-      <c r="BB10" s="68"/>
-    </row>
-    <row r="11" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="59" t="s">
+      <c r="AC10" s="50"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="56"/>
+      <c r="AH10" s="56"/>
+      <c r="AI10" s="56"/>
+      <c r="AJ10" s="56"/>
+      <c r="AK10" s="56"/>
+      <c r="AL10" s="56"/>
+      <c r="AM10" s="56"/>
+      <c r="AN10" s="56"/>
+      <c r="AO10" s="56"/>
+      <c r="AP10" s="56"/>
+      <c r="AQ10" s="56"/>
+      <c r="AR10" s="56"/>
+      <c r="AS10" s="56"/>
+      <c r="AT10" s="56"/>
+      <c r="AU10" s="56"/>
+      <c r="AV10" s="56"/>
+      <c r="AW10" s="56"/>
+      <c r="AX10" s="56"/>
+      <c r="AY10" s="56"/>
+      <c r="AZ10" s="56"/>
+      <c r="BA10" s="56"/>
+      <c r="BB10" s="56"/>
+    </row>
+    <row r="11" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A11" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="67">
+      <c r="B11" s="55">
         <v>0</v>
       </c>
-      <c r="C11" s="67">
+      <c r="C11" s="55">
         <v>0.6</v>
       </c>
-      <c r="D11" s="67">
+      <c r="D11" s="55">
         <v>0.5</v>
       </c>
-      <c r="E11" s="67">
+      <c r="E11" s="55">
         <v>1.7999999999999998</v>
       </c>
-      <c r="F11" s="67">
+      <c r="F11" s="55">
         <v>2</v>
       </c>
-      <c r="G11" s="67">
+      <c r="G11" s="55">
         <v>3.5999999999999996</v>
       </c>
-      <c r="H11" s="67">
+      <c r="H11" s="55">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I11" s="67">
+      <c r="I11" s="55">
         <v>1.5</v>
       </c>
-      <c r="J11" s="67">
+      <c r="J11" s="55">
         <v>2.1999999999999997</v>
       </c>
-      <c r="K11" s="67">
+      <c r="K11" s="55">
         <v>2.5</v>
       </c>
-      <c r="L11" s="67">
+      <c r="L11" s="55">
         <v>3.1</v>
       </c>
-      <c r="M11" s="67">
+      <c r="M11" s="55">
         <v>3.2</v>
       </c>
-      <c r="N11" s="67">
+      <c r="N11" s="55">
         <v>3.6999999999999997</v>
       </c>
-      <c r="O11" s="67">
+      <c r="O11" s="55">
         <v>4.8</v>
       </c>
-      <c r="P11" s="67">
+      <c r="P11" s="55">
         <v>3.6999999999999997</v>
       </c>
-      <c r="Q11" s="67">
+      <c r="Q11" s="55">
         <v>3.5999999999999996</v>
       </c>
-      <c r="R11" s="67">
+      <c r="R11" s="55">
         <v>4.1000000000000005</v>
       </c>
-      <c r="S11" s="67">
+      <c r="S11" s="55">
         <v>5.0999999999999996</v>
       </c>
-      <c r="T11" s="67">
+      <c r="T11" s="55">
         <v>5</v>
       </c>
-      <c r="U11" s="67">
+      <c r="U11" s="55">
         <v>6</v>
       </c>
-      <c r="V11" s="67">
+      <c r="V11" s="55">
         <v>6.6000000000000005</v>
       </c>
-      <c r="W11" s="67">
+      <c r="W11" s="55">
         <v>6.5</v>
       </c>
-      <c r="X11" s="67">
+      <c r="X11" s="55">
         <v>8.2000000000000011</v>
       </c>
-      <c r="Y11" s="67">
+      <c r="Y11" s="55">
         <v>10.100000000000001</v>
       </c>
-      <c r="Z11" s="67">
+      <c r="Z11" s="55">
         <v>9.4</v>
       </c>
-      <c r="AA11" s="67">
+      <c r="AA11" s="55">
         <v>9.9</v>
       </c>
-      <c r="AB11" s="67">
+      <c r="AB11" s="55">
         <v>10</v>
       </c>
-      <c r="AC11" s="59"/>
-      <c r="AD11" s="68"/>
-      <c r="AE11" s="68"/>
-      <c r="AF11" s="68"/>
-      <c r="AG11" s="68"/>
-      <c r="AH11" s="68"/>
-      <c r="AI11" s="68"/>
-      <c r="AJ11" s="68"/>
-      <c r="AK11" s="68"/>
-      <c r="AL11" s="68"/>
-      <c r="AM11" s="68"/>
-      <c r="AN11" s="68"/>
-      <c r="AO11" s="68"/>
-      <c r="AP11" s="68"/>
-      <c r="AQ11" s="68"/>
-      <c r="AR11" s="68"/>
-      <c r="AS11" s="68"/>
-      <c r="AT11" s="68"/>
-      <c r="AU11" s="68"/>
-      <c r="AV11" s="68"/>
-      <c r="AW11" s="68"/>
-      <c r="AX11" s="68"/>
-      <c r="AY11" s="68"/>
-      <c r="AZ11" s="68"/>
-      <c r="BA11" s="68"/>
-      <c r="BB11" s="68"/>
-    </row>
-    <row r="12" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="59" t="s">
+      <c r="AC11" s="50"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="56"/>
+      <c r="AH11" s="56"/>
+      <c r="AI11" s="56"/>
+      <c r="AJ11" s="56"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="56"/>
+      <c r="AN11" s="56"/>
+      <c r="AO11" s="56"/>
+      <c r="AP11" s="56"/>
+      <c r="AQ11" s="56"/>
+      <c r="AR11" s="56"/>
+      <c r="AS11" s="56"/>
+      <c r="AT11" s="56"/>
+      <c r="AU11" s="56"/>
+      <c r="AV11" s="56"/>
+      <c r="AW11" s="56"/>
+      <c r="AX11" s="56"/>
+      <c r="AY11" s="56"/>
+      <c r="AZ11" s="56"/>
+      <c r="BA11" s="56"/>
+      <c r="BB11" s="56"/>
+    </row>
+    <row r="12" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A12" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="69">
+      <c r="B12" s="57">
         <v>12.7</v>
       </c>
-      <c r="C12" s="67">
+      <c r="C12" s="55">
         <v>14.399999999999999</v>
       </c>
-      <c r="D12" s="67">
+      <c r="D12" s="55">
         <v>14.499999999999998</v>
       </c>
-      <c r="E12" s="67">
+      <c r="E12" s="55">
         <v>15.299999999999999</v>
       </c>
-      <c r="F12" s="67">
+      <c r="F12" s="55">
         <v>15.1</v>
       </c>
-      <c r="G12" s="67">
+      <c r="G12" s="55">
         <v>15.2</v>
       </c>
-      <c r="H12" s="67">
+      <c r="H12" s="55">
         <v>18.899999999999999</v>
       </c>
-      <c r="I12" s="67">
+      <c r="I12" s="55">
         <v>15</v>
       </c>
-      <c r="J12" s="67">
+      <c r="J12" s="55">
         <v>14.899999999999999</v>
       </c>
-      <c r="K12" s="67">
+      <c r="K12" s="55">
         <v>16.7</v>
       </c>
-      <c r="L12" s="67">
+      <c r="L12" s="55">
         <v>16.7</v>
       </c>
-      <c r="M12" s="67">
+      <c r="M12" s="55">
         <v>16.7</v>
       </c>
-      <c r="N12" s="67">
+      <c r="N12" s="55">
         <v>15.8</v>
       </c>
-      <c r="O12" s="67">
+      <c r="O12" s="55">
         <v>16.100000000000001</v>
       </c>
-      <c r="P12" s="67">
+      <c r="P12" s="55">
         <v>14.799999999999999</v>
       </c>
-      <c r="Q12" s="67">
+      <c r="Q12" s="55">
         <v>15.7</v>
       </c>
-      <c r="R12" s="67">
+      <c r="R12" s="55">
         <v>15.9</v>
       </c>
-      <c r="S12" s="67">
+      <c r="S12" s="55">
         <v>14.499999999999998</v>
       </c>
-      <c r="T12" s="67">
+      <c r="T12" s="55">
         <v>14.499999999999998</v>
       </c>
-      <c r="U12" s="67">
+      <c r="U12" s="55">
         <v>13.8</v>
       </c>
-      <c r="V12" s="67">
+      <c r="V12" s="55">
         <v>12.9</v>
       </c>
-      <c r="W12" s="67">
+      <c r="W12" s="55">
         <v>10.6</v>
       </c>
-      <c r="X12" s="67">
+      <c r="X12" s="55">
         <v>11.5</v>
       </c>
-      <c r="Y12" s="67">
+      <c r="Y12" s="55">
         <v>12.3</v>
       </c>
-      <c r="Z12" s="67">
+      <c r="Z12" s="55">
         <v>10.100000000000001</v>
       </c>
-      <c r="AA12" s="67">
+      <c r="AA12" s="55">
         <v>10.6</v>
       </c>
-      <c r="AB12" s="67">
+      <c r="AB12" s="55">
         <v>11.5</v>
       </c>
-      <c r="AC12" s="59"/>
-      <c r="AD12" s="68"/>
-      <c r="AE12" s="68"/>
-      <c r="AF12" s="68"/>
-      <c r="AG12" s="68"/>
-      <c r="AH12" s="68"/>
-      <c r="AI12" s="68"/>
-      <c r="AJ12" s="68"/>
-      <c r="AK12" s="68"/>
-      <c r="AL12" s="68"/>
-      <c r="AM12" s="68"/>
-      <c r="AN12" s="68"/>
-      <c r="AO12" s="68"/>
-      <c r="AP12" s="68"/>
-      <c r="AQ12" s="68"/>
-      <c r="AR12" s="68"/>
-      <c r="AS12" s="68"/>
-      <c r="AT12" s="68"/>
-      <c r="AU12" s="68"/>
-      <c r="AV12" s="68"/>
-      <c r="AW12" s="68"/>
-      <c r="AX12" s="68"/>
-      <c r="AY12" s="68"/>
-      <c r="AZ12" s="68"/>
-      <c r="BA12" s="68"/>
-      <c r="BB12" s="68"/>
-    </row>
-    <row r="13" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
+      <c r="AJ12" s="56"/>
+      <c r="AK12" s="56"/>
+      <c r="AL12" s="56"/>
+      <c r="AM12" s="56"/>
+      <c r="AN12" s="56"/>
+      <c r="AO12" s="56"/>
+      <c r="AP12" s="56"/>
+      <c r="AQ12" s="56"/>
+      <c r="AR12" s="56"/>
+      <c r="AS12" s="56"/>
+      <c r="AT12" s="56"/>
+      <c r="AU12" s="56"/>
+      <c r="AV12" s="56"/>
+      <c r="AW12" s="56"/>
+      <c r="AX12" s="56"/>
+      <c r="AY12" s="56"/>
+      <c r="AZ12" s="56"/>
+      <c r="BA12" s="56"/>
+      <c r="BB12" s="56"/>
+    </row>
+    <row r="13" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A13" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="69">
+      <c r="B13" s="57">
         <v>2.1</v>
       </c>
-      <c r="C13" s="67">
+      <c r="C13" s="55">
         <v>5.8999999999999995</v>
       </c>
-      <c r="D13" s="67">
+      <c r="D13" s="55">
         <v>10</v>
       </c>
-      <c r="E13" s="67">
+      <c r="E13" s="55">
         <v>8.2000000000000011</v>
       </c>
-      <c r="F13" s="67">
+      <c r="F13" s="55">
         <v>10</v>
       </c>
-      <c r="G13" s="67">
+      <c r="G13" s="55">
         <v>10.9</v>
       </c>
-      <c r="H13" s="67">
+      <c r="H13" s="55">
         <v>10</v>
       </c>
-      <c r="I13" s="67">
+      <c r="I13" s="55">
         <v>11</v>
       </c>
-      <c r="J13" s="67">
+      <c r="J13" s="55">
         <v>10.7</v>
       </c>
-      <c r="K13" s="67">
+      <c r="K13" s="55">
         <v>8.7999999999999989</v>
       </c>
-      <c r="L13" s="67">
+      <c r="L13" s="55">
         <v>10.299999999999999</v>
       </c>
-      <c r="M13" s="67">
+      <c r="M13" s="55">
         <v>9.6</v>
       </c>
-      <c r="N13" s="67">
+      <c r="N13" s="55">
         <v>10.199999999999999</v>
       </c>
-      <c r="O13" s="67">
+      <c r="O13" s="55">
         <v>7.9</v>
       </c>
-      <c r="P13" s="67">
+      <c r="P13" s="55">
         <v>7.7</v>
       </c>
-      <c r="Q13" s="67">
+      <c r="Q13" s="55">
         <v>7.8</v>
       </c>
-      <c r="R13" s="67">
+      <c r="R13" s="55">
         <v>6.1</v>
       </c>
-      <c r="S13" s="67">
+      <c r="S13" s="55">
         <v>9.3000000000000007</v>
       </c>
-      <c r="T13" s="67">
+      <c r="T13" s="55">
         <v>7.7</v>
       </c>
-      <c r="U13" s="67">
+      <c r="U13" s="55">
         <v>5.5</v>
       </c>
-      <c r="V13" s="67">
+      <c r="V13" s="55">
         <v>5.7</v>
       </c>
-      <c r="W13" s="67">
+      <c r="W13" s="55">
         <v>4</v>
       </c>
-      <c r="X13" s="67">
+      <c r="X13" s="55">
         <v>5</v>
       </c>
-      <c r="Y13" s="67">
+      <c r="Y13" s="55">
         <v>4.3</v>
       </c>
-      <c r="Z13" s="67">
+      <c r="Z13" s="55">
         <v>4.9000000000000004</v>
       </c>
-      <c r="AA13" s="67">
+      <c r="AA13" s="55">
         <v>3.8</v>
       </c>
-      <c r="AB13" s="67">
+      <c r="AB13" s="55">
         <v>3.9</v>
       </c>
-      <c r="AC13" s="59"/>
-      <c r="AD13" s="68"/>
-      <c r="AE13" s="68"/>
-      <c r="AF13" s="68"/>
-      <c r="AG13" s="68"/>
-      <c r="AH13" s="68"/>
-      <c r="AI13" s="68"/>
-      <c r="AJ13" s="68"/>
-      <c r="AK13" s="68"/>
-      <c r="AL13" s="68"/>
-      <c r="AM13" s="68"/>
-      <c r="AN13" s="68"/>
-      <c r="AO13" s="68"/>
-      <c r="AP13" s="68"/>
-      <c r="AQ13" s="68"/>
-      <c r="AR13" s="68"/>
-      <c r="AS13" s="68"/>
-      <c r="AT13" s="68"/>
-      <c r="AU13" s="68"/>
-      <c r="AV13" s="68"/>
-      <c r="AW13" s="68"/>
-      <c r="AX13" s="68"/>
-      <c r="AY13" s="68"/>
-      <c r="AZ13" s="68"/>
-      <c r="BA13" s="68"/>
-      <c r="BB13" s="68"/>
-    </row>
-    <row r="14" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="59" t="s">
+      <c r="AC13" s="50"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="56"/>
+      <c r="AH13" s="56"/>
+      <c r="AI13" s="56"/>
+      <c r="AJ13" s="56"/>
+      <c r="AK13" s="56"/>
+      <c r="AL13" s="56"/>
+      <c r="AM13" s="56"/>
+      <c r="AN13" s="56"/>
+      <c r="AO13" s="56"/>
+      <c r="AP13" s="56"/>
+      <c r="AQ13" s="56"/>
+      <c r="AR13" s="56"/>
+      <c r="AS13" s="56"/>
+      <c r="AT13" s="56"/>
+      <c r="AU13" s="56"/>
+      <c r="AV13" s="56"/>
+      <c r="AW13" s="56"/>
+      <c r="AX13" s="56"/>
+      <c r="AY13" s="56"/>
+      <c r="AZ13" s="56"/>
+      <c r="BA13" s="56"/>
+      <c r="BB13" s="56"/>
+    </row>
+    <row r="14" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A14" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="69">
+      <c r="B14" s="57">
         <v>1.6</v>
       </c>
-      <c r="C14" s="67">
+      <c r="C14" s="55">
         <v>4.5</v>
       </c>
-      <c r="D14" s="67">
+      <c r="D14" s="55">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E14" s="67">
+      <c r="E14" s="55">
         <v>6.9</v>
       </c>
-      <c r="F14" s="67">
+      <c r="F14" s="55">
         <v>6.2</v>
       </c>
-      <c r="G14" s="67">
+      <c r="G14" s="55">
         <v>6.3</v>
       </c>
-      <c r="H14" s="67">
+      <c r="H14" s="55">
         <v>9.1</v>
       </c>
-      <c r="I14" s="67">
+      <c r="I14" s="55">
         <v>10.5</v>
       </c>
-      <c r="J14" s="67">
+      <c r="J14" s="55">
         <v>12.2</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="55">
         <v>14.499999999999998</v>
       </c>
-      <c r="L14" s="67">
+      <c r="L14" s="55">
         <v>14.7</v>
       </c>
-      <c r="M14" s="67">
+      <c r="M14" s="55">
         <v>15.4</v>
       </c>
-      <c r="N14" s="67">
+      <c r="N14" s="55">
         <v>15.2</v>
       </c>
-      <c r="O14" s="67">
+      <c r="O14" s="55">
         <v>17.299999999999997</v>
       </c>
-      <c r="P14" s="67">
+      <c r="P14" s="55">
         <v>22.3</v>
       </c>
-      <c r="Q14" s="67">
+      <c r="Q14" s="55">
         <v>22.6</v>
       </c>
-      <c r="R14" s="67">
+      <c r="R14" s="55">
         <v>25.900000000000002</v>
       </c>
-      <c r="S14" s="67">
+      <c r="S14" s="55">
         <v>20.599999999999998</v>
       </c>
-      <c r="T14" s="67">
+      <c r="T14" s="55">
         <v>19.900000000000002</v>
       </c>
-      <c r="U14" s="67">
+      <c r="U14" s="55">
         <v>21.7</v>
       </c>
-      <c r="V14" s="67">
+      <c r="V14" s="55">
         <v>22.1</v>
       </c>
-      <c r="W14" s="67">
+      <c r="W14" s="55">
         <v>18.399999999999999</v>
       </c>
-      <c r="X14" s="67">
+      <c r="X14" s="55">
         <v>20.8</v>
       </c>
-      <c r="Y14" s="67">
+      <c r="Y14" s="55">
         <v>25.6</v>
       </c>
-      <c r="Z14" s="67">
+      <c r="Z14" s="55">
         <v>20.599999999999998</v>
       </c>
-      <c r="AA14" s="67">
+      <c r="AA14" s="55">
         <v>22.400000000000002</v>
       </c>
-      <c r="AB14" s="67">
+      <c r="AB14" s="55">
         <v>23.3</v>
       </c>
-      <c r="AC14" s="59"/>
-      <c r="AD14" s="68"/>
-      <c r="AE14" s="68"/>
-      <c r="AF14" s="68"/>
-      <c r="AG14" s="68"/>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-      <c r="AJ14" s="68"/>
-      <c r="AK14" s="68"/>
-      <c r="AL14" s="68"/>
-      <c r="AM14" s="68"/>
-      <c r="AN14" s="68"/>
-      <c r="AO14" s="68"/>
-      <c r="AP14" s="68"/>
-      <c r="AQ14" s="68"/>
-      <c r="AR14" s="68"/>
-      <c r="AS14" s="68"/>
-      <c r="AT14" s="68"/>
-      <c r="AU14" s="68"/>
-      <c r="AV14" s="68"/>
-      <c r="AW14" s="68"/>
-      <c r="AX14" s="68"/>
-      <c r="AY14" s="68"/>
-      <c r="AZ14" s="68"/>
-      <c r="BA14" s="68"/>
-      <c r="BB14" s="68"/>
-    </row>
-    <row r="15" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
+      <c r="AC14" s="50"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="56"/>
+      <c r="AM14" s="56"/>
+      <c r="AN14" s="56"/>
+      <c r="AO14" s="56"/>
+      <c r="AP14" s="56"/>
+      <c r="AQ14" s="56"/>
+      <c r="AR14" s="56"/>
+      <c r="AS14" s="56"/>
+      <c r="AT14" s="56"/>
+      <c r="AU14" s="56"/>
+      <c r="AV14" s="56"/>
+      <c r="AW14" s="56"/>
+      <c r="AX14" s="56"/>
+      <c r="AY14" s="56"/>
+      <c r="AZ14" s="56"/>
+      <c r="BA14" s="56"/>
+      <c r="BB14" s="56"/>
+    </row>
+    <row r="15" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A15" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="70"/>
-      <c r="V15" s="70"/>
-      <c r="W15" s="70"/>
-      <c r="X15" s="70"/>
-      <c r="Y15" s="70"/>
-      <c r="Z15" s="70"/>
-      <c r="AA15" s="65"/>
-      <c r="AB15" s="65"/>
-      <c r="AC15" s="55"/>
-      <c r="AD15" s="70"/>
-      <c r="AE15" s="70"/>
-      <c r="AF15" s="70"/>
-      <c r="AG15" s="70"/>
-      <c r="AH15" s="70"/>
-      <c r="AI15" s="70"/>
-      <c r="AJ15" s="70"/>
-      <c r="AK15" s="70"/>
-      <c r="AL15" s="70"/>
-      <c r="AM15" s="70"/>
-      <c r="AN15" s="70"/>
-      <c r="AO15" s="70"/>
-      <c r="AP15" s="70"/>
-      <c r="AQ15" s="70"/>
-      <c r="AR15" s="70"/>
-      <c r="AS15" s="70"/>
-      <c r="AT15" s="70"/>
-      <c r="AU15" s="70"/>
-      <c r="AV15" s="70"/>
-      <c r="AW15" s="70"/>
-      <c r="AX15" s="70"/>
-      <c r="AY15" s="70"/>
-      <c r="AZ15" s="70"/>
-      <c r="BA15" s="70"/>
-      <c r="BB15" s="70"/>
-    </row>
-    <row r="16" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="58"/>
+      <c r="S15" s="58"/>
+      <c r="T15" s="58"/>
+      <c r="U15" s="58"/>
+      <c r="V15" s="58"/>
+      <c r="W15" s="58"/>
+      <c r="X15" s="58"/>
+      <c r="Y15" s="58"/>
+      <c r="Z15" s="58"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="54"/>
+      <c r="AC15" s="47"/>
+      <c r="AD15" s="58"/>
+      <c r="AE15" s="58"/>
+      <c r="AF15" s="58"/>
+      <c r="AG15" s="58"/>
+      <c r="AH15" s="58"/>
+      <c r="AI15" s="58"/>
+      <c r="AJ15" s="58"/>
+      <c r="AK15" s="58"/>
+      <c r="AL15" s="58"/>
+      <c r="AM15" s="58"/>
+      <c r="AN15" s="58"/>
+      <c r="AO15" s="58"/>
+      <c r="AP15" s="58"/>
+      <c r="AQ15" s="58"/>
+      <c r="AR15" s="58"/>
+      <c r="AS15" s="58"/>
+      <c r="AT15" s="58"/>
+      <c r="AU15" s="58"/>
+      <c r="AV15" s="58"/>
+      <c r="AW15" s="58"/>
+      <c r="AX15" s="58"/>
+      <c r="AY15" s="58"/>
+      <c r="AZ15" s="58"/>
+      <c r="BA15" s="58"/>
+      <c r="BB15" s="58"/>
+    </row>
+    <row r="16" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A16" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="71">
+      <c r="B16" s="59">
         <v>20</v>
       </c>
-      <c r="C16" s="71">
+      <c r="C16" s="59">
         <v>23</v>
       </c>
-      <c r="D16" s="71">
+      <c r="D16" s="59">
         <v>23.3</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="59">
         <v>23.4</v>
       </c>
-      <c r="F16" s="71">
+      <c r="F16" s="59">
         <v>23.1</v>
       </c>
-      <c r="G16" s="71">
+      <c r="G16" s="59">
         <v>23.5</v>
       </c>
-      <c r="H16" s="71">
+      <c r="H16" s="59">
         <v>23.3</v>
       </c>
-      <c r="I16" s="71">
+      <c r="I16" s="59">
         <v>23.4</v>
       </c>
-      <c r="J16" s="71">
+      <c r="J16" s="59">
         <v>23.3</v>
       </c>
-      <c r="K16" s="71">
+      <c r="K16" s="59">
         <v>23.4</v>
       </c>
-      <c r="L16" s="71">
+      <c r="L16" s="59">
         <v>23.4</v>
       </c>
-      <c r="M16" s="71">
+      <c r="M16" s="59">
         <v>23</v>
       </c>
-      <c r="N16" s="71">
+      <c r="N16" s="59">
         <v>22.9</v>
       </c>
-      <c r="O16" s="71">
+      <c r="O16" s="59">
         <v>23</v>
       </c>
-      <c r="P16" s="71">
+      <c r="P16" s="59">
         <v>23.1</v>
       </c>
-      <c r="Q16" s="71">
+      <c r="Q16" s="59">
         <v>23.3</v>
       </c>
-      <c r="R16" s="71">
+      <c r="R16" s="59">
         <v>23.1</v>
       </c>
-      <c r="S16" s="71">
+      <c r="S16" s="59">
         <v>23.5</v>
       </c>
-      <c r="T16" s="71">
+      <c r="T16" s="59">
         <v>23.3</v>
       </c>
-      <c r="U16" s="71">
+      <c r="U16" s="59">
         <v>24.1</v>
       </c>
-      <c r="V16" s="71">
+      <c r="V16" s="59">
         <v>24.3</v>
       </c>
-      <c r="W16" s="71">
+      <c r="W16" s="59">
         <v>25.3</v>
       </c>
-      <c r="X16" s="71">
+      <c r="X16" s="59">
         <v>26.2</v>
       </c>
-      <c r="Y16" s="71">
+      <c r="Y16" s="59">
         <v>26</v>
       </c>
-      <c r="Z16" s="71">
+      <c r="Z16" s="59">
         <v>27.8</v>
       </c>
-      <c r="AA16" s="65">
+      <c r="AA16" s="54">
         <v>28.3</v>
       </c>
-      <c r="AB16" s="65">
+      <c r="AB16" s="54">
         <v>28.7</v>
       </c>
-      <c r="AC16" s="59"/>
-      <c r="AD16" s="72"/>
-      <c r="AE16" s="72"/>
-      <c r="AF16" s="72"/>
-      <c r="AG16" s="72"/>
-      <c r="AH16" s="72"/>
-      <c r="AI16" s="72"/>
-      <c r="AJ16" s="72"/>
-      <c r="AK16" s="72"/>
-      <c r="AL16" s="72"/>
-      <c r="AM16" s="72"/>
-      <c r="AN16" s="72"/>
-      <c r="AO16" s="72"/>
-      <c r="AP16" s="72"/>
-      <c r="AQ16" s="72"/>
-      <c r="AR16" s="72"/>
-      <c r="AS16" s="72"/>
-      <c r="AT16" s="72"/>
-      <c r="AU16" s="72"/>
-      <c r="AV16" s="72"/>
-      <c r="AW16" s="72"/>
-      <c r="AX16" s="72"/>
-      <c r="AY16" s="72"/>
-      <c r="AZ16" s="72"/>
-      <c r="BA16" s="72"/>
-      <c r="BB16" s="72"/>
-    </row>
-    <row r="17" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="59" t="s">
+      <c r="AC16" s="50"/>
+      <c r="AD16" s="59"/>
+      <c r="AE16" s="59"/>
+      <c r="AF16" s="59"/>
+      <c r="AG16" s="59"/>
+      <c r="AH16" s="59"/>
+      <c r="AI16" s="59"/>
+      <c r="AJ16" s="59"/>
+      <c r="AK16" s="59"/>
+      <c r="AL16" s="59"/>
+      <c r="AM16" s="59"/>
+      <c r="AN16" s="59"/>
+      <c r="AO16" s="59"/>
+      <c r="AP16" s="59"/>
+      <c r="AQ16" s="59"/>
+      <c r="AR16" s="59"/>
+      <c r="AS16" s="59"/>
+      <c r="AT16" s="59"/>
+      <c r="AU16" s="59"/>
+      <c r="AV16" s="59"/>
+      <c r="AW16" s="59"/>
+      <c r="AX16" s="59"/>
+      <c r="AY16" s="59"/>
+      <c r="AZ16" s="59"/>
+      <c r="BA16" s="59"/>
+      <c r="BB16" s="59"/>
+    </row>
+    <row r="17" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A17" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="71">
+      <c r="B17" s="59">
         <v>14.6</v>
       </c>
-      <c r="C17" s="71">
+      <c r="C17" s="59">
         <v>20.100000000000001</v>
       </c>
-      <c r="D17" s="71">
+      <c r="D17" s="59">
         <v>18.8</v>
       </c>
-      <c r="E17" s="71">
+      <c r="E17" s="59">
         <v>18.2</v>
       </c>
-      <c r="F17" s="71">
+      <c r="F17" s="59">
         <v>17.8</v>
       </c>
-      <c r="G17" s="71">
+      <c r="G17" s="59">
         <v>17</v>
       </c>
-      <c r="H17" s="71">
+      <c r="H17" s="59">
         <v>18</v>
       </c>
-      <c r="I17" s="71">
+      <c r="I17" s="59">
         <v>17.8</v>
       </c>
-      <c r="J17" s="71">
+      <c r="J17" s="59">
         <v>18.399999999999999</v>
       </c>
-      <c r="K17" s="71">
+      <c r="K17" s="59">
         <v>19.2</v>
       </c>
-      <c r="L17" s="71">
+      <c r="L17" s="59">
         <v>18.2</v>
       </c>
-      <c r="M17" s="71">
+      <c r="M17" s="59">
         <v>18.5</v>
       </c>
-      <c r="N17" s="71">
+      <c r="N17" s="59">
         <v>17.899999999999999</v>
       </c>
-      <c r="O17" s="71">
+      <c r="O17" s="59">
         <v>18.8</v>
       </c>
-      <c r="P17" s="71">
+      <c r="P17" s="59">
         <v>19.3</v>
       </c>
-      <c r="Q17" s="71">
+      <c r="Q17" s="59">
         <v>19.899999999999999</v>
       </c>
-      <c r="R17" s="71">
+      <c r="R17" s="59">
         <v>20</v>
       </c>
-      <c r="S17" s="71">
+      <c r="S17" s="59">
         <v>20.2</v>
       </c>
-      <c r="T17" s="71">
+      <c r="T17" s="59">
         <v>20.5</v>
       </c>
-      <c r="U17" s="71">
+      <c r="U17" s="59">
         <v>20.6</v>
       </c>
-      <c r="V17" s="71">
+      <c r="V17" s="59">
         <v>21.2</v>
       </c>
-      <c r="W17" s="71">
+      <c r="W17" s="59">
         <v>22</v>
       </c>
-      <c r="X17" s="71">
+      <c r="X17" s="59">
         <v>23</v>
       </c>
-      <c r="Y17" s="71">
+      <c r="Y17" s="59">
         <v>23.6</v>
       </c>
-      <c r="Z17" s="71">
+      <c r="Z17" s="59">
         <v>23.4</v>
       </c>
-      <c r="AA17" s="65">
+      <c r="AA17" s="54">
         <v>24.5</v>
       </c>
-      <c r="AB17" s="65">
+      <c r="AB17" s="54">
         <v>24.3</v>
       </c>
-      <c r="AC17" s="59"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="72"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="72"/>
-      <c r="AJ17" s="72"/>
-      <c r="AK17" s="72"/>
-      <c r="AL17" s="72"/>
-      <c r="AM17" s="72"/>
-      <c r="AN17" s="72"/>
-      <c r="AO17" s="72"/>
-      <c r="AP17" s="72"/>
-      <c r="AQ17" s="72"/>
-      <c r="AR17" s="72"/>
-      <c r="AS17" s="72"/>
-      <c r="AT17" s="72"/>
-      <c r="AU17" s="72"/>
-      <c r="AV17" s="72"/>
-      <c r="AW17" s="72"/>
-      <c r="AX17" s="72"/>
-      <c r="AY17" s="72"/>
-      <c r="AZ17" s="72"/>
-      <c r="BA17" s="72"/>
-      <c r="BB17" s="72"/>
-    </row>
-    <row r="18" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="59" t="s">
+      <c r="AC17" s="50"/>
+      <c r="AD17" s="59"/>
+      <c r="AE17" s="59"/>
+      <c r="AF17" s="59"/>
+      <c r="AG17" s="59"/>
+      <c r="AH17" s="59"/>
+      <c r="AI17" s="59"/>
+      <c r="AJ17" s="59"/>
+      <c r="AK17" s="59"/>
+      <c r="AL17" s="59"/>
+      <c r="AM17" s="59"/>
+      <c r="AN17" s="59"/>
+      <c r="AO17" s="59"/>
+      <c r="AP17" s="59"/>
+      <c r="AQ17" s="59"/>
+      <c r="AR17" s="59"/>
+      <c r="AS17" s="59"/>
+      <c r="AT17" s="59"/>
+      <c r="AU17" s="59"/>
+      <c r="AV17" s="59"/>
+      <c r="AW17" s="59"/>
+      <c r="AX17" s="59"/>
+      <c r="AY17" s="59"/>
+      <c r="AZ17" s="59"/>
+      <c r="BA17" s="59"/>
+      <c r="BB17" s="59"/>
+    </row>
+    <row r="18" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A18" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="71">
+      <c r="B18" s="59">
         <v>16.5</v>
       </c>
-      <c r="C18" s="71">
+      <c r="C18" s="59">
         <v>18.2</v>
       </c>
-      <c r="D18" s="71">
+      <c r="D18" s="59">
         <v>17.399999999999999</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="59">
         <v>18.2</v>
       </c>
-      <c r="F18" s="71">
+      <c r="F18" s="59">
         <v>17.5</v>
       </c>
-      <c r="G18" s="71">
+      <c r="G18" s="59">
         <v>17.600000000000001</v>
       </c>
-      <c r="H18" s="71">
+      <c r="H18" s="59">
         <v>17.399999999999999</v>
       </c>
-      <c r="I18" s="71">
+      <c r="I18" s="59">
         <v>16.899999999999999</v>
       </c>
-      <c r="J18" s="71">
+      <c r="J18" s="59">
         <v>17.100000000000001</v>
       </c>
-      <c r="K18" s="71">
+      <c r="K18" s="59">
         <v>16.8</v>
       </c>
-      <c r="L18" s="71">
+      <c r="L18" s="59">
         <v>17</v>
       </c>
-      <c r="M18" s="71">
+      <c r="M18" s="59">
         <v>16.3</v>
       </c>
-      <c r="N18" s="71">
+      <c r="N18" s="59">
         <v>16.7</v>
       </c>
-      <c r="O18" s="71">
+      <c r="O18" s="59">
         <v>16</v>
       </c>
-      <c r="P18" s="71">
+      <c r="P18" s="59">
         <v>15.8</v>
       </c>
-      <c r="Q18" s="71">
+      <c r="Q18" s="59">
         <v>16.100000000000001</v>
       </c>
-      <c r="R18" s="71">
+      <c r="R18" s="59">
         <v>15.7</v>
       </c>
-      <c r="S18" s="71">
+      <c r="S18" s="59">
         <v>15.8</v>
       </c>
-      <c r="T18" s="71">
+      <c r="T18" s="59">
         <v>16.100000000000001</v>
       </c>
-      <c r="U18" s="71">
+      <c r="U18" s="59">
         <v>16.2</v>
       </c>
-      <c r="V18" s="71">
+      <c r="V18" s="59">
         <v>16.5</v>
       </c>
-      <c r="W18" s="71">
+      <c r="W18" s="59">
         <v>16.899999999999999</v>
       </c>
-      <c r="X18" s="71">
+      <c r="X18" s="59">
         <v>16.899999999999999</v>
       </c>
-      <c r="Y18" s="71">
+      <c r="Y18" s="59">
         <v>17.2</v>
       </c>
-      <c r="Z18" s="71">
+      <c r="Z18" s="59">
         <v>17.2</v>
       </c>
-      <c r="AA18" s="65">
+      <c r="AA18" s="54">
         <v>17.399999999999999</v>
       </c>
-      <c r="AB18" s="71">
+      <c r="AB18" s="59">
         <v>18</v>
       </c>
-      <c r="AC18" s="59"/>
-      <c r="AD18" s="72"/>
-      <c r="AE18" s="72"/>
-      <c r="AF18" s="72"/>
-      <c r="AG18" s="72"/>
-      <c r="AH18" s="72"/>
-      <c r="AI18" s="72"/>
-      <c r="AJ18" s="72"/>
-      <c r="AK18" s="72"/>
-      <c r="AL18" s="72"/>
-      <c r="AM18" s="72"/>
-      <c r="AN18" s="72"/>
-      <c r="AO18" s="72"/>
-      <c r="AP18" s="72"/>
-      <c r="AQ18" s="72"/>
-      <c r="AR18" s="72"/>
-      <c r="AS18" s="72"/>
-      <c r="AT18" s="72"/>
-      <c r="AU18" s="72"/>
-      <c r="AV18" s="72"/>
-      <c r="AW18" s="72"/>
-      <c r="AX18" s="72"/>
-      <c r="AY18" s="72"/>
-      <c r="AZ18" s="72"/>
-      <c r="BA18" s="72"/>
-      <c r="BB18" s="72"/>
-    </row>
-    <row r="19" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="AC18" s="50"/>
+      <c r="AD18" s="59"/>
+      <c r="AE18" s="59"/>
+      <c r="AF18" s="59"/>
+      <c r="AG18" s="59"/>
+      <c r="AH18" s="59"/>
+      <c r="AI18" s="59"/>
+      <c r="AJ18" s="59"/>
+      <c r="AK18" s="59"/>
+      <c r="AL18" s="59"/>
+      <c r="AM18" s="59"/>
+      <c r="AN18" s="59"/>
+      <c r="AO18" s="59"/>
+      <c r="AP18" s="59"/>
+      <c r="AQ18" s="59"/>
+      <c r="AR18" s="59"/>
+      <c r="AS18" s="59"/>
+      <c r="AT18" s="59"/>
+      <c r="AU18" s="59"/>
+      <c r="AV18" s="59"/>
+      <c r="AW18" s="59"/>
+      <c r="AX18" s="59"/>
+      <c r="AY18" s="59"/>
+      <c r="AZ18" s="59"/>
+      <c r="BA18" s="59"/>
+      <c r="BB18" s="59"/>
+    </row>
+    <row r="19" spans="1:54" ht="16.5" customHeight="1">
+      <c r="A19" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="59">
         <v>14.1</v>
       </c>
-      <c r="C19" s="71">
+      <c r="C19" s="59">
         <v>16.5</v>
       </c>
-      <c r="D19" s="71">
+      <c r="D19" s="59">
         <v>17.8</v>
       </c>
-      <c r="E19" s="71">
+      <c r="E19" s="59">
         <v>17.899999999999999</v>
       </c>
-      <c r="F19" s="71">
+      <c r="F19" s="59">
         <v>17.899999999999999</v>
       </c>
-      <c r="G19" s="71">
+      <c r="G19" s="59">
         <v>18.2</v>
       </c>
-      <c r="H19" s="71">
+      <c r="H19" s="59">
         <v>17.8</v>
       </c>
-      <c r="I19" s="71">
+      <c r="I19" s="59">
         <v>18.100000000000001</v>
       </c>
-      <c r="J19" s="71">
+      <c r="J19" s="59">
         <v>18.3</v>
       </c>
-      <c r="K19" s="71">
+      <c r="K19" s="59">
         <v>18.2</v>
       </c>
-      <c r="L19" s="71">
+      <c r="L19" s="59">
         <v>18.7</v>
       </c>
-      <c r="M19" s="71">
+      <c r="M19" s="59">
         <v>18.3</v>
       </c>
-      <c r="N19" s="71">
+      <c r="N19" s="59">
         <v>18.600000000000001</v>
       </c>
-      <c r="O19" s="71">
+      <c r="O19" s="59">
         <v>18</v>
       </c>
-      <c r="P19" s="71">
+      <c r="P19" s="59">
         <v>18.7</v>
       </c>
-      <c r="Q19" s="71">
+      <c r="Q19" s="59">
         <v>19</v>
       </c>
-      <c r="R19" s="71">
+      <c r="R19" s="59">
         <v>19.2</v>
       </c>
-      <c r="S19" s="71">
+      <c r="S19" s="59">
         <v>19.3</v>
       </c>
-      <c r="T19" s="71">
+      <c r="T19" s="59">
         <v>19.5</v>
       </c>
-      <c r="U19" s="71">
+      <c r="U19" s="59">
         <v>19.5</v>
       </c>
-      <c r="V19" s="71">
+      <c r="V19" s="59">
         <v>19.8</v>
       </c>
-      <c r="W19" s="71">
+      <c r="W19" s="59">
         <v>20.100000000000001</v>
       </c>
-      <c r="X19" s="71">
+      <c r="X19" s="59">
         <v>20.100000000000001</v>
       </c>
-      <c r="Y19" s="71">
+      <c r="Y19" s="59">
         <v>21</v>
       </c>
-      <c r="Z19" s="71">
+      <c r="Z19" s="59">
         <v>21.4</v>
       </c>
-      <c r="AA19" s="65">
+      <c r="AA19" s="54">
         <v>21.1</v>
       </c>
-      <c r="AB19" s="65">
+      <c r="AB19" s="54">
         <v>21.2</v>
       </c>
-      <c r="AC19" s="59"/>
-      <c r="AD19" s="72"/>
-      <c r="AE19" s="72"/>
-      <c r="AF19" s="72"/>
-      <c r="AG19" s="72"/>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="72"/>
-      <c r="AJ19" s="72"/>
-      <c r="AK19" s="72"/>
-      <c r="AL19" s="72"/>
-      <c r="AM19" s="72"/>
-      <c r="AN19" s="72"/>
-      <c r="AO19" s="72"/>
-      <c r="AP19" s="72"/>
-      <c r="AQ19" s="72"/>
-      <c r="AR19" s="72"/>
-      <c r="AS19" s="72"/>
-      <c r="AT19" s="72"/>
-      <c r="AU19" s="72"/>
-      <c r="AV19" s="72"/>
-      <c r="AW19" s="72"/>
-      <c r="AX19" s="72"/>
-      <c r="AY19" s="72"/>
-      <c r="AZ19" s="72"/>
-      <c r="BA19" s="72"/>
-      <c r="BB19" s="72"/>
-    </row>
-    <row r="20" spans="1:54" s="13" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="73" t="s">
+      <c r="AC19" s="50"/>
+      <c r="AD19" s="59"/>
+      <c r="AE19" s="59"/>
+      <c r="AF19" s="59"/>
+      <c r="AG19" s="59"/>
+      <c r="AH19" s="59"/>
+      <c r="AI19" s="59"/>
+      <c r="AJ19" s="59"/>
+      <c r="AK19" s="59"/>
+      <c r="AL19" s="59"/>
+      <c r="AM19" s="59"/>
+      <c r="AN19" s="59"/>
+      <c r="AO19" s="59"/>
+      <c r="AP19" s="59"/>
+      <c r="AQ19" s="59"/>
+      <c r="AR19" s="59"/>
+      <c r="AS19" s="59"/>
+      <c r="AT19" s="59"/>
+      <c r="AU19" s="59"/>
+      <c r="AV19" s="59"/>
+      <c r="AW19" s="59"/>
+      <c r="AX19" s="59"/>
+      <c r="AY19" s="59"/>
+      <c r="AZ19" s="59"/>
+      <c r="BA19" s="59"/>
+      <c r="BB19" s="59"/>
+    </row>
+    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A20" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="74">
+      <c r="B20" s="61">
         <v>13.2</v>
       </c>
-      <c r="C20" s="74">
+      <c r="C20" s="61">
         <v>16.5</v>
       </c>
-      <c r="D20" s="74">
+      <c r="D20" s="61">
         <v>16.399999999999999</v>
       </c>
-      <c r="E20" s="74">
+      <c r="E20" s="61">
         <v>16.7</v>
       </c>
-      <c r="F20" s="74">
+      <c r="F20" s="61">
         <v>16.2</v>
       </c>
-      <c r="G20" s="74">
+      <c r="G20" s="61">
         <v>16.3</v>
       </c>
-      <c r="H20" s="74">
+      <c r="H20" s="61">
         <v>16</v>
       </c>
-      <c r="I20" s="74">
+      <c r="I20" s="61">
         <v>16</v>
       </c>
-      <c r="J20" s="74">
+      <c r="J20" s="61">
         <v>16.2</v>
       </c>
-      <c r="K20" s="74">
+      <c r="K20" s="61">
         <v>16.100000000000001</v>
       </c>
-      <c r="L20" s="74">
+      <c r="L20" s="61">
         <v>16.2</v>
       </c>
-      <c r="M20" s="74">
+      <c r="M20" s="61">
         <v>16.100000000000001</v>
       </c>
-      <c r="N20" s="74">
+      <c r="N20" s="61">
         <v>16</v>
       </c>
-      <c r="O20" s="74">
+      <c r="O20" s="61">
         <v>16.399999999999999</v>
       </c>
-      <c r="P20" s="74">
+      <c r="P20" s="61">
         <v>16.3</v>
       </c>
-      <c r="Q20" s="74">
+      <c r="Q20" s="61">
         <v>16.399999999999999</v>
       </c>
-      <c r="R20" s="74">
+      <c r="R20" s="61">
         <v>16.5</v>
       </c>
-      <c r="S20" s="74">
+      <c r="S20" s="61">
         <v>16.7</v>
       </c>
-      <c r="T20" s="74">
+      <c r="T20" s="61">
         <v>17.2</v>
       </c>
-      <c r="U20" s="74">
+      <c r="U20" s="61">
         <v>17.7</v>
       </c>
-      <c r="V20" s="74">
+      <c r="V20" s="61">
         <v>18.2</v>
       </c>
-      <c r="W20" s="74">
+      <c r="W20" s="61">
         <v>19.3</v>
       </c>
-      <c r="X20" s="74">
+      <c r="X20" s="61">
         <v>19.7</v>
       </c>
-      <c r="Y20" s="74">
+      <c r="Y20" s="61">
         <v>19.8</v>
       </c>
-      <c r="Z20" s="74">
+      <c r="Z20" s="61">
         <v>20</v>
       </c>
-      <c r="AA20" s="75">
+      <c r="AA20" s="62">
         <v>20.9</v>
       </c>
-      <c r="AB20" s="75">
+      <c r="AB20" s="62">
         <v>21.2</v>
       </c>
-      <c r="AC20" s="59"/>
-      <c r="AD20" s="72"/>
-      <c r="AE20" s="72"/>
-      <c r="AF20" s="72"/>
-      <c r="AG20" s="72"/>
-      <c r="AH20" s="72"/>
-      <c r="AI20" s="72"/>
-      <c r="AJ20" s="72"/>
-      <c r="AK20" s="72"/>
-      <c r="AL20" s="72"/>
-      <c r="AM20" s="72"/>
-      <c r="AN20" s="72"/>
-      <c r="AO20" s="72"/>
-      <c r="AP20" s="72"/>
-      <c r="AQ20" s="72"/>
-      <c r="AR20" s="72"/>
-      <c r="AS20" s="72"/>
-      <c r="AT20" s="72"/>
-      <c r="AU20" s="72"/>
-      <c r="AV20" s="72"/>
-      <c r="AW20" s="72"/>
-      <c r="AX20" s="72"/>
-      <c r="AY20" s="72"/>
-      <c r="AZ20" s="72"/>
-      <c r="BA20" s="72"/>
-      <c r="BB20" s="72"/>
-    </row>
-    <row r="21" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="97" t="s">
+      <c r="AC20" s="50"/>
+      <c r="AD20" s="59"/>
+      <c r="AE20" s="59"/>
+      <c r="AF20" s="59"/>
+      <c r="AG20" s="59"/>
+      <c r="AH20" s="59"/>
+      <c r="AI20" s="59"/>
+      <c r="AJ20" s="59"/>
+      <c r="AK20" s="59"/>
+      <c r="AL20" s="59"/>
+      <c r="AM20" s="59"/>
+      <c r="AN20" s="59"/>
+      <c r="AO20" s="59"/>
+      <c r="AP20" s="59"/>
+      <c r="AQ20" s="59"/>
+      <c r="AR20" s="59"/>
+      <c r="AS20" s="59"/>
+      <c r="AT20" s="59"/>
+      <c r="AU20" s="59"/>
+      <c r="AV20" s="59"/>
+      <c r="AW20" s="59"/>
+      <c r="AX20" s="59"/>
+      <c r="AY20" s="59"/>
+      <c r="AZ20" s="59"/>
+      <c r="BA20" s="59"/>
+      <c r="BB20" s="59"/>
+    </row>
+    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A21" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="97"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="97"/>
-      <c r="M21" s="97"/>
-      <c r="N21" s="97"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="97"/>
-      <c r="Q21" s="97"/>
-    </row>
-    <row r="22" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="98"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="98"/>
-      <c r="O22" s="98"/>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-    </row>
-    <row r="23" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="98" t="s">
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+    </row>
+    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A22" s="81"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="81"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="81"/>
+    </row>
+    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A23" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-      <c r="N23" s="98"/>
-      <c r="O23" s="98"/>
-      <c r="P23" s="98"/>
-      <c r="Q23" s="98"/>
-    </row>
-    <row r="24" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="91" t="s">
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="81"/>
+      <c r="Q23" s="81"/>
+    </row>
+    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A24" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="91"/>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="91"/>
-      <c r="P24" s="91"/>
-      <c r="Q24" s="91"/>
-    </row>
-    <row r="25" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="91" t="s">
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="77"/>
+      <c r="M24" s="77"/>
+      <c r="N24" s="77"/>
+      <c r="O24" s="77"/>
+      <c r="P24" s="77"/>
+      <c r="Q24" s="77"/>
+    </row>
+    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A25" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="91"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="91"/>
-      <c r="H25" s="91"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="91"/>
-    </row>
-    <row r="26" spans="1:54" s="76" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="92" t="s">
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="77"/>
+      <c r="M25" s="77"/>
+      <c r="N25" s="77"/>
+      <c r="O25" s="77"/>
+      <c r="P25" s="77"/>
+      <c r="Q25" s="77"/>
+    </row>
+    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A26" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="92"/>
-      <c r="I26" s="92"/>
-      <c r="J26" s="92"/>
-      <c r="K26" s="92"/>
-      <c r="L26" s="92"/>
-      <c r="M26" s="92"/>
-      <c r="N26" s="92"/>
-      <c r="O26" s="92"/>
-      <c r="P26" s="92"/>
-      <c r="Q26" s="92"/>
-    </row>
-    <row r="27" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="92"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="92"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="92"/>
-      <c r="I27" s="92"/>
-      <c r="J27" s="92"/>
-      <c r="K27" s="92"/>
-      <c r="L27" s="92"/>
-      <c r="M27" s="92"/>
-      <c r="N27" s="92"/>
-      <c r="O27" s="92"/>
-      <c r="P27" s="92"/>
-      <c r="Q27" s="92"/>
-    </row>
-    <row r="28" spans="1:54" s="76" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="93" t="s">
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+    </row>
+    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A27" s="82"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="82"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+    </row>
+    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A28" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="93"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="93"/>
-      <c r="O28" s="93"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="93"/>
-    </row>
-    <row r="29" spans="1:54" s="76" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="94" t="s">
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+    </row>
+    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A29" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="94"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="94"/>
-      <c r="E29" s="94"/>
-      <c r="F29" s="94"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94"/>
-      <c r="M29" s="94"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="94"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="94"/>
-    </row>
-    <row r="30" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="33" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="34" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="35" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="36" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="40" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="41" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="42" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="43" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="45" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="46" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="47" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="48" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="49" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="50" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="51" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="52" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="53" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="54" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="55" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="56" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="57" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="58" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="59" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="60" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="61" s="77" customFormat="1" x14ac:dyDescent="0.3"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="84"/>
+    </row>
+    <row r="33" customFormat="1"/>
+    <row r="34" customFormat="1"/>
+    <row r="35" customFormat="1"/>
+    <row r="36" customFormat="1"/>
+    <row r="37" customFormat="1"/>
+    <row r="38" customFormat="1"/>
+    <row r="39" customFormat="1"/>
+    <row r="40" customFormat="1"/>
+    <row r="41" customFormat="1"/>
+    <row r="42" customFormat="1"/>
+    <row r="43" customFormat="1"/>
+    <row r="44" customFormat="1"/>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
+    <row r="47" customFormat="1"/>
+    <row r="48" customFormat="1"/>
+    <row r="49" customFormat="1"/>
+    <row r="50" customFormat="1"/>
+    <row r="51" customFormat="1"/>
+    <row r="52" customFormat="1"/>
+    <row r="53" customFormat="1"/>
+    <row r="54" customFormat="1"/>
+    <row r="55" customFormat="1"/>
+    <row r="56" customFormat="1"/>
+    <row r="57" customFormat="1"/>
+    <row r="58" customFormat="1"/>
+    <row r="59" customFormat="1"/>
+    <row r="60" customFormat="1"/>
+    <row r="61" customFormat="1"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A25:Q25"/>
+    <mergeCell ref="A26:Q26"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="A29:Q29"/>
     <mergeCell ref="A24:Q24"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="AC1:BB1"/>
     <mergeCell ref="A21:Q21"/>
     <mergeCell ref="A22:Q22"/>
     <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A25:Q25"/>
-    <mergeCell ref="A26:Q26"/>
-    <mergeCell ref="A27:Q27"/>
-    <mergeCell ref="A28:Q28"/>
-    <mergeCell ref="A29:Q29"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4645,26 +4581,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.125" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9.125" style="3"/>
+    <col min="1" max="1" width="30.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" customFormat="1" ht="15" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="57.6">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4681,11 +4617,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" thickBot="1">
       <c r="A3" s="3">
         <v>13</v>
       </c>
-      <c r="B3" s="86">
+      <c r="B3" s="68">
         <v>14</v>
       </c>
       <c r="C3" s="5">
@@ -4701,466 +4637,458 @@
         <v>13.378781688359696</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:5" ht="15" thickBot="1">
+      <c r="A5" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="64" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="84"/>
-    </row>
-    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="86">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1">
+      <c r="A7" s="68">
         <v>28</v>
       </c>
-      <c r="B7" s="80">
+      <c r="B7" s="65">
         <v>11932239</v>
       </c>
-      <c r="C7" s="86">
+      <c r="C7" s="68">
         <v>23</v>
       </c>
-      <c r="D7" s="83">
+      <c r="D7" s="66">
         <v>1007829.3084223459</v>
       </c>
-      <c r="E7" s="85"/>
-    </row>
-    <row r="8" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="81"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="E7" s="67"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-    </row>
-    <row r="11" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:5" s="9" customFormat="1">
+      <c r="A11" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="1:5" s="9" customFormat="1">
+      <c r="A12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:5" s="9" customFormat="1">
+      <c r="A13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:5" s="9" customFormat="1" ht="15" thickBot="1">
+      <c r="A14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:5" s="9" customFormat="1">
+      <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="22"/>
-    </row>
-    <row r="16" spans="1:5" s="10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="24">
+    </row>
+    <row r="16" spans="1:5" s="9" customFormat="1" ht="15" thickBot="1">
+      <c r="A16" s="18">
         <v>24</v>
       </c>
-      <c r="C16" s="21"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:5" ht="15" thickBot="1">
+      <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="9"/>
-      <c r="B22" s="14" t="s">
+    <row r="22" spans="1:5" ht="15" thickBot="1">
+      <c r="A22"/>
+      <c r="B22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="12">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-    </row>
-    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="41" t="s">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1">
+      <c r="A27" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:5" ht="15" thickBot="1">
+      <c r="A28" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="12">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="12" t="s">
+    <row r="30" spans="1:5" ht="15" thickBot="1">
+      <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-    </row>
-    <row r="31" spans="1:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="A31" s="27" t="s">
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+    </row>
+    <row r="31" spans="1:5" ht="28.8">
+      <c r="A31" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="E31" s="30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="26">
+    <row r="32" spans="1:5">
+      <c r="A32" s="20">
         <v>1997</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="24">
         <v>3826373</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="27">
         <v>260000</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="26">
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="20">
         <v>1998</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="24">
         <v>3879450</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="27">
         <v>311000</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="24">
         <f t="shared" ref="D33:D41" si="0">C33-(B33-B32)</f>
         <v>257923</v>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="31">
         <f>D33/B33</f>
         <v>6.6484424338501588E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="26">
+    <row r="34" spans="1:5">
+      <c r="A34" s="20">
         <v>1999</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="24">
         <v>4152433</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="27">
         <v>394000</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="24">
         <f t="shared" si="0"/>
         <v>121017</v>
       </c>
-      <c r="E34" s="38">
+      <c r="E34" s="31">
         <f t="shared" ref="E34:E42" si="1">D34/B34</f>
         <v>2.9143636995467476E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="26">
+    <row r="35" spans="1:5">
+      <c r="A35" s="20">
         <v>2000</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="24">
         <v>4346068</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="27">
         <v>490000</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="24">
         <f t="shared" si="0"/>
         <v>296365</v>
       </c>
-      <c r="E35" s="38">
+      <c r="E35" s="31">
         <f t="shared" si="1"/>
         <v>6.8191523924614153E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="26">
+    <row r="36" spans="1:5">
+      <c r="A36" s="20">
         <v>2001</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="24">
         <v>4903056</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="27">
         <v>577000</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="24">
         <f t="shared" si="0"/>
         <v>20012</v>
       </c>
-      <c r="E36" s="38">
+      <c r="E36" s="31">
         <f t="shared" si="1"/>
         <v>4.0815360868813244E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="26">
+    <row r="37" spans="1:5">
+      <c r="A37" s="20">
         <v>2002</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="24">
         <v>5004156</v>
       </c>
-      <c r="C37" s="33">
+      <c r="C37" s="27">
         <v>640000</v>
       </c>
-      <c r="D37" s="35">
+      <c r="D37" s="24">
         <f t="shared" si="0"/>
         <v>538900</v>
       </c>
-      <c r="E37" s="38">
+      <c r="E37" s="31">
         <f t="shared" si="1"/>
         <v>0.10769048766665149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="26">
+    <row r="38" spans="1:5">
+      <c r="A38" s="20">
         <v>2003</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="24">
         <v>5370035</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="27">
         <v>683000</v>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="24">
         <f t="shared" si="0"/>
         <v>317121</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="31">
         <f t="shared" si="1"/>
         <v>5.9053805049687755E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="26">
+    <row r="39" spans="1:5">
+      <c r="A39" s="20">
         <v>2004</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="24">
         <v>5780870</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="27">
         <v>750000</v>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="24">
         <f t="shared" si="0"/>
         <v>339165</v>
       </c>
-      <c r="E39" s="38">
+      <c r="E39" s="31">
         <f t="shared" si="1"/>
         <v>5.8670234757052138E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="26">
+    <row r="40" spans="1:5">
+      <c r="A40" s="20">
         <v>2005</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="24">
         <v>6227146</v>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="27">
         <v>831000</v>
       </c>
-      <c r="D40" s="35">
+      <c r="D40" s="24">
         <f t="shared" si="0"/>
         <v>384724</v>
       </c>
-      <c r="E40" s="38">
+      <c r="E40" s="31">
         <f t="shared" si="1"/>
         <v>6.1781753631599455E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="26">
+    <row r="41" spans="1:5">
+      <c r="A41" s="20">
         <v>2006</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="24">
         <v>6678958</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="27">
         <v>892000</v>
       </c>
-      <c r="D41" s="35">
+      <c r="D41" s="24">
         <f t="shared" si="0"/>
         <v>440188</v>
       </c>
-      <c r="E41" s="38">
+      <c r="E41" s="31">
         <f t="shared" si="1"/>
         <v>6.5906687839630079E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="31">
+    <row r="42" spans="1:5" ht="15" thickBot="1">
+      <c r="A42" s="25">
         <v>2007</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="23">
         <v>7138476</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="22">
         <v>885000</v>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="24">
         <f>C42-(B42-B41)</f>
         <v>425482</v>
       </c>
-      <c r="E42" s="38">
+      <c r="E42" s="31">
         <f t="shared" si="1"/>
         <v>5.9604038733197397E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="34">
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="28">
         <f>AVERAGE(E33:E42)</f>
         <v>5.8060812902328285E-2</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-    </row>
-    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="1:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="A47" s="44" t="s">
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:5" ht="15" thickBot="1">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:5" ht="28.8">
+      <c r="A47" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="43">
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:5" ht="15" thickBot="1">
+      <c r="A48" s="35">
         <f>1/A45</f>
         <v>17.22332068760786</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
     </row>
   </sheetData>
   <phoneticPr fontId="38" type="noConversion"/>
@@ -5174,681 +5102,681 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD149825-14BA-415D-91AD-354F00EEF420}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="88" customWidth="1"/>
-    <col min="2" max="2" width="11.125" style="88" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="88" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" style="88" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="88" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="88" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.125" style="88" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.75" style="88"/>
+    <col min="1" max="1" width="19.109375" style="70" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.44140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.77734375" style="70"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="70" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+    <row r="2" spans="1:9">
+      <c r="B2" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="88" t="s">
+      <c r="D2" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="G2" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="H2" s="88" t="s">
+      <c r="H2" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="88" t="s">
+      <c r="I2" s="70" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="88" t="s">
+    <row r="3" spans="1:9">
+      <c r="B3" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="88">
+      <c r="C3" s="70">
         <v>84650.742266925648</v>
       </c>
-      <c r="D3" s="88">
+      <c r="D3" s="70">
         <v>25214.586997392125</v>
       </c>
-      <c r="E3" s="88">
+      <c r="E3" s="70">
         <v>8072982.1194173032</v>
       </c>
-      <c r="F3" s="88">
+      <c r="F3" s="70">
         <v>4633956.5131107848</v>
       </c>
-      <c r="G3" s="88">
+      <c r="G3" s="70">
         <v>477958.89831224794</v>
       </c>
-      <c r="H3" s="88">
+      <c r="H3" s="70">
         <v>1315953.270937951</v>
       </c>
-      <c r="I3" s="88">
+      <c r="I3" s="70">
         <v>7728.5710293009906</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="88" t="s">
+    <row r="4" spans="1:9">
+      <c r="B4" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="88">
+      <c r="C4" s="70">
         <v>34802.257733074344</v>
       </c>
-      <c r="D4" s="88">
+      <c r="D4" s="70">
         <v>10314.28274882044</v>
       </c>
-      <c r="E4" s="88">
+      <c r="E4" s="70">
         <v>3302335.2797511155</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="70">
         <v>1895566.9480886636</v>
       </c>
-      <c r="G4" s="88">
+      <c r="G4" s="70">
         <v>195513.93881712668</v>
       </c>
-      <c r="H4" s="88">
+      <c r="H4" s="70">
         <v>538304.04289758822</v>
       </c>
-      <c r="I4" s="88">
+      <c r="I4" s="70">
         <v>3161.4504274369956</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="88" t="s">
+    <row r="5" spans="1:9">
+      <c r="B5" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="88">
+      <c r="C5" s="70">
         <v>0</v>
       </c>
-      <c r="D5" s="88">
+      <c r="D5" s="70">
         <v>0</v>
       </c>
-      <c r="E5" s="88">
+      <c r="E5" s="70">
         <v>0</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="70">
         <v>822</v>
       </c>
-      <c r="G5" s="88">
+      <c r="G5" s="70">
         <v>0</v>
       </c>
-      <c r="H5" s="88">
+      <c r="H5" s="70">
         <v>0</v>
       </c>
-      <c r="I5" s="88">
+      <c r="I5" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="88" t="s">
+    <row r="6" spans="1:9">
+      <c r="B6" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="88">
+      <c r="C6" s="70">
         <v>1046.875</v>
       </c>
-      <c r="D6" s="88">
+      <c r="D6" s="70">
         <v>0</v>
       </c>
-      <c r="E6" s="88">
+      <c r="E6" s="70">
         <v>0</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="70">
         <v>669.83333333333326</v>
       </c>
-      <c r="G6" s="88">
+      <c r="G6" s="70">
         <v>0</v>
       </c>
-      <c r="H6" s="88">
+      <c r="H6" s="70">
         <v>0</v>
       </c>
-      <c r="I6" s="88">
+      <c r="I6" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="88" t="s">
+    <row r="7" spans="1:9">
+      <c r="B7" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="88">
+      <c r="C7" s="70">
         <v>0</v>
       </c>
-      <c r="D7" s="88">
+      <c r="D7" s="70">
         <v>0</v>
       </c>
-      <c r="E7" s="88">
+      <c r="E7" s="70">
         <v>0.4823245691429916</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="70">
         <v>328</v>
       </c>
-      <c r="G7" s="88">
+      <c r="G7" s="70">
         <v>0</v>
       </c>
-      <c r="H7" s="88">
+      <c r="H7" s="70">
         <v>0.19292982765719663</v>
       </c>
-      <c r="I7" s="88">
+      <c r="I7" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="88" t="s">
+    <row r="8" spans="1:9">
+      <c r="B8" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="88">
+      <c r="C8" s="70">
         <v>0</v>
       </c>
-      <c r="D8" s="88">
+      <c r="D8" s="70">
         <v>0</v>
       </c>
-      <c r="E8" s="88">
+      <c r="E8" s="70">
         <v>272564</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="70">
         <v>0</v>
       </c>
-      <c r="G8" s="88">
+      <c r="G8" s="70">
         <v>0</v>
       </c>
-      <c r="H8" s="88">
+      <c r="H8" s="70">
         <v>0</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="88" t="s">
+    <row r="10" spans="1:9">
+      <c r="A10" s="70" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="88" t="s">
+    <row r="11" spans="1:9">
+      <c r="B11" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="88" t="s">
+      <c r="E11" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="88" t="s">
+      <c r="F11" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="88" t="s">
+      <c r="G11" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="88" t="s">
+      <c r="H11" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="88" t="s">
+      <c r="I11" s="70" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="88" t="s">
+    <row r="12" spans="1:9">
+      <c r="B12" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="88">
+      <c r="C12" s="70">
         <v>11965.956562995307</v>
       </c>
-      <c r="D12" s="88">
+      <c r="D12" s="70">
         <v>1366</v>
       </c>
-      <c r="E12" s="88">
+      <c r="E12" s="70">
         <v>14255.143043258835</v>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="70">
         <v>2664174.8230804084</v>
       </c>
-      <c r="G12" s="88">
+      <c r="G12" s="70">
         <v>0</v>
       </c>
-      <c r="H12" s="88">
+      <c r="H12" s="70">
         <v>94459.997166222995</v>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="88" t="s">
+    <row r="13" spans="1:9">
+      <c r="B13" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="88">
+      <c r="C13" s="70">
         <v>3543.0434370046937</v>
       </c>
-      <c r="D13" s="88">
+      <c r="D13" s="70">
         <v>0</v>
       </c>
-      <c r="E13" s="88">
+      <c r="E13" s="70">
         <v>4220.8569567411641</v>
       </c>
-      <c r="F13" s="88">
+      <c r="F13" s="70">
         <v>788845.17691959161</v>
       </c>
-      <c r="G13" s="88">
+      <c r="G13" s="70">
         <v>0</v>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="70">
         <v>27969.002833777009</v>
       </c>
-      <c r="I13" s="88">
+      <c r="I13" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="88" t="s">
+    <row r="14" spans="1:9">
+      <c r="B14" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="88">
+      <c r="C14" s="70">
         <v>0</v>
       </c>
-      <c r="D14" s="88">
+      <c r="D14" s="70">
         <v>0</v>
       </c>
-      <c r="E14" s="88">
+      <c r="E14" s="70">
         <v>0</v>
       </c>
-      <c r="F14" s="88">
+      <c r="F14" s="70">
         <v>36</v>
       </c>
-      <c r="G14" s="88">
+      <c r="G14" s="70">
         <v>0</v>
       </c>
-      <c r="H14" s="88">
+      <c r="H14" s="70">
         <v>0</v>
       </c>
-      <c r="I14" s="88">
+      <c r="I14" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="88" t="s">
+    <row r="15" spans="1:9">
+      <c r="B15" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="88">
+      <c r="C15" s="70">
         <v>87.5</v>
       </c>
-      <c r="D15" s="88">
+      <c r="D15" s="70">
         <v>0</v>
       </c>
-      <c r="E15" s="88">
+      <c r="E15" s="70">
         <v>0</v>
       </c>
-      <c r="F15" s="88">
+      <c r="F15" s="70">
         <v>127</v>
       </c>
-      <c r="G15" s="88">
+      <c r="G15" s="70">
         <v>0</v>
       </c>
-      <c r="H15" s="88">
+      <c r="H15" s="70">
         <v>0</v>
       </c>
-      <c r="I15" s="88">
+      <c r="I15" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="88" t="s">
+    <row r="16" spans="1:9">
+      <c r="B16" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="88">
+      <c r="C16" s="70">
         <v>0</v>
       </c>
-      <c r="D16" s="88">
+      <c r="D16" s="70">
         <v>0</v>
       </c>
-      <c r="E16" s="88">
+      <c r="E16" s="70">
         <v>2.1101699900005881</v>
       </c>
-      <c r="F16" s="88">
+      <c r="F16" s="70">
         <v>630.10013528615957</v>
       </c>
-      <c r="G16" s="88">
+      <c r="G16" s="70">
         <v>0</v>
       </c>
-      <c r="H16" s="88">
+      <c r="H16" s="70">
         <v>0.8440679960002353</v>
       </c>
-      <c r="I16" s="88">
+      <c r="I16" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="88" t="s">
+    <row r="17" spans="1:9">
+      <c r="B17" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="88">
+      <c r="C17" s="70">
         <v>0</v>
       </c>
-      <c r="D17" s="88">
+      <c r="D17" s="70">
         <v>0</v>
       </c>
-      <c r="E17" s="88">
+      <c r="E17" s="70">
         <v>2016445</v>
       </c>
-      <c r="F17" s="88">
+      <c r="F17" s="70">
         <v>0</v>
       </c>
-      <c r="G17" s="88">
+      <c r="G17" s="70">
         <v>0</v>
       </c>
-      <c r="H17" s="88">
+      <c r="H17" s="70">
         <v>0</v>
       </c>
-      <c r="I17" s="88">
+      <c r="I17" s="70">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="88" t="s">
+    <row r="20" spans="1:9">
+      <c r="A20" s="70" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="88">
+    <row r="22" spans="1:9">
+      <c r="B22" s="70">
         <v>2019</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="C22" s="71" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="88" t="s">
+    <row r="23" spans="1:9">
+      <c r="A23" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="88">
+      <c r="B23" s="70">
         <v>688548.12375329144</v>
       </c>
-      <c r="C23" s="90">
+      <c r="C23" s="72">
         <f>B23/E3</f>
         <v>8.5290430917365878E-2</v>
       </c>
-      <c r="D23" s="88">
+      <c r="D23" s="70">
         <f>1/C23</f>
         <v>11.724644713881862</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="88" t="s">
+    <row r="24" spans="1:9">
+      <c r="A24" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="88">
+      <c r="B24" s="70">
         <v>409171.81100616272</v>
       </c>
-      <c r="C24" s="90">
+      <c r="C24" s="72">
         <f>B24/F3</f>
         <v>8.8298586714937649E-2</v>
       </c>
-      <c r="D24" s="88">
+      <c r="D24" s="70">
         <f t="shared" ref="D24:D30" si="0">1/C24</f>
         <v>11.325209578137313</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="88" t="s">
+    <row r="25" spans="1:9">
+      <c r="A25" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="88">
+      <c r="B25" s="70">
         <v>23570.553989311142</v>
       </c>
-      <c r="C25" s="90">
+      <c r="C25" s="72">
         <f>B25/C3</f>
         <v>0.27844474080318277</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="88" t="s">
+    <row r="26" spans="1:9">
+      <c r="A26" s="70" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="88">
+      <c r="B26" s="70">
         <v>3006.7960130674305</v>
       </c>
-      <c r="C26" s="90">
+      <c r="C26" s="72">
         <f>B26/I3</f>
         <v>0.38904941180819808</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="90"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="90"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="88" t="s">
+    <row r="27" spans="1:9">
+      <c r="C27" s="72"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="C28" s="72"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="88">
+      <c r="B29" s="70">
         <v>206.54622970105956</v>
       </c>
-      <c r="C29" s="90">
+      <c r="C29" s="72">
         <f>B29/E13</f>
         <v>4.8934667016180905E-2</v>
       </c>
-      <c r="D29" s="88">
+      <c r="D29" s="70">
         <f t="shared" si="0"/>
         <v>20.43541033331925</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="88" t="s">
+    <row r="30" spans="1:9">
+      <c r="A30" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="88">
+      <c r="B30" s="70">
         <v>56719.050638672627</v>
       </c>
-      <c r="C30" s="90">
+      <c r="C30" s="72">
         <f>B30/F13</f>
         <v>7.190137215538063E-2</v>
       </c>
-      <c r="D30" s="88">
+      <c r="D30" s="70">
         <f t="shared" si="0"/>
         <v>13.907940419258974</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="88" t="s">
+    <row r="31" spans="1:9">
+      <c r="A31" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="B31" s="88">
+      <c r="B31" s="70">
         <v>243.47183425946551</v>
       </c>
-      <c r="C31" s="90">
+      <c r="C31" s="72">
         <f>B31/C13</f>
         <v>6.8718275287445466E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="88" t="s">
+    <row r="32" spans="1:9">
+      <c r="A32" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="B32" s="88">
+      <c r="B32" s="70">
         <v>0</v>
       </c>
-      <c r="C32" s="90" t="e">
+      <c r="C32" s="72" t="e">
         <f>B32/I13</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="100" t="s">
+    <row r="34" spans="1:10">
+      <c r="A34" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="100"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="100"/>
-      <c r="B35" s="100">
+      <c r="B34" s="74"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="74"/>
+      <c r="B35" s="74">
         <v>2000</v>
       </c>
-      <c r="C35" s="100">
+      <c r="C35" s="74">
         <v>2005</v>
       </c>
-      <c r="D35" s="100">
+      <c r="D35" s="74">
         <v>2010</v>
       </c>
-      <c r="E35" s="100">
+      <c r="E35" s="74">
         <v>2015</v>
       </c>
-      <c r="F35" s="100">
+      <c r="F35" s="74">
         <v>2020</v>
       </c>
-      <c r="G35" s="100">
+      <c r="G35" s="74">
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="100" t="s">
+    <row r="36" spans="1:10">
+      <c r="A36" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="102">
+      <c r="B36" s="76">
         <v>8.4</v>
       </c>
-      <c r="C36" s="102">
+      <c r="C36" s="76">
         <v>11.2</v>
       </c>
-      <c r="D36" s="102">
+      <c r="D36" s="76">
         <v>13.4</v>
       </c>
-      <c r="E36" s="102">
+      <c r="E36" s="76">
         <v>14.8</v>
       </c>
-      <c r="F36" s="102">
+      <c r="F36" s="76">
         <v>15.3</v>
       </c>
-      <c r="G36" s="102">
+      <c r="G36" s="76">
         <v>15.6</v>
       </c>
-      <c r="I36" s="100" t="s">
+      <c r="I36" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="J36" s="101">
+      <c r="J36" s="75">
         <f>AVERAGE(F36:F37)</f>
         <v>15.4</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="100" t="s">
+    <row r="37" spans="1:10">
+      <c r="A37" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="B37" s="102">
+      <c r="B37" s="76">
         <v>8.1999999999999993</v>
       </c>
-      <c r="C37" s="102">
+      <c r="C37" s="76">
         <v>10.199999999999999</v>
       </c>
-      <c r="D37" s="102">
+      <c r="D37" s="76">
         <v>12</v>
       </c>
-      <c r="E37" s="102">
+      <c r="E37" s="76">
         <v>14.9</v>
       </c>
-      <c r="F37" s="102">
+      <c r="F37" s="76">
         <v>15.5</v>
       </c>
-      <c r="G37" s="102">
+      <c r="G37" s="76">
         <v>15.5</v>
       </c>
-      <c r="I37" s="101" t="s">
+      <c r="I37" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="75">
         <f>AVERAGE(F38:F39)</f>
         <v>16.8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="100" t="s">
+    <row r="38" spans="1:10">
+      <c r="A38" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="B38" s="102">
+      <c r="B38" s="76">
         <v>8</v>
       </c>
-      <c r="C38" s="102">
+      <c r="C38" s="76">
         <v>10.9</v>
       </c>
-      <c r="D38" s="102">
+      <c r="D38" s="76">
         <v>8</v>
       </c>
-      <c r="E38" s="102">
+      <c r="E38" s="76">
         <v>15.1</v>
       </c>
-      <c r="F38" s="102">
+      <c r="F38" s="76">
         <v>16.8</v>
       </c>
-      <c r="G38" s="102">
+      <c r="G38" s="76">
         <v>17.3</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="100" t="s">
+    <row r="39" spans="1:10">
+      <c r="A39" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="102">
+      <c r="B39" s="76">
         <v>9.9</v>
       </c>
-      <c r="C39" s="102">
+      <c r="C39" s="76">
         <v>11.9</v>
       </c>
-      <c r="D39" s="102">
+      <c r="D39" s="76">
         <v>15.6</v>
       </c>
-      <c r="E39" s="102">
+      <c r="E39" s="76">
         <v>17.100000000000001</v>
       </c>
-      <c r="F39" s="102">
+      <c r="F39" s="76">
         <v>16.8</v>
       </c>
-      <c r="G39" s="102">
+      <c r="G39" s="76">
         <v>18.2</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="100" t="s">
+    <row r="40" spans="1:10">
+      <c r="A40" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="B40" s="102">
+      <c r="B40" s="76">
         <v>8.3000000000000007</v>
       </c>
-      <c r="C40" s="102">
+      <c r="C40" s="76">
         <v>11.05</v>
       </c>
-      <c r="D40" s="102">
+      <c r="D40" s="76">
         <v>13.25</v>
       </c>
-      <c r="E40" s="102">
+      <c r="E40" s="76">
         <v>14.87</v>
       </c>
-      <c r="F40" s="102">
+      <c r="F40" s="76">
         <v>15.59</v>
       </c>
-      <c r="G40" s="102">
+      <c r="G40" s="76">
         <v>16</v>
       </c>
     </row>
@@ -5865,68 +5793,68 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:3" ht="28.8">
+      <c r="A1" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="99">
+      <c r="B2" s="73">
         <f>'SK calcs'!J36</f>
         <v>15.4</v>
       </c>
-      <c r="C2" s="99">
+      <c r="C2" s="73">
         <f t="shared" ref="C2:C7" si="0">B2</f>
         <v>15.4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="99">
+      <c r="B3" s="73">
         <f>'SK calcs'!J37</f>
         <v>16.8</v>
       </c>
-      <c r="C3" s="99">
+      <c r="C3" s="73">
         <f t="shared" si="0"/>
         <v>16.8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="37">
         <f>ROUND(Data!A16,0)</f>
         <v>24</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="37">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="78">
+      <c r="B5">
         <f>ROUND(Data!C22,0)</f>
         <v>34</v>
       </c>
@@ -5935,11 +5863,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6">
         <f>ROUND(Data!C28,0)</f>
         <v>33</v>
       </c>
@@ -5948,11 +5876,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7">
         <f>ROUND(Data!A48,0)</f>
         <v>17</v>
       </c>
@@ -5968,9 +5896,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6118,26 +6049,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B68363-87CD-464E-8916-DF6FCE3B5AB7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6161,9 +6081,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B68363-87CD-464E-8916-DF6FCE3B5AB7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
+++ b/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\AVL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2026\01.EPS\01.EI\01.메일\260108_메일회신\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF34157-7591-4A0D-850C-5B993E103A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1944F64F-AD81-4996-A4B5-75E70CAE79BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32595" yWindow="3795" windowWidth="20145" windowHeight="11235" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="132">
   <si>
     <t>Car Avg Lifetime, years (Page 22, Table 7)</t>
   </si>
@@ -463,27 +463,39 @@
     <t>Source: Decommissioning cycles by year (https://v.daum.net/v/E5WSO03fTV)</t>
     <phoneticPr fontId="38" type="noConversion"/>
   </si>
+  <si>
+    <t>Passenger</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDV+HDV</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>freight</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="9">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="###0.00_)"/>
-    <numFmt numFmtId="165" formatCode="\(\R\)General"/>
-    <numFmt numFmtId="166" formatCode="\(\R\)\ ###0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="\(\R\)0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0_)"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="###0.00_)"/>
+    <numFmt numFmtId="178" formatCode="\(\R\)General"/>
+    <numFmt numFmtId="179" formatCode="\(\R\)\ ###0"/>
+    <numFmt numFmtId="180" formatCode="0.0"/>
+    <numFmt numFmtId="181" formatCode="\(\R\)0.0"/>
+    <numFmt numFmtId="182" formatCode="#,##0_)"/>
+    <numFmt numFmtId="183" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="184" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -491,7 +503,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -499,7 +511,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -507,14 +519,14 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -522,7 +534,7 @@
       <u/>
       <sz val="10"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -537,7 +549,7 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -554,14 +566,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -569,7 +581,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Cambria"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -577,7 +589,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -585,7 +597,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -593,35 +605,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -629,7 +641,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -637,14 +649,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -652,14 +664,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -667,21 +679,21 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -738,13 +750,13 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -752,7 +764,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1330,7 +1342,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10">
@@ -1387,10 +1399,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="10">
+    <xf numFmtId="182" fontId="33" fillId="0" borderId="10">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1495,10 +1507,10 @@
     <xf numFmtId="1" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,7 +1522,7 @@
     <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1530,21 +1542,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1567,16 +1579,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="24" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="184" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1589,80 +1610,71 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="63">
-    <cellStyle name="20% - Accent1" xfId="35" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="39" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="43" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="47" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="51" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="55" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="36" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="40" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="44" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="48" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="52" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="56" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="37" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="41" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="45" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="49" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="53" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="57" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="34" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="38" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="42" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="46" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="50" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="54" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색1" xfId="35" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="39" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="43" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="47" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="51" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="55" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="36" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="40" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="44" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="48" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="52" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="56" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="37" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="41" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="45" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="49" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="53" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="57" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Body: normal cell" xfId="3" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Calculation" xfId="27" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="29" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="62" builtinId="3"/>
     <cellStyle name="Data" xfId="14" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
     <cellStyle name="Data no deci" xfId="61" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="Explanatory Text" xfId="32" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="11" builtinId="9" customBuiltin="1"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="9" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="Footnotes: all except top row" xfId="12" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
     <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="Good" xfId="22" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Header: bottom row" xfId="2" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="Header: top rows" xfId="4" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="19" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="20" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="21" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Hed Side" xfId="15" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
     <cellStyle name="Hed Side Regular" xfId="60" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="Hed Top" xfId="59" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="Input" xfId="25" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="28" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="31" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="26" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Percent" xfId="16" builtinId="5"/>
     <cellStyle name="Section Break" xfId="8" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="Section Break: parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="Table title" xfId="13" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="Title" xfId="17" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Title-2" xfId="58" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="Total" xfId="33" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="30" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="34" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="38" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="42" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="46" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="50" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="54" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="30" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="27" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="23" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="31" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="백분율" xfId="16" builtinId="5"/>
+    <cellStyle name="보통" xfId="24" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="32" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="29" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="쉼표" xfId="62" builtinId="3"/>
+    <cellStyle name="연결된 셀" xfId="28" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="열어 본 하이퍼링크" xfId="11" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="33" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="25" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="17" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="18" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="19" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="20" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="21" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="22" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="26" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1995,17 +2007,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="132.21875" customWidth="1"/>
+    <col min="2" max="2" width="132.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
@@ -2013,233 +2025,232 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="9">
         <v>2006</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
         <v>2016</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="9">
         <v>2015</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="2:2"/>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="2:2">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="9">
         <v>2019</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="9">
         <v>2013</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" s="9">
         <v>2009</v>
       </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>99</v>
       </c>
@@ -2260,72 +2271,72 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB61"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="27" width="7.77734375" customWidth="1"/>
-    <col min="28" max="28" width="7.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.375" customWidth="1"/>
+    <col min="2" max="27" width="7.75" customWidth="1"/>
+    <col min="28" max="28" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="79"/>
-      <c r="AD1" s="79"/>
-      <c r="AE1" s="79"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="79"/>
-      <c r="AH1" s="79"/>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="79"/>
-      <c r="AL1" s="79"/>
-      <c r="AM1" s="79"/>
-      <c r="AN1" s="79"/>
-      <c r="AO1" s="79"/>
-      <c r="AP1" s="79"/>
-      <c r="AQ1" s="79"/>
-      <c r="AR1" s="79"/>
-      <c r="AS1" s="79"/>
-      <c r="AT1" s="79"/>
-      <c r="AU1" s="79"/>
-      <c r="AV1" s="79"/>
-      <c r="AW1" s="79"/>
-      <c r="AX1" s="79"/>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
-      <c r="BA1" s="79"/>
-      <c r="BB1" s="79"/>
-    </row>
-    <row r="2" spans="1:54" ht="16.5" customHeight="1">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="81"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+      <c r="AI1" s="82"/>
+      <c r="AJ1" s="82"/>
+      <c r="AK1" s="82"/>
+      <c r="AL1" s="82"/>
+      <c r="AM1" s="82"/>
+      <c r="AN1" s="82"/>
+      <c r="AO1" s="82"/>
+      <c r="AP1" s="82"/>
+      <c r="AQ1" s="82"/>
+      <c r="AR1" s="82"/>
+      <c r="AS1" s="82"/>
+      <c r="AT1" s="82"/>
+      <c r="AU1" s="82"/>
+      <c r="AV1" s="82"/>
+      <c r="AW1" s="82"/>
+      <c r="AX1" s="82"/>
+      <c r="AY1" s="82"/>
+      <c r="AZ1" s="82"/>
+      <c r="BA1" s="82"/>
+      <c r="BB1" s="82"/>
+    </row>
+    <row r="2" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38"/>
       <c r="B2" s="39">
         <v>1980</v>
@@ -2435,7 +2446,7 @@
       <c r="BA2" s="45"/>
       <c r="BB2" s="46"/>
     </row>
-    <row r="3" spans="1:54" ht="16.5" customHeight="1">
+    <row r="3" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
@@ -2547,7 +2558,7 @@
       <c r="BA3" s="48"/>
       <c r="BB3" s="48"/>
     </row>
-    <row r="4" spans="1:54" ht="16.5" customHeight="1">
+    <row r="4" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50" t="s">
         <v>67</v>
       </c>
@@ -2659,7 +2670,7 @@
       <c r="BA4" s="52"/>
       <c r="BB4" s="52"/>
     </row>
-    <row r="5" spans="1:54" ht="16.5" customHeight="1">
+    <row r="5" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>68</v>
       </c>
@@ -2771,7 +2782,7 @@
       <c r="BA5" s="52"/>
       <c r="BB5" s="52"/>
     </row>
-    <row r="6" spans="1:54" ht="16.5" customHeight="1">
+    <row r="6" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50" t="s">
         <v>69</v>
       </c>
@@ -2883,7 +2894,7 @@
       <c r="BA6" s="52"/>
       <c r="BB6" s="52"/>
     </row>
-    <row r="7" spans="1:54" ht="16.5" customHeight="1">
+    <row r="7" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
         <v>70</v>
       </c>
@@ -2995,7 +3006,7 @@
       <c r="BA7" s="52"/>
       <c r="BB7" s="52"/>
     </row>
-    <row r="8" spans="1:54" ht="16.5" customHeight="1">
+    <row r="8" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
         <v>71</v>
       </c>
@@ -3107,7 +3118,7 @@
       <c r="BA8" s="52"/>
       <c r="BB8" s="52"/>
     </row>
-    <row r="9" spans="1:54" ht="16.5" customHeight="1">
+    <row r="9" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="53" t="s">
         <v>72</v>
       </c>
@@ -3165,7 +3176,7 @@
       <c r="BA9" s="54"/>
       <c r="BB9" s="54"/>
     </row>
-    <row r="10" spans="1:54" ht="16.5" customHeight="1">
+    <row r="10" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50" t="s">
         <v>67</v>
       </c>
@@ -3279,7 +3290,7 @@
       <c r="BA10" s="56"/>
       <c r="BB10" s="56"/>
     </row>
-    <row r="11" spans="1:54" ht="16.5" customHeight="1">
+    <row r="11" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50" t="s">
         <v>68</v>
       </c>
@@ -3391,7 +3402,7 @@
       <c r="BA11" s="56"/>
       <c r="BB11" s="56"/>
     </row>
-    <row r="12" spans="1:54" ht="16.5" customHeight="1">
+    <row r="12" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
         <v>69</v>
       </c>
@@ -3503,7 +3514,7 @@
       <c r="BA12" s="56"/>
       <c r="BB12" s="56"/>
     </row>
-    <row r="13" spans="1:54" ht="16.5" customHeight="1">
+    <row r="13" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50" t="s">
         <v>70</v>
       </c>
@@ -3615,7 +3626,7 @@
       <c r="BA13" s="56"/>
       <c r="BB13" s="56"/>
     </row>
-    <row r="14" spans="1:54" ht="16.5" customHeight="1">
+    <row r="14" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50" t="s">
         <v>71</v>
       </c>
@@ -3727,7 +3738,7 @@
       <c r="BA14" s="56"/>
       <c r="BB14" s="56"/>
     </row>
-    <row r="15" spans="1:54" ht="16.5" customHeight="1">
+    <row r="15" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>73</v>
       </c>
@@ -3785,7 +3796,7 @@
       <c r="BA15" s="58"/>
       <c r="BB15" s="58"/>
     </row>
-    <row r="16" spans="1:54" ht="16.5" customHeight="1">
+    <row r="16" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50" t="s">
         <v>67</v>
       </c>
@@ -3897,7 +3908,7 @@
       <c r="BA16" s="59"/>
       <c r="BB16" s="59"/>
     </row>
-    <row r="17" spans="1:54" ht="16.5" customHeight="1">
+    <row r="17" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50" t="s">
         <v>68</v>
       </c>
@@ -4009,7 +4020,7 @@
       <c r="BA17" s="59"/>
       <c r="BB17" s="59"/>
     </row>
-    <row r="18" spans="1:54" ht="16.5" customHeight="1">
+    <row r="18" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50" t="s">
         <v>69</v>
       </c>
@@ -4121,7 +4132,7 @@
       <c r="BA18" s="59"/>
       <c r="BB18" s="59"/>
     </row>
-    <row r="19" spans="1:54" ht="16.5" customHeight="1">
+    <row r="19" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50" t="s">
         <v>70</v>
       </c>
@@ -4233,7 +4244,7 @@
       <c r="BA19" s="59"/>
       <c r="BB19" s="59"/>
     </row>
-    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1">
+    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="60" t="s">
         <v>71</v>
       </c>
@@ -4345,68 +4356,68 @@
       <c r="BA20" s="59"/>
       <c r="BB20" s="59"/>
     </row>
-    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A21" s="80" t="s">
+    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-    </row>
-    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A22" s="81"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-    </row>
-    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A23" s="81" t="s">
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+    </row>
+    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="84"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+    </row>
+    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="81"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="81"/>
-    </row>
-    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="B23" s="84"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="84"/>
+      <c r="Q23" s="84"/>
+    </row>
+    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="77" t="s">
         <v>76</v>
       </c>
@@ -4427,7 +4438,7 @@
       <c r="P24" s="77"/>
       <c r="Q24" s="77"/>
     </row>
-    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="77" t="s">
         <v>77</v>
       </c>
@@ -4448,130 +4459,130 @@
       <c r="P25" s="77"/>
       <c r="Q25" s="77"/>
     </row>
-    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A26" s="82" t="s">
+    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="82"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="82"/>
-      <c r="J26" s="82"/>
-      <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
-      <c r="M26" s="82"/>
-      <c r="N26" s="82"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="82"/>
-      <c r="Q26" s="82"/>
-    </row>
-    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A27" s="82"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="82"/>
-      <c r="H27" s="82"/>
-      <c r="I27" s="82"/>
-      <c r="J27" s="82"/>
-      <c r="K27" s="82"/>
-      <c r="L27" s="82"/>
-      <c r="M27" s="82"/>
-      <c r="N27" s="82"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="82"/>
-      <c r="Q27" s="82"/>
-    </row>
-    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A28" s="83" t="s">
+      <c r="B26" s="78"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
+      <c r="M26" s="78"/>
+      <c r="N26" s="78"/>
+      <c r="O26" s="78"/>
+      <c r="P26" s="78"/>
+      <c r="Q26" s="78"/>
+    </row>
+    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="78"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="78"/>
+      <c r="L27" s="78"/>
+      <c r="M27" s="78"/>
+      <c r="N27" s="78"/>
+      <c r="O27" s="78"/>
+      <c r="P27" s="78"/>
+      <c r="Q27" s="78"/>
+    </row>
+    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
-    </row>
-    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A29" s="84" t="s">
+      <c r="B28" s="79"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="79"/>
+      <c r="P28" s="79"/>
+      <c r="Q28" s="79"/>
+    </row>
+    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="84"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="84"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="84"/>
-      <c r="M29" s="84"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="84"/>
-      <c r="Q29" s="84"/>
-    </row>
-    <row r="33" customFormat="1"/>
-    <row r="34" customFormat="1"/>
-    <row r="35" customFormat="1"/>
-    <row r="36" customFormat="1"/>
-    <row r="37" customFormat="1"/>
-    <row r="38" customFormat="1"/>
-    <row r="39" customFormat="1"/>
-    <row r="40" customFormat="1"/>
-    <row r="41" customFormat="1"/>
-    <row r="42" customFormat="1"/>
-    <row r="43" customFormat="1"/>
-    <row r="44" customFormat="1"/>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
-    <row r="47" customFormat="1"/>
-    <row r="48" customFormat="1"/>
-    <row r="49" customFormat="1"/>
-    <row r="50" customFormat="1"/>
-    <row r="51" customFormat="1"/>
-    <row r="52" customFormat="1"/>
-    <row r="53" customFormat="1"/>
-    <row r="54" customFormat="1"/>
-    <row r="55" customFormat="1"/>
-    <row r="56" customFormat="1"/>
-    <row r="57" customFormat="1"/>
-    <row r="58" customFormat="1"/>
-    <row r="59" customFormat="1"/>
-    <row r="60" customFormat="1"/>
-    <row r="61" customFormat="1"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="80"/>
+    </row>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A25:Q25"/>
-    <mergeCell ref="A26:Q26"/>
-    <mergeCell ref="A27:Q27"/>
-    <mergeCell ref="A28:Q28"/>
-    <mergeCell ref="A29:Q29"/>
     <mergeCell ref="A24:Q24"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="AC1:BB1"/>
     <mergeCell ref="A21:Q21"/>
     <mergeCell ref="A22:Q22"/>
     <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A25:Q25"/>
+    <mergeCell ref="A26:Q26"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="A29:Q29"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4581,17 +4592,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" width="30.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.125" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" customFormat="1" ht="15" thickBot="1">
+    <row r="1" spans="1:5" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -4600,7 +4611,7 @@
       <c r="D1" s="33"/>
       <c r="E1" s="33"/>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="57.6">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4617,7 +4628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1">
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>13</v>
       </c>
@@ -4637,12 +4648,12 @@
         <v>13.378781688359696</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1">
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>59</v>
       </c>
@@ -4657,7 +4668,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1">
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="68">
         <v>28</v>
       </c>
@@ -4672,7 +4683,7 @@
       </c>
       <c r="E7" s="67"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>56</v>
       </c>
@@ -4681,14 +4692,14 @@
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:5" s="9" customFormat="1">
+    <row r="11" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:5" s="9" customFormat="1">
+    <row r="12" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>34</v>
       </c>
@@ -4696,7 +4707,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="9" customFormat="1">
+    <row r="13" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>36</v>
       </c>
@@ -4704,7 +4715,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="9" customFormat="1" ht="15" thickBot="1">
+    <row r="14" spans="1:5" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>38</v>
       </c>
@@ -4712,17 +4723,17 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="9" customFormat="1">
+    <row r="15" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="9" customFormat="1" ht="15" thickBot="1">
+    <row r="16" spans="1:5" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="18">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>21</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="D18" s="34"/>
       <c r="E18" s="34"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>10</v>
       </c>
@@ -4742,7 +4753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -4753,7 +4764,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1">
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4764,7 +4775,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1">
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22"/>
       <c r="B22" s="11" t="s">
         <v>26</v>
@@ -4773,17 +4784,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>13</v>
       </c>
@@ -4792,7 +4803,7 @@
       <c r="D26" s="34"/>
       <c r="E26" s="34"/>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1">
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
         <v>10</v>
       </c>
@@ -4803,7 +4814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1">
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -4814,7 +4825,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1">
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
@@ -4823,7 +4834,7 @@
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>43</v>
       </c>
@@ -4840,7 +4851,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="20">
         <v>1997</v>
       </c>
@@ -4853,7 +4864,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="20">
         <v>1998</v>
       </c>
@@ -4872,7 +4883,7 @@
         <v>6.6484424338501588E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>1999</v>
       </c>
@@ -4891,7 +4902,7 @@
         <v>2.9143636995467476E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="20">
         <v>2000</v>
       </c>
@@ -4910,7 +4921,7 @@
         <v>6.8191523924614153E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="20">
         <v>2001</v>
       </c>
@@ -4929,7 +4940,7 @@
         <v>4.0815360868813244E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="20">
         <v>2002</v>
       </c>
@@ -4948,7 +4959,7 @@
         <v>0.10769048766665149</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="20">
         <v>2003</v>
       </c>
@@ -4967,7 +4978,7 @@
         <v>5.9053805049687755E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="20">
         <v>2004</v>
       </c>
@@ -4986,7 +4997,7 @@
         <v>5.8670234757052138E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="20">
         <v>2005</v>
       </c>
@@ -5005,7 +5016,7 @@
         <v>6.1781753631599455E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="20">
         <v>2006</v>
       </c>
@@ -5024,7 +5035,7 @@
         <v>6.5906687839630079E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1">
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="25">
         <v>2007</v>
       </c>
@@ -5043,14 +5054,14 @@
         <v>5.9604038733197397E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -5058,7 +5069,7 @@
       <c r="C44"/>
       <c r="D44"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="28">
         <f>AVERAGE(E33:E42)</f>
         <v>5.8060812902328285E-2</v>
@@ -5067,13 +5078,13 @@
       <c r="C45"/>
       <c r="D45"/>
     </row>
-    <row r="46" spans="1:5" ht="15" thickBot="1">
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
       <c r="D46"/>
     </row>
-    <row r="47" spans="1:5" ht="28.8">
+    <row r="47" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" s="36" t="s">
         <v>48</v>
       </c>
@@ -5081,7 +5092,7 @@
       <c r="C47"/>
       <c r="D47"/>
     </row>
-    <row r="48" spans="1:5" ht="15" thickBot="1">
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="35">
         <f>1/A45</f>
         <v>17.22332068760786</v>
@@ -5101,25 +5112,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD149825-14BA-415D-91AD-354F00EEF420}">
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="70" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.44140625" style="70" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="70" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="70"/>
+    <col min="1" max="1" width="19.125" style="70" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" style="70" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="70" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" style="70" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.75" style="70"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="70" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="70" t="s">
         <v>101</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="70" t="s">
         <v>52</v>
       </c>
@@ -5171,7 +5182,7 @@
         <v>7728.5710293009906</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="70" t="s">
         <v>55</v>
       </c>
@@ -5197,7 +5208,7 @@
         <v>3161.4504274369956</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="70" t="s">
         <v>56</v>
       </c>
@@ -5223,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="70" t="s">
         <v>21</v>
       </c>
@@ -5249,7 +5260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="70" t="s">
         <v>13</v>
       </c>
@@ -5275,7 +5286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="70" t="s">
         <v>58</v>
       </c>
@@ -5301,12 +5312,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="70" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="70" t="s">
         <v>101</v>
       </c>
@@ -5332,7 +5343,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="70" t="s">
         <v>52</v>
       </c>
@@ -5358,7 +5369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="70" t="s">
         <v>55</v>
       </c>
@@ -5384,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="70" t="s">
         <v>56</v>
       </c>
@@ -5410,7 +5421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="70" t="s">
         <v>21</v>
       </c>
@@ -5436,7 +5447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="70" t="s">
         <v>13</v>
       </c>
@@ -5462,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" s="70" t="s">
         <v>58</v>
       </c>
@@ -5488,12 +5499,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="70" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B22" s="70">
         <v>2019</v>
       </c>
@@ -5501,7 +5512,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="70" t="s">
         <v>111</v>
       </c>
@@ -5517,7 +5528,7 @@
         <v>11.724644713881862</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="70" t="s">
         <v>112</v>
       </c>
@@ -5533,7 +5544,7 @@
         <v>11.325209578137313</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="70" t="s">
         <v>113</v>
       </c>
@@ -5545,7 +5556,7 @@
         <v>0.27844474080318277</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="70" t="s">
         <v>114</v>
       </c>
@@ -5557,13 +5568,13 @@
         <v>0.38904941180819808</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C27" s="72"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C28" s="72"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="70" t="s">
         <v>115</v>
       </c>
@@ -5579,7 +5590,7 @@
         <v>20.43541033331925</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="70" t="s">
         <v>116</v>
       </c>
@@ -5595,7 +5606,7 @@
         <v>13.907940419258974</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="70" t="s">
         <v>117</v>
       </c>
@@ -5607,7 +5618,7 @@
         <v>6.8718275287445466E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="70" t="s">
         <v>118</v>
       </c>
@@ -5619,7 +5630,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="74" t="s">
         <v>128</v>
       </c>
@@ -5630,7 +5641,7 @@
       <c r="F34" s="74"/>
       <c r="G34" s="74"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="74"/>
       <c r="B35" s="74">
         <v>2000</v>
@@ -5650,8 +5661,10 @@
       <c r="G35" s="74">
         <v>2021</v>
       </c>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="74" t="s">
         <v>121</v>
       </c>
@@ -5673,15 +5686,15 @@
       <c r="G36" s="76">
         <v>15.6</v>
       </c>
+      <c r="H36" s="70" t="s">
+        <v>126</v>
+      </c>
       <c r="I36" s="74" t="s">
-        <v>126</v>
-      </c>
-      <c r="J36" s="75">
-        <f>AVERAGE(F36:F37)</f>
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>129</v>
+      </c>
+      <c r="J36" s="75"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="74" t="s">
         <v>122</v>
       </c>
@@ -5703,15 +5716,15 @@
       <c r="G37" s="76">
         <v>15.5</v>
       </c>
+      <c r="H37" s="70" t="s">
+        <v>127</v>
+      </c>
       <c r="I37" s="75" t="s">
-        <v>127</v>
-      </c>
-      <c r="J37" s="75">
-        <f>AVERAGE(F38:F39)</f>
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>129</v>
+      </c>
+      <c r="J37" s="75"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="74" t="s">
         <v>123</v>
       </c>
@@ -5733,8 +5746,14 @@
       <c r="G38" s="76">
         <v>17.3</v>
       </c>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="H38" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="I38" s="70" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="74" t="s">
         <v>124</v>
       </c>
@@ -5756,8 +5775,14 @@
       <c r="G39" s="76">
         <v>18.2</v>
       </c>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="H39" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" s="70" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="74" t="s">
         <v>125</v>
       </c>
@@ -5793,14 +5818,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.8">
+    <row r="1" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A1" s="69" t="s">
         <v>100</v>
       </c>
@@ -5811,33 +5836,33 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="73">
-        <f>'SK calcs'!J36</f>
-        <v>15.4</v>
+        <f>'SK calcs'!G36</f>
+        <v>15.6</v>
       </c>
       <c r="C2" s="73">
-        <f t="shared" ref="C2:C7" si="0">B2</f>
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <f>AVERAGE('SK calcs'!$G$38:$G$39)</f>
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
       <c r="B3" s="73">
-        <f>'SK calcs'!J37</f>
-        <v>16.8</v>
+        <f>'SK calcs'!G37</f>
+        <v>15.5</v>
       </c>
       <c r="C3" s="73">
-        <f t="shared" si="0"/>
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <f>AVERAGE('SK calcs'!$G$38:$G$39)</f>
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -5846,11 +5871,11 @@
         <v>24</v>
       </c>
       <c r="C4" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C2:C7" si="0">B4</f>
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -5863,7 +5888,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -5876,7 +5901,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -5896,15 +5921,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -6048,6 +6064,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6055,14 +6080,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A9F799-6530-441C-9A49-116D487C0166}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6076,6 +6093,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
+++ b/InputData/trans/AVL/Avg Vehicle Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2026\01.EPS\01.EI\01.메일\260108_메일회신\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\AVL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1944F64F-AD81-4996-A4B5-75E70CAE79BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C569AA2F-C350-4EDA-85E0-CDF30FF8D608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25260" yWindow="1515" windowWidth="24345" windowHeight="13980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="SK calcs" sheetId="12" r:id="rId4"/>
     <sheet name="AVL" sheetId="10" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="133">
   <si>
     <t>Car Avg Lifetime, years (Page 22, Table 7)</t>
   </si>
@@ -475,27 +475,30 @@
     <t>freight</t>
     <phoneticPr fontId="38" type="noConversion"/>
   </si>
+  <si>
+    <t>Passenger LDVs lifetime calculated by calibration</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="9">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="###0.00_)"/>
-    <numFmt numFmtId="178" formatCode="\(\R\)General"/>
-    <numFmt numFmtId="179" formatCode="\(\R\)\ ###0"/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="181" formatCode="\(\R\)0.0"/>
-    <numFmt numFmtId="182" formatCode="#,##0_)"/>
-    <numFmt numFmtId="183" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="184" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="###0.00_)"/>
+    <numFmt numFmtId="165" formatCode="\(\R\)General"/>
+    <numFmt numFmtId="166" formatCode="\(\R\)\ ###0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="\(\R\)0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0_)"/>
+    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -503,7 +506,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -511,7 +514,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -519,14 +522,14 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -534,7 +537,7 @@
       <u/>
       <sz val="10"/>
       <color theme="4"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -549,7 +552,7 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -566,14 +569,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -581,7 +584,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Cambria"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -589,7 +592,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -597,7 +600,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -605,35 +608,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -641,7 +644,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -649,14 +652,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -664,14 +667,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -679,21 +682,21 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -750,13 +753,13 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -764,7 +767,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1342,7 +1345,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10">
@@ -1399,10 +1402,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="33" fillId="0" borderId="10">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="10">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1507,10 +1510,10 @@
     <xf numFmtId="1" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1522,7 +1525,7 @@
     <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="59" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1542,21 +1545,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="61" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1579,16 +1582,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="183" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="37" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="183" fontId="24" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="183" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="39" fillId="0" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1598,83 +1613,71 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="63">
-    <cellStyle name="20% - 강조색1" xfId="35" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="39" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="43" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="47" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="51" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="55" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="36" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="40" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="44" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="48" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="52" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="56" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="37" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="41" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="45" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="49" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="53" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="57" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="35" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="39" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="43" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="47" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="51" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="55" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="36" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="40" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="44" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="48" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="52" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="56" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="37" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="41" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="45" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="49" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="53" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="57" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="34" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="38" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="42" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="46" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="50" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="54" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Body: normal cell" xfId="3" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Calculation" xfId="27" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="29" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="62" builtinId="3"/>
     <cellStyle name="Data" xfId="14" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
     <cellStyle name="Data no deci" xfId="61" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Explanatory Text" xfId="32" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="11" builtinId="9" customBuiltin="1"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="9" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="Footnotes: all except top row" xfId="12" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
     <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Good" xfId="22" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Header: bottom row" xfId="2" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="Header: top rows" xfId="4" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Heading 1" xfId="18" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="19" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="20" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="21" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Hed Side" xfId="15" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
     <cellStyle name="Hed Side Regular" xfId="60" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="Hed Top" xfId="59" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Input" xfId="25" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="28" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="31" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="26" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Percent" xfId="16" builtinId="5"/>
     <cellStyle name="Section Break" xfId="8" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="Section Break: parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="Table title" xfId="13" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Title" xfId="17" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Title-2" xfId="58" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="강조색1" xfId="34" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="38" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="42" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="46" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="50" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="54" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="30" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="27" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="23" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="31" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="백분율" xfId="16" builtinId="5"/>
-    <cellStyle name="보통" xfId="24" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="32" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="29" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="62" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="28" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="열어 본 하이퍼링크" xfId="11" builtinId="9" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="33" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="25" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="17" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="18" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="19" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="20" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="21" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="22" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="26" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Total" xfId="33" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="30" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -2007,17 +2010,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="132.25" customWidth="1"/>
+    <col min="2" max="2" width="132.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
@@ -2025,232 +2028,232 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="B5" s="9">
         <v>2006</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="B10" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="B12" s="9">
         <v>2016</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2">
       <c r="B17" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2">
       <c r="B19" s="9">
         <v>2015</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2">
       <c r="B21" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2">
       <c r="B24" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2">
       <c r="B25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2">
       <c r="B26" s="9">
         <v>2019</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2">
       <c r="B27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2">
       <c r="B28" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2">
       <c r="B30" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2">
       <c r="B31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2">
       <c r="B32" s="9">
         <v>2013</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2">
       <c r="B33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2">
       <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2">
       <c r="B35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2">
       <c r="B37" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2">
       <c r="B38" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2">
       <c r="B39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2">
       <c r="B40" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2">
       <c r="B41" s="19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2">
       <c r="B42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2">
       <c r="B44" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2">
       <c r="B45" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2">
       <c r="B46" s="9">
         <v>2009</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2">
       <c r="B47" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2">
       <c r="B48" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="B49" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>99</v>
       </c>
@@ -2271,72 +2274,72 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB61"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.375" customWidth="1"/>
-    <col min="2" max="27" width="7.75" customWidth="1"/>
-    <col min="28" max="28" width="7.125" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="27" width="7.7109375" customWidth="1"/>
+    <col min="28" max="28" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:54" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A1" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="82"/>
-      <c r="AG1" s="82"/>
-      <c r="AH1" s="82"/>
-      <c r="AI1" s="82"/>
-      <c r="AJ1" s="82"/>
-      <c r="AK1" s="82"/>
-      <c r="AL1" s="82"/>
-      <c r="AM1" s="82"/>
-      <c r="AN1" s="82"/>
-      <c r="AO1" s="82"/>
-      <c r="AP1" s="82"/>
-      <c r="AQ1" s="82"/>
-      <c r="AR1" s="82"/>
-      <c r="AS1" s="82"/>
-      <c r="AT1" s="82"/>
-      <c r="AU1" s="82"/>
-      <c r="AV1" s="82"/>
-      <c r="AW1" s="82"/>
-      <c r="AX1" s="82"/>
-      <c r="AY1" s="82"/>
-      <c r="AZ1" s="82"/>
-      <c r="BA1" s="82"/>
-      <c r="BB1" s="82"/>
-    </row>
-    <row r="2" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="79"/>
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
+      <c r="BA1" s="79"/>
+      <c r="BB1" s="79"/>
+    </row>
+    <row r="2" spans="1:54" ht="16.5" customHeight="1">
       <c r="A2" s="38"/>
       <c r="B2" s="39">
         <v>1980</v>
@@ -2446,7 +2449,7 @@
       <c r="BA2" s="45"/>
       <c r="BB2" s="46"/>
     </row>
-    <row r="3" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="16.5" customHeight="1">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
@@ -2558,7 +2561,7 @@
       <c r="BA3" s="48"/>
       <c r="BB3" s="48"/>
     </row>
-    <row r="4" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" ht="16.5" customHeight="1">
       <c r="A4" s="50" t="s">
         <v>67</v>
       </c>
@@ -2670,7 +2673,7 @@
       <c r="BA4" s="52"/>
       <c r="BB4" s="52"/>
     </row>
-    <row r="5" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" ht="16.5" customHeight="1">
       <c r="A5" s="50" t="s">
         <v>68</v>
       </c>
@@ -2782,7 +2785,7 @@
       <c r="BA5" s="52"/>
       <c r="BB5" s="52"/>
     </row>
-    <row r="6" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" ht="16.5" customHeight="1">
       <c r="A6" s="50" t="s">
         <v>69</v>
       </c>
@@ -2894,7 +2897,7 @@
       <c r="BA6" s="52"/>
       <c r="BB6" s="52"/>
     </row>
-    <row r="7" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" ht="16.5" customHeight="1">
       <c r="A7" s="50" t="s">
         <v>70</v>
       </c>
@@ -3006,7 +3009,7 @@
       <c r="BA7" s="52"/>
       <c r="BB7" s="52"/>
     </row>
-    <row r="8" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" ht="16.5" customHeight="1">
       <c r="A8" s="50" t="s">
         <v>71</v>
       </c>
@@ -3118,7 +3121,7 @@
       <c r="BA8" s="52"/>
       <c r="BB8" s="52"/>
     </row>
-    <row r="9" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" ht="16.5" customHeight="1">
       <c r="A9" s="53" t="s">
         <v>72</v>
       </c>
@@ -3176,7 +3179,7 @@
       <c r="BA9" s="54"/>
       <c r="BB9" s="54"/>
     </row>
-    <row r="10" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" ht="16.5" customHeight="1">
       <c r="A10" s="50" t="s">
         <v>67</v>
       </c>
@@ -3290,7 +3293,7 @@
       <c r="BA10" s="56"/>
       <c r="BB10" s="56"/>
     </row>
-    <row r="11" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="16.5" customHeight="1">
       <c r="A11" s="50" t="s">
         <v>68</v>
       </c>
@@ -3402,7 +3405,7 @@
       <c r="BA11" s="56"/>
       <c r="BB11" s="56"/>
     </row>
-    <row r="12" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" ht="16.5" customHeight="1">
       <c r="A12" s="50" t="s">
         <v>69</v>
       </c>
@@ -3514,7 +3517,7 @@
       <c r="BA12" s="56"/>
       <c r="BB12" s="56"/>
     </row>
-    <row r="13" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" ht="16.5" customHeight="1">
       <c r="A13" s="50" t="s">
         <v>70</v>
       </c>
@@ -3626,7 +3629,7 @@
       <c r="BA13" s="56"/>
       <c r="BB13" s="56"/>
     </row>
-    <row r="14" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" ht="16.5" customHeight="1">
       <c r="A14" s="50" t="s">
         <v>71</v>
       </c>
@@ -3738,7 +3741,7 @@
       <c r="BA14" s="56"/>
       <c r="BB14" s="56"/>
     </row>
-    <row r="15" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" ht="16.5" customHeight="1">
       <c r="A15" s="47" t="s">
         <v>73</v>
       </c>
@@ -3796,7 +3799,7 @@
       <c r="BA15" s="58"/>
       <c r="BB15" s="58"/>
     </row>
-    <row r="16" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" ht="16.5" customHeight="1">
       <c r="A16" s="50" t="s">
         <v>67</v>
       </c>
@@ -3908,7 +3911,7 @@
       <c r="BA16" s="59"/>
       <c r="BB16" s="59"/>
     </row>
-    <row r="17" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" ht="16.5" customHeight="1">
       <c r="A17" s="50" t="s">
         <v>68</v>
       </c>
@@ -4020,7 +4023,7 @@
       <c r="BA17" s="59"/>
       <c r="BB17" s="59"/>
     </row>
-    <row r="18" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" ht="16.5" customHeight="1">
       <c r="A18" s="50" t="s">
         <v>69</v>
       </c>
@@ -4132,7 +4135,7 @@
       <c r="BA18" s="59"/>
       <c r="BB18" s="59"/>
     </row>
-    <row r="19" spans="1:54" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" ht="16.5" customHeight="1">
       <c r="A19" s="50" t="s">
         <v>70</v>
       </c>
@@ -4244,7 +4247,7 @@
       <c r="BA19" s="59"/>
       <c r="BB19" s="59"/>
     </row>
-    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:54" ht="16.5" customHeight="1" thickBot="1">
       <c r="A20" s="60" t="s">
         <v>71</v>
       </c>
@@ -4356,68 +4359,68 @@
       <c r="BA20" s="59"/>
       <c r="BB20" s="59"/>
     </row>
-    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="83" t="s">
+    <row r="21" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A21" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-    </row>
-    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="84"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-    </row>
-    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="84" t="s">
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+    </row>
+    <row r="22" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A22" s="81"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="81"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="81"/>
+    </row>
+    <row r="23" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A23" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="84"/>
-      <c r="P23" s="84"/>
-      <c r="Q23" s="84"/>
-    </row>
-    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="81"/>
+      <c r="Q23" s="81"/>
+    </row>
+    <row r="24" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
       <c r="A24" s="77" t="s">
         <v>76</v>
       </c>
@@ -4438,7 +4441,7 @@
       <c r="P24" s="77"/>
       <c r="Q24" s="77"/>
     </row>
-    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
       <c r="A25" s="77" t="s">
         <v>77</v>
       </c>
@@ -4459,130 +4462,130 @@
       <c r="P25" s="77"/>
       <c r="Q25" s="77"/>
     </row>
-    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="78" t="s">
+    <row r="26" spans="1:54" s="63" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A26" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
-      <c r="N26" s="78"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="78"/>
-    </row>
-    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="78"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="78"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
-      <c r="Q27" s="78"/>
-    </row>
-    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="79" t="s">
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+    </row>
+    <row r="27" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A27" s="82"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="82"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+    </row>
+    <row r="28" spans="1:54" s="63" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A28" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="79"/>
-      <c r="Q28" s="79"/>
-    </row>
-    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="80" t="s">
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+    </row>
+    <row r="29" spans="1:54" s="63" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A29" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="80"/>
-      <c r="M29" s="80"/>
-      <c r="N29" s="80"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="80"/>
-      <c r="Q29" s="80"/>
-    </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.3"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="84"/>
+    </row>
+    <row r="33" customFormat="1"/>
+    <row r="34" customFormat="1"/>
+    <row r="35" customFormat="1"/>
+    <row r="36" customFormat="1"/>
+    <row r="37" customFormat="1"/>
+    <row r="38" customFormat="1"/>
+    <row r="39" customFormat="1"/>
+    <row r="40" customFormat="1"/>
+    <row r="41" customFormat="1"/>
+    <row r="42" customFormat="1"/>
+    <row r="43" customFormat="1"/>
+    <row r="44" customFormat="1"/>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
+    <row r="47" customFormat="1"/>
+    <row r="48" customFormat="1"/>
+    <row r="49" customFormat="1"/>
+    <row r="50" customFormat="1"/>
+    <row r="51" customFormat="1"/>
+    <row r="52" customFormat="1"/>
+    <row r="53" customFormat="1"/>
+    <row r="54" customFormat="1"/>
+    <row r="55" customFormat="1"/>
+    <row r="56" customFormat="1"/>
+    <row r="57" customFormat="1"/>
+    <row r="58" customFormat="1"/>
+    <row r="59" customFormat="1"/>
+    <row r="60" customFormat="1"/>
+    <row r="61" customFormat="1"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A25:Q25"/>
+    <mergeCell ref="A26:Q26"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="A29:Q29"/>
     <mergeCell ref="A24:Q24"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="AC1:BB1"/>
     <mergeCell ref="A21:Q21"/>
     <mergeCell ref="A22:Q22"/>
     <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A25:Q25"/>
-    <mergeCell ref="A26:Q26"/>
-    <mergeCell ref="A27:Q27"/>
-    <mergeCell ref="A28:Q28"/>
-    <mergeCell ref="A29:Q29"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4592,17 +4595,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.125" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9.125" style="3"/>
+    <col min="1" max="1" width="30.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -4611,7 +4614,7 @@
       <c r="D1" s="33"/>
       <c r="E1" s="33"/>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="60">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4628,7 +4631,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15.75" thickBot="1">
       <c r="A3" s="3">
         <v>13</v>
       </c>
@@ -4648,12 +4651,12 @@
         <v>13.378781688359696</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1">
       <c r="A5" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="7" t="s">
         <v>59</v>
       </c>
@@ -4668,7 +4671,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1">
       <c r="A7" s="68">
         <v>28</v>
       </c>
@@ -4683,7 +4686,7 @@
       </c>
       <c r="E7" s="67"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="10" t="s">
         <v>56</v>
       </c>
@@ -4692,14 +4695,14 @@
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" s="9" customFormat="1">
       <c r="A11" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" s="9" customFormat="1">
       <c r="A12" s="9" t="s">
         <v>34</v>
       </c>
@@ -4707,7 +4710,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" s="9" customFormat="1">
       <c r="A13" s="9" t="s">
         <v>36</v>
       </c>
@@ -4715,7 +4718,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" s="9" customFormat="1" ht="15.75" thickBot="1">
       <c r="A14" s="9" t="s">
         <v>38</v>
       </c>
@@ -4723,17 +4726,17 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" s="9" customFormat="1">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="9" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" s="9" customFormat="1" ht="15.75" thickBot="1">
       <c r="A16" s="18">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="10" t="s">
         <v>21</v>
       </c>
@@ -4742,7 +4745,7 @@
       <c r="D18" s="34"/>
       <c r="E18" s="34"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="15" t="s">
         <v>10</v>
       </c>
@@ -4753,7 +4756,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="15.75" thickBot="1">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4775,7 +4778,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15.75" thickBot="1">
       <c r="A22"/>
       <c r="B22" s="11" t="s">
         <v>26</v>
@@ -4784,17 +4787,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="10" t="s">
         <v>13</v>
       </c>
@@ -4803,7 +4806,7 @@
       <c r="D26" s="34"/>
       <c r="E26" s="34"/>
     </row>
-    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="15.75" thickBot="1">
       <c r="A27" s="15" t="s">
         <v>10</v>
       </c>
@@ -4814,7 +4817,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="15.75" thickBot="1">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -4825,7 +4828,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="15.75" thickBot="1">
       <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
@@ -4834,7 +4837,7 @@
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
     </row>
-    <row r="31" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="21" t="s">
         <v>43</v>
       </c>
@@ -4851,7 +4854,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="20">
         <v>1997</v>
       </c>
@@ -4864,7 +4867,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="20">
         <v>1998</v>
       </c>
@@ -4883,7 +4886,7 @@
         <v>6.6484424338501588E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="20">
         <v>1999</v>
       </c>
@@ -4902,7 +4905,7 @@
         <v>2.9143636995467476E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="20">
         <v>2000</v>
       </c>
@@ -4921,7 +4924,7 @@
         <v>6.8191523924614153E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="20">
         <v>2001</v>
       </c>
@@ -4940,7 +4943,7 @@
         <v>4.0815360868813244E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="20">
         <v>2002</v>
       </c>
@@ -4959,7 +4962,7 @@
         <v>0.10769048766665149</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="20">
         <v>2003</v>
       </c>
@@ -4978,7 +4981,7 @@
         <v>5.9053805049687755E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="20">
         <v>2004</v>
       </c>
@@ -4997,7 +5000,7 @@
         <v>5.8670234757052138E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="20">
         <v>2005</v>
       </c>
@@ -5016,7 +5019,7 @@
         <v>6.1781753631599455E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="20">
         <v>2006</v>
       </c>
@@ -5035,7 +5038,7 @@
         <v>6.5906687839630079E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15.75" thickBot="1">
       <c r="A42" s="25">
         <v>2007</v>
       </c>
@@ -5054,14 +5057,14 @@
         <v>5.9604038733197397E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -5069,7 +5072,7 @@
       <c r="C44"/>
       <c r="D44"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="28">
         <f>AVERAGE(E33:E42)</f>
         <v>5.8060812902328285E-2</v>
@@ -5078,13 +5081,13 @@
       <c r="C45"/>
       <c r="D45"/>
     </row>
-    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="15.75" thickBot="1">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
       <c r="D46"/>
     </row>
-    <row r="47" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="30">
       <c r="A47" s="36" t="s">
         <v>48</v>
       </c>
@@ -5092,7 +5095,7 @@
       <c r="C47"/>
       <c r="D47"/>
     </row>
-    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="15.75" thickBot="1">
       <c r="A48" s="35">
         <f>1/A45</f>
         <v>17.22332068760786</v>
@@ -5112,25 +5115,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD149825-14BA-415D-91AD-354F00EEF420}">
-  <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K43"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="70" customWidth="1"/>
-    <col min="2" max="2" width="11.125" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="70" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" style="70" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="70" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="70" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.125" style="70" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.75" style="70"/>
+    <col min="1" max="1" width="19.140625" style="70" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.42578125" style="70" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="70" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="70"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="70" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="70" t="s">
         <v>101</v>
       </c>
@@ -5156,7 +5159,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="B3" s="70" t="s">
         <v>52</v>
       </c>
@@ -5182,7 +5185,7 @@
         <v>7728.5710293009906</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="70" t="s">
         <v>55</v>
       </c>
@@ -5208,7 +5211,7 @@
         <v>3161.4504274369956</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="B5" s="70" t="s">
         <v>56</v>
       </c>
@@ -5234,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="B6" s="70" t="s">
         <v>21</v>
       </c>
@@ -5260,7 +5263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="B7" s="70" t="s">
         <v>13</v>
       </c>
@@ -5286,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="B8" s="70" t="s">
         <v>58</v>
       </c>
@@ -5312,12 +5315,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="70" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="B11" s="70" t="s">
         <v>101</v>
       </c>
@@ -5343,7 +5346,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="B12" s="70" t="s">
         <v>52</v>
       </c>
@@ -5369,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="B13" s="70" t="s">
         <v>55</v>
       </c>
@@ -5395,7 +5398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="B14" s="70" t="s">
         <v>56</v>
       </c>
@@ -5421,7 +5424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="B15" s="70" t="s">
         <v>21</v>
       </c>
@@ -5447,7 +5450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="B16" s="70" t="s">
         <v>13</v>
       </c>
@@ -5473,7 +5476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="B17" s="70" t="s">
         <v>58</v>
       </c>
@@ -5499,12 +5502,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="70" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="B22" s="70">
         <v>2019</v>
       </c>
@@ -5512,7 +5515,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="70" t="s">
         <v>111</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>11.724644713881862</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="70" t="s">
         <v>112</v>
       </c>
@@ -5544,7 +5547,7 @@
         <v>11.325209578137313</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="70" t="s">
         <v>113</v>
       </c>
@@ -5556,7 +5559,7 @@
         <v>0.27844474080318277</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="70" t="s">
         <v>114</v>
       </c>
@@ -5568,13 +5571,13 @@
         <v>0.38904941180819808</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="C27" s="72"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="C28" s="72"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="70" t="s">
         <v>115</v>
       </c>
@@ -5590,7 +5593,7 @@
         <v>20.43541033331925</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="70" t="s">
         <v>116</v>
       </c>
@@ -5606,7 +5609,7 @@
         <v>13.907940419258974</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="70" t="s">
         <v>117</v>
       </c>
@@ -5618,7 +5621,7 @@
         <v>6.8718275287445466E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="70" t="s">
         <v>118</v>
       </c>
@@ -5630,7 +5633,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34" s="74" t="s">
         <v>128</v>
       </c>
@@ -5641,7 +5644,7 @@
       <c r="F34" s="74"/>
       <c r="G34" s="74"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35" s="74"/>
       <c r="B35" s="74">
         <v>2000</v>
@@ -5664,7 +5667,7 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36" s="74" t="s">
         <v>121</v>
       </c>
@@ -5694,7 +5697,7 @@
       </c>
       <c r="J36" s="75"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37" s="74" t="s">
         <v>122</v>
       </c>
@@ -5724,7 +5727,7 @@
       </c>
       <c r="J37" s="75"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38" s="74" t="s">
         <v>123</v>
       </c>
@@ -5753,7 +5756,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39" s="74" t="s">
         <v>124</v>
       </c>
@@ -5782,7 +5785,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40" s="74" t="s">
         <v>125</v>
       </c>
@@ -5803,6 +5806,11 @@
       </c>
       <c r="G40" s="76">
         <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="70" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -5818,14 +5826,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="45">
       <c r="A1" s="69" t="s">
         <v>100</v>
       </c>
@@ -5836,20 +5844,19 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="73">
-        <f>'SK calcs'!G36</f>
-        <v>15.6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="73">
         <f>AVERAGE('SK calcs'!$G$38:$G$39)</f>
         <v>17.75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -5862,7 +5869,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -5871,11 +5878,11 @@
         <v>24</v>
       </c>
       <c r="C4" s="37">
-        <f t="shared" ref="C2:C7" si="0">B4</f>
+        <f t="shared" ref="C4:C7" si="0">B4</f>
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -5888,7 +5895,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -5901,7 +5908,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -5921,6 +5928,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -6064,15 +6080,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6080,6 +6087,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A9F799-6530-441C-9A49-116D487C0166}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6093,14 +6108,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C589ED-403D-43C7-8D67-619C9CBC31EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
